--- a/VerveStacks_CHN_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C6BF26-0FF4-439B-8568-5F39889B6EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88AB956-5AA1-4B61-912D-3975EF50FF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1815,6 +1815,366 @@
     <t>connecting solar to buses in cluster 119</t>
   </si>
   <si>
+    <t>distr_solelc_spv_CHN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_132</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 132</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_122</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 122</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_133</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 133</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_128</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 128</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_134</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 134</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_135</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 135</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_120</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 120</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_136</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 136</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_116</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 116</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_118</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 118</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_130</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 130</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_CHN_078</t>
   </si>
   <si>
@@ -1845,6 +2205,102 @@
     <t>connecting solar to buses in cluster 114</t>
   </si>
   <si>
+    <t>distr_solelc_spv_CHN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_127</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 127</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_129</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 129</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_121</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 121</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_123</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 123</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_CHN_001</t>
   </si>
   <si>
@@ -1881,6 +2337,42 @@
     <t>connecting solar to buses in cluster 115</t>
   </si>
   <si>
+    <t>distr_solelc_spv_CHN_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_124</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 124</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_CHN_032</t>
   </si>
   <si>
@@ -1917,6 +2409,66 @@
     <t>connecting solar to buses in cluster 106</t>
   </si>
   <si>
+    <t>distr_solelc_spv_CHN_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_126</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 126</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_CHN_012</t>
   </si>
   <si>
@@ -1971,438 +2523,6 @@
     <t>connecting solar to buses in cluster 131</t>
   </si>
   <si>
-    <t>distr_solelc_spv_CHN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_121</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 121</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_123</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 123</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_128</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 128</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_134</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 134</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_135</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 135</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_124</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 124</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_132</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 132</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_127</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 127</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_129</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 129</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_120</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 120</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_136</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 136</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_116</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 116</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_118</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 118</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_130</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 130</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_CHN_016</t>
   </si>
   <si>
@@ -2457,126 +2577,6 @@
     <t>connecting solar to buses in cluster 117</t>
   </si>
   <si>
-    <t>distr_solelc_spv_CHN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_122</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 122</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_133</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 133</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_126</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 126</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -2604,13 +2604,112 @@
     <t>e_CHN44p4N121p8E_CHN</t>
   </si>
   <si>
+    <t>e_Yiyang_CHN</t>
+  </si>
+  <si>
+    <t>e_Chongqing_CHN</t>
+  </si>
+  <si>
+    <t>e_Kuqa_CHN</t>
+  </si>
+  <si>
+    <t>e_CHN45p9N129p3E_CHN</t>
+  </si>
+  <si>
+    <t>e_Shaoguan_CHN</t>
+  </si>
+  <si>
+    <t>e_Rizhao_CHN</t>
+  </si>
+  <si>
+    <t>e_Wuan_CHN</t>
+  </si>
+  <si>
+    <t>e_Yakeshi_CHN</t>
+  </si>
+  <si>
+    <t>e_Linyi_CHN</t>
+  </si>
+  <si>
+    <t>e_Wulan_CHN</t>
+  </si>
+  <si>
+    <t>e_Yangjiang_CHN</t>
+  </si>
+  <si>
+    <t>e_Xichang_CHN</t>
+  </si>
+  <si>
+    <t>e_Mianyang_CHN</t>
+  </si>
+  <si>
+    <t>e_Sizhan_CHN</t>
+  </si>
+  <si>
+    <t>e_Tianjin_CHN</t>
+  </si>
+  <si>
+    <t>e_Hangzhou_CHN</t>
+  </si>
+  <si>
+    <t>e_Fangchenggang_CHN</t>
+  </si>
+  <si>
+    <t>e_Hohhot_CHN</t>
+  </si>
+  <si>
+    <t>e_Qabqa_CHN</t>
+  </si>
+  <si>
+    <t>e_Yuanquan_CHN</t>
+  </si>
+  <si>
+    <t>e_CHN44p2N116p5E_CHN</t>
+  </si>
+  <si>
+    <t>e_Tongling_CHN</t>
+  </si>
+  <si>
+    <t>e_Shijiazhuang_CHN</t>
+  </si>
+  <si>
+    <t>e_Sanhe_CHN</t>
+  </si>
+  <si>
+    <t>e_Liuzhou_CHN</t>
+  </si>
+  <si>
+    <t>e_Jingling_CHN</t>
+  </si>
+  <si>
+    <t>e_Beichengqu_CHN</t>
+  </si>
+  <si>
+    <t>e_Yanggezhuang_CHN</t>
+  </si>
+  <si>
+    <t>e_Liaoyang_CHN</t>
+  </si>
+  <si>
+    <t>e_Anqing_CHN</t>
+  </si>
+  <si>
+    <t>e_Manlin_CHN</t>
+  </si>
+  <si>
     <t>e_Luohe_CHN</t>
   </si>
   <si>
-    <t>e_Rizhao_CHN</t>
-  </si>
-  <si>
-    <t>e_Yuanquan_CHN</t>
+    <t>e_Ningde_CHN</t>
+  </si>
+  <si>
+    <t>e_Wuhan_CHN</t>
+  </si>
+  <si>
+    <t>e_Jinbi_CHN</t>
+  </si>
+  <si>
+    <t>e_Tongshan_CHN</t>
   </si>
   <si>
     <t>e_Nantong_CHN</t>
@@ -2619,22 +2718,31 @@
     <t>e_Hejin_CHN</t>
   </si>
   <si>
+    <t>e_Fuzhou_CHN</t>
+  </si>
+  <si>
+    <t>e_Xiaoyi_CHN</t>
+  </si>
+  <si>
+    <t>e_Changzhou_CHN</t>
+  </si>
+  <si>
     <t>e_Shanghai_CHN</t>
   </si>
   <si>
-    <t>e_CHN45p9N129p3E_CHN</t>
-  </si>
-  <si>
     <t>e_Xiaoxita_CHN</t>
   </si>
   <si>
-    <t>e_Wulan_CHN</t>
+    <t>e_Nanjing_CHN</t>
   </si>
   <si>
     <t>e_Zouping_CHN</t>
   </si>
   <si>
-    <t>e_Mianyang_CHN</t>
+    <t>e_Dayan_CHN</t>
+  </si>
+  <si>
+    <t>e_Tangshan_CHN</t>
   </si>
   <si>
     <t>e_Anshun_CHN</t>
@@ -2643,121 +2751,175 @@
     <t>e_Putian_CHN</t>
   </si>
   <si>
-    <t>e_Jingling_CHN</t>
-  </si>
-  <si>
-    <t>e_Fuzhou_CHN</t>
-  </si>
-  <si>
     <t>e_Yangzhou_CHN</t>
   </si>
   <si>
-    <t>e_Tongshan_CHN</t>
-  </si>
-  <si>
-    <t>e_Wuhan_CHN</t>
-  </si>
-  <si>
-    <t>e_Changzhou_CHN</t>
-  </si>
-  <si>
-    <t>e_Yiyang_CHN</t>
-  </si>
-  <si>
-    <t>e_Sizhan_CHN</t>
-  </si>
-  <si>
-    <t>e_Tianjin_CHN</t>
-  </si>
-  <si>
-    <t>e_Hangzhou_CHN</t>
-  </si>
-  <si>
-    <t>e_Fangchenggang_CHN</t>
-  </si>
-  <si>
-    <t>e_Hohhot_CHN</t>
-  </si>
-  <si>
-    <t>e_Qabqa_CHN</t>
-  </si>
-  <si>
-    <t>e_Shaoguan_CHN</t>
-  </si>
-  <si>
-    <t>e_CHN44p2N116p5E_CHN</t>
-  </si>
-  <si>
-    <t>e_Tongling_CHN</t>
-  </si>
-  <si>
-    <t>e_Shijiazhuang_CHN</t>
-  </si>
-  <si>
-    <t>e_Sanhe_CHN</t>
-  </si>
-  <si>
-    <t>e_Liuzhou_CHN</t>
-  </si>
-  <si>
-    <t>e_Beichengqu_CHN</t>
-  </si>
-  <si>
-    <t>e_Yanggezhuang_CHN</t>
-  </si>
-  <si>
-    <t>e_Liaoyang_CHN</t>
-  </si>
-  <si>
-    <t>e_Anqing_CHN</t>
-  </si>
-  <si>
-    <t>e_Kuqa_CHN</t>
-  </si>
-  <si>
-    <t>e_Nanjing_CHN</t>
-  </si>
-  <si>
-    <t>e_Chongqing_CHN</t>
-  </si>
-  <si>
-    <t>e_Wuan_CHN</t>
-  </si>
-  <si>
-    <t>e_Yangjiang_CHN</t>
-  </si>
-  <si>
-    <t>e_Xiaoyi_CHN</t>
-  </si>
-  <si>
-    <t>e_Yakeshi_CHN</t>
-  </si>
-  <si>
-    <t>e_Manlin_CHN</t>
-  </si>
-  <si>
-    <t>e_Ningde_CHN</t>
-  </si>
-  <si>
-    <t>e_Jinbi_CHN</t>
-  </si>
-  <si>
     <t>e_Bayi_CHN</t>
   </si>
   <si>
     <t>e_Yicheng_CHN</t>
   </si>
   <si>
-    <t>e_Linyi_CHN</t>
-  </si>
-  <si>
-    <t>e_Xichang_CHN</t>
-  </si>
-  <si>
-    <t>e_Dayan_CHN</t>
-  </si>
-  <si>
-    <t>e_Tangshan_CHN</t>
+    <t>distr_wonelc_won_CHN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_080</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_107</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_081</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_085</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_086</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_088</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_092</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_095</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_096</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_106</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_091</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 91</t>
   </si>
   <si>
     <t>distr_wonelc_won_CHN_039</t>
@@ -2814,6 +2976,264 @@
     <t>connecting wind onshore to buses in cluster 105</t>
   </si>
   <si>
+    <t>distr_wonelc_won_CHN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_090</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_102</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_113</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_093</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_082</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_072</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_074</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_078</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_079</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_111</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_073</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_077</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_084</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_089</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_109</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_083</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_103</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_108</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_112</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 112</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_CHN_004</t>
   </si>
   <si>
@@ -2868,102 +3288,6 @@
     <t>connecting wind onshore to buses in cluster 100</t>
   </si>
   <si>
-    <t>distr_wonelc_won_CHN_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_083</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_103</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_108</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_112</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_073</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_077</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_084</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_089</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_109</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 109</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_CHN_006</t>
   </si>
   <si>
@@ -3000,90 +3324,6 @@
     <t>connecting wind onshore to buses in cluster 110</t>
   </si>
   <si>
-    <t>distr_wonelc_won_CHN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_082</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_080</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_107</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_091</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 91</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_CHN_001</t>
   </si>
   <si>
@@ -3114,142 +3354,34 @@
     <t>connecting wind onshore to buses in cluster 61</t>
   </si>
   <si>
-    <t>distr_wonelc_won_CHN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_090</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_102</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_113</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_081</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_085</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_086</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_088</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_093</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 93</t>
+    <t>distr_wonelc_won_CHN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_099</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_104</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 104</t>
   </si>
   <si>
     <t>distr_wonelc_won_CHN_003</t>
@@ -3306,136 +3438,85 @@
     <t>connecting wind onshore to buses in cluster 101</t>
   </si>
   <si>
-    <t>distr_wonelc_won_CHN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_072</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_074</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_078</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_079</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_111</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_092</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_095</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_096</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_106</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_099</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_104</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 104</t>
+    <t>elc_won_CHN_010</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_043</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_080</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_107</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_013</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_020</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_024</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_033</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_057</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_081</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_085</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_086</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_088</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_025</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_034</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_037</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_042</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_092</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_095</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_096</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_106</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_008</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_016</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_062</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_063</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_069</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_091</t>
   </si>
   <si>
     <t>elc_won_CHN_039</t>
@@ -3465,6 +3546,135 @@
     <t>elc_won_CHN_105</t>
   </si>
   <si>
+    <t>elc_won_CHN_002</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_018</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_028</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_031</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_041</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_049</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_090</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_102</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_113</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_023</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_029</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_036</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_053</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_093</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_015</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_019</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_060</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_082</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_007</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_009</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_011</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_021</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_072</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_074</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_078</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_079</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_111</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_038</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_040</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_050</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_055</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_073</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_077</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_084</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_089</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_109</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_035</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_064</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_066</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_083</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_103</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_108</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_112</t>
+  </si>
+  <si>
     <t>elc_won_CHN_004</t>
   </si>
   <si>
@@ -3492,54 +3702,6 @@
     <t>elc_won_CHN_100</t>
   </si>
   <si>
-    <t>elc_won_CHN_035</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_064</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_066</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_083</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_103</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_108</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_112</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_038</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_040</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_050</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_055</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_073</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_077</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_084</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_089</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_109</t>
-  </si>
-  <si>
     <t>elc_won_CHN_006</t>
   </si>
   <si>
@@ -3558,48 +3720,6 @@
     <t>elc_won_CHN_110</t>
   </si>
   <si>
-    <t>elc_won_CHN_015</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_019</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_060</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_082</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_010</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_043</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_080</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_107</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_008</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_016</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_062</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_063</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_069</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_091</t>
-  </si>
-  <si>
     <t>elc_won_CHN_001</t>
   </si>
   <si>
@@ -3615,73 +3735,19 @@
     <t>elc_won_CHN_061</t>
   </si>
   <si>
-    <t>elc_won_CHN_002</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_018</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_028</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_031</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_041</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_049</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_090</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_102</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_113</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_013</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_020</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_024</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_033</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_057</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_081</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_085</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_086</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_088</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_023</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_029</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_036</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_053</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_093</t>
+    <t>elc_won_CHN_012</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_054</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_068</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_099</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_104</t>
   </si>
   <si>
     <t>elc_won_CHN_003</t>
@@ -3711,70 +3777,28 @@
     <t>elc_won_CHN_101</t>
   </si>
   <si>
-    <t>elc_won_CHN_007</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_009</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_011</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_021</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_072</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_074</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_078</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_079</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_111</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_025</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_034</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_037</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_042</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_092</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_095</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_096</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_106</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_012</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_054</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_068</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_099</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_104</t>
+    <t>distr_wofelc_wof_CHN_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wofelc_wof_CHN_029</t>
@@ -3783,6 +3807,108 @@
     <t>connecting wind offshore to buses in cluster 29</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_CHN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_CHN_015</t>
   </si>
   <si>
@@ -3795,22 +3921,28 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_CHN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
+    <t>distr_wofelc_wof_CHN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
   </si>
   <si>
     <t>distr_wofelc_wof_CHN_032</t>
@@ -3819,30 +3951,6 @@
     <t>connecting wind offshore to buses in cluster 32</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_CHN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_CHN_003</t>
   </si>
   <si>
@@ -3855,114 +3963,6 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_CHN_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_CHN_006</t>
   </si>
   <si>
@@ -3981,97 +3981,97 @@
     <t>connecting wind offshore to buses in cluster 25</t>
   </si>
   <si>
+    <t>elc_wof_CHN_011</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_001</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_019</t>
+  </si>
+  <si>
     <t>elc_wof_CHN_029</t>
   </si>
   <si>
+    <t>elc_wof_CHN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_016</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_018</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_022</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_005</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_008</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_028</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_031</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_013</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_027</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_026</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_034</t>
+  </si>
+  <si>
     <t>elc_wof_CHN_015</t>
   </si>
   <si>
     <t>elc_wof_CHN_017</t>
   </si>
   <si>
-    <t>elc_wof_CHN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_031</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_027</t>
+    <t>elc_wof_CHN_014</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_030</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_033</t>
   </si>
   <si>
     <t>elc_wof_CHN_032</t>
   </si>
   <si>
-    <t>elc_wof_CHN_014</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_023</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_030</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_033</t>
-  </si>
-  <si>
     <t>elc_wof_CHN_003</t>
   </si>
   <si>
     <t>elc_wof_CHN_012</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_011</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_026</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_034</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_005</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_008</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_028</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_013</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_010</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_019</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_016</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_018</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_022</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_024</t>
   </si>
   <si>
     <t>elc_wof_CHN_006</t>
@@ -10134,7 +10134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00738E49-D95D-4011-8B8E-F8771609BEE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194A03C1-1F29-4B4E-9021-2234FCFF78A8}">
   <dimension ref="B9:BD146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10411,13 +10411,13 @@
         <v>1124</v>
       </c>
       <c r="AN11" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="AO11">
-        <v>0.99430130634228164</v>
+        <v>0.96363263183226566</v>
       </c>
       <c r="AP11">
-        <v>104.47605039150224</v>
+        <v>666.73508307513055</v>
       </c>
       <c r="AR11" t="s">
         <v>562</v>
@@ -10447,13 +10447,13 @@
         <v>1305</v>
       </c>
       <c r="BB11" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="BC11">
-        <v>0.98475443499607906</v>
+        <v>0.90777469227524876</v>
       </c>
       <c r="BD11">
-        <v>601.9858707809102</v>
+        <v>1208.8428425634561</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10557,13 +10557,13 @@
         <v>1125</v>
       </c>
       <c r="AN12" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
       <c r="AO12">
-        <v>0.99215445883125275</v>
+        <v>0.99153439104508034</v>
       </c>
       <c r="AP12">
-        <v>143.83492142703278</v>
+        <v>155.20283084019445</v>
       </c>
       <c r="AR12" t="s">
         <v>562</v>
@@ -10593,13 +10593,13 @@
         <v>1306</v>
       </c>
       <c r="BB12" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="BC12">
-        <v>0.98029614417839783</v>
+        <v>0.97748676055693473</v>
       </c>
       <c r="BD12">
-        <v>637.13206339363023</v>
+        <v>659.27937094283163</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10703,13 +10703,13 @@
         <v>1126</v>
       </c>
       <c r="AN13" t="s">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="AO13">
-        <v>0.97814391961975855</v>
+        <v>0.98940041671700285</v>
       </c>
       <c r="AP13">
-        <v>400.69480697109378</v>
+        <v>194.32569352161357</v>
       </c>
       <c r="AR13" t="s">
         <v>562</v>
@@ -10739,13 +10739,13 @@
         <v>1307</v>
       </c>
       <c r="BB13" t="s">
-        <v>886</v>
+        <v>841</v>
       </c>
       <c r="BC13">
-        <v>0.98865855459335616</v>
+        <v>0.98661815843628831</v>
       </c>
       <c r="BD13">
-        <v>571.20839462237564</v>
+        <v>587.29351766059415</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10849,13 +10849,13 @@
         <v>1127</v>
       </c>
       <c r="AN14" t="s">
-        <v>856</v>
+        <v>866</v>
       </c>
       <c r="AO14">
-        <v>0.99224639661619274</v>
+        <v>0.98639521029542421</v>
       </c>
       <c r="AP14">
-        <v>142.14939536980046</v>
+        <v>249.42114458389037</v>
       </c>
       <c r="AR14" t="s">
         <v>562</v>
@@ -10885,13 +10885,13 @@
         <v>1308</v>
       </c>
       <c r="BB14" t="s">
-        <v>851</v>
+        <v>894</v>
       </c>
       <c r="BC14">
-        <v>0.97775230782134392</v>
+        <v>0.99038640993878491</v>
       </c>
       <c r="BD14">
-        <v>657.18597334173887</v>
+        <v>557.58713498257862</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10995,13 +10995,13 @@
         <v>1128</v>
       </c>
       <c r="AN15" t="s">
-        <v>878</v>
+        <v>840</v>
       </c>
       <c r="AO15">
-        <v>0.98477063994548064</v>
+        <v>0.98896692202674552</v>
       </c>
       <c r="AP15">
-        <v>279.20493433285503</v>
+        <v>202.27309617633225</v>
       </c>
       <c r="AR15" t="s">
         <v>562</v>
@@ -11031,13 +11031,13 @@
         <v>1309</v>
       </c>
       <c r="BB15" t="s">
-        <v>847</v>
+        <v>878</v>
       </c>
       <c r="BC15">
-        <v>0.97884476097844741</v>
+        <v>0.98475443499607906</v>
       </c>
       <c r="BD15">
-        <v>648.57380095323958</v>
+        <v>601.9858707809102</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -11141,13 +11141,13 @@
         <v>1129</v>
       </c>
       <c r="AN16" t="s">
-        <v>872</v>
+        <v>853</v>
       </c>
       <c r="AO16">
-        <v>0.98880526729129725</v>
+        <v>0.99224743662419923</v>
       </c>
       <c r="AP16">
-        <v>205.23676632621752</v>
+        <v>142.13032855634668</v>
       </c>
       <c r="AR16" t="s">
         <v>562</v>
@@ -11177,13 +11177,13 @@
         <v>1310</v>
       </c>
       <c r="BB16" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="BC16">
-        <v>0.97671054233736465</v>
+        <v>0.97776667041974696</v>
       </c>
       <c r="BD16">
-        <v>665.39855790710828</v>
+        <v>657.0727481909945</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -11287,13 +11287,13 @@
         <v>1130</v>
       </c>
       <c r="AN17" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="AO17">
-        <v>0.98562926828922137</v>
+        <v>0.96642968891663028</v>
       </c>
       <c r="AP17">
-        <v>263.46341469760875</v>
+        <v>615.45570319511182</v>
       </c>
       <c r="AR17" t="s">
         <v>562</v>
@@ -11323,13 +11323,13 @@
         <v>1311</v>
       </c>
       <c r="BB17" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="BC17">
-        <v>0.97543237988175824</v>
+        <v>0.98620687652221406</v>
       </c>
       <c r="BD17">
-        <v>675.47473859880586</v>
+        <v>590.53579008321287</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11433,13 +11433,13 @@
         <v>1131</v>
       </c>
       <c r="AN18" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="AO18">
-        <v>0.98557285435300757</v>
+        <v>0.97580462137033996</v>
       </c>
       <c r="AP18">
-        <v>264.4976701948608</v>
+        <v>443.58194154376798</v>
       </c>
       <c r="AR18" t="s">
         <v>562</v>
@@ -11469,13 +11469,13 @@
         <v>1312</v>
       </c>
       <c r="BB18" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="BC18">
-        <v>0.9808842004636289</v>
+        <v>0.97563785990108609</v>
       </c>
       <c r="BD18">
-        <v>632.49621967839255</v>
+        <v>673.85487111310465</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11579,13 +11579,13 @@
         <v>1132</v>
       </c>
       <c r="AN19" t="s">
-        <v>873</v>
+        <v>849</v>
       </c>
       <c r="AO19">
-        <v>0.99063307902321618</v>
+        <v>0.98941824689872981</v>
       </c>
       <c r="AP19">
-        <v>171.72688457437104</v>
+        <v>193.99880685662112</v>
       </c>
       <c r="AR19" t="s">
         <v>562</v>
@@ -11615,13 +11615,13 @@
         <v>1313</v>
       </c>
       <c r="BB19" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="BC19">
-        <v>0.97529697423998973</v>
+        <v>0.97060428364656626</v>
       </c>
       <c r="BD19">
-        <v>676.54218640808119</v>
+        <v>713.53623058623612</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11686,16 +11686,16 @@
         <v>583</v>
       </c>
       <c r="Y20" t="s">
-        <v>502</v>
+        <v>429</v>
       </c>
       <c r="Z20" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="AA20">
-        <v>0.99142410630444711</v>
+        <v>0.99232963975206445</v>
       </c>
       <c r="AB20">
-        <v>157.22471775180347</v>
+        <v>140.62327121215228</v>
       </c>
       <c r="AD20" t="s">
         <v>562</v>
@@ -11725,13 +11725,13 @@
         <v>1133</v>
       </c>
       <c r="AN20" t="s">
-        <v>839</v>
+        <v>878</v>
       </c>
       <c r="AO20">
-        <v>0.99304329114881718</v>
+        <v>0.9911899510437201</v>
       </c>
       <c r="AP20">
-        <v>127.53966227168546</v>
+        <v>161.51756419846544</v>
       </c>
       <c r="AR20" t="s">
         <v>562</v>
@@ -11761,13 +11761,13 @@
         <v>1314</v>
       </c>
       <c r="BB20" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="BC20">
-        <v>0.97190684035904551</v>
+        <v>0.98574293134283075</v>
       </c>
       <c r="BD20">
-        <v>703.26774183619148</v>
+        <v>594.19322458068439</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11832,16 +11832,16 @@
         <v>585</v>
       </c>
       <c r="Y21" t="s">
-        <v>523</v>
+        <v>443</v>
       </c>
       <c r="Z21" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AA21">
-        <v>0.99218904910018979</v>
+        <v>0.98863637284234351</v>
       </c>
       <c r="AB21">
-        <v>143.20076649652023</v>
+        <v>208.33316455703533</v>
       </c>
       <c r="AD21" t="s">
         <v>562</v>
@@ -11871,13 +11871,13 @@
         <v>1134</v>
       </c>
       <c r="AN21" t="s">
-        <v>839</v>
+        <v>865</v>
       </c>
       <c r="AO21">
-        <v>0.99264385543323097</v>
+        <v>0.97139194185607003</v>
       </c>
       <c r="AP21">
-        <v>134.8626503907652</v>
+        <v>524.48106597204946</v>
       </c>
       <c r="AR21" t="s">
         <v>562</v>
@@ -11907,13 +11907,13 @@
         <v>1315</v>
       </c>
       <c r="BB21" t="s">
-        <v>879</v>
+        <v>850</v>
       </c>
       <c r="BC21">
-        <v>0.99063171688389717</v>
+        <v>0.98120414321706895</v>
       </c>
       <c r="BD21">
-        <v>548.62415996795482</v>
+        <v>629.97400430543962</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11978,16 +11978,16 @@
         <v>587</v>
       </c>
       <c r="Y22" t="s">
-        <v>527</v>
+        <v>454</v>
       </c>
       <c r="Z22" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AA22">
-        <v>0.97564251840922733</v>
+        <v>0.99016939403137849</v>
       </c>
       <c r="AB22">
-        <v>446.55382916416522</v>
+        <v>180.22777609139402</v>
       </c>
       <c r="AD22" t="s">
         <v>562</v>
@@ -12017,13 +12017,13 @@
         <v>1135</v>
       </c>
       <c r="AN22" t="s">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="AO22">
-        <v>0.98530274641518678</v>
+        <v>0.98117052771194446</v>
       </c>
       <c r="AP22">
-        <v>269.44964905490986</v>
+        <v>345.20699194768525</v>
       </c>
       <c r="AR22" t="s">
         <v>562</v>
@@ -12053,13 +12053,13 @@
         <v>1316</v>
       </c>
       <c r="BB22" t="s">
-        <v>851</v>
+        <v>887</v>
       </c>
       <c r="BC22">
-        <v>0.9783099865431607</v>
+        <v>0.98556171669906312</v>
       </c>
       <c r="BD22">
-        <v>652.78960608475018</v>
+        <v>595.62180002238608</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -12124,16 +12124,16 @@
         <v>589</v>
       </c>
       <c r="Y23" t="s">
-        <v>534</v>
+        <v>461</v>
       </c>
       <c r="Z23" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AA23">
-        <v>0.9954097472817981</v>
+        <v>0.9849937388690081</v>
       </c>
       <c r="AB23">
-        <v>84.154633167035314</v>
+        <v>275.11478740151779</v>
       </c>
       <c r="AD23" t="s">
         <v>562</v>
@@ -12163,13 +12163,13 @@
         <v>1136</v>
       </c>
       <c r="AN23" t="s">
-        <v>884</v>
+        <v>865</v>
       </c>
       <c r="AO23">
-        <v>0.98558146952732006</v>
+        <v>0.98127559165304223</v>
       </c>
       <c r="AP23">
-        <v>264.33972533246634</v>
+        <v>343.28081969422635</v>
       </c>
       <c r="AR23" t="s">
         <v>562</v>
@@ -12199,13 +12199,13 @@
         <v>1317</v>
       </c>
       <c r="BB23" t="s">
-        <v>886</v>
+        <v>839</v>
       </c>
       <c r="BC23">
-        <v>0.91905535977869501</v>
+        <v>0.99041503856315227</v>
       </c>
       <c r="BD23">
-        <v>1119.9135804112877</v>
+        <v>557.36144599381669</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -12270,16 +12270,16 @@
         <v>591</v>
       </c>
       <c r="Y24" t="s">
-        <v>538</v>
+        <v>465</v>
       </c>
       <c r="Z24" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="AA24">
-        <v>0.98928836714403978</v>
+        <v>0.96879824550148963</v>
       </c>
       <c r="AB24">
-        <v>196.37993569260354</v>
+        <v>572.03216580602339</v>
       </c>
       <c r="AD24" t="s">
         <v>562</v>
@@ -12309,13 +12309,13 @@
         <v>1137</v>
       </c>
       <c r="AN24" t="s">
-        <v>843</v>
+        <v>853</v>
       </c>
       <c r="AO24">
-        <v>0.98563706266808038</v>
+        <v>0.98086141539930738</v>
       </c>
       <c r="AP24">
-        <v>263.32051775185897</v>
+        <v>350.87405101269854</v>
       </c>
       <c r="AR24" t="s">
         <v>562</v>
@@ -12345,13 +12345,13 @@
         <v>1318</v>
       </c>
       <c r="BB24" t="s">
-        <v>886</v>
+        <v>839</v>
       </c>
       <c r="BC24">
-        <v>0.90777469227524876</v>
+        <v>0.98222546540109945</v>
       </c>
       <c r="BD24">
-        <v>1208.8428425634561</v>
+        <v>621.92258108799922</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12416,16 +12416,16 @@
         <v>593</v>
       </c>
       <c r="Y25" t="s">
-        <v>425</v>
+        <v>497</v>
       </c>
       <c r="Z25" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="AA25">
-        <v>0.99579045202592908</v>
+        <v>0.99058937597842778</v>
       </c>
       <c r="AB25">
-        <v>77.175046191301078</v>
+        <v>172.52810706215647</v>
       </c>
       <c r="AD25" t="s">
         <v>562</v>
@@ -12455,13 +12455,13 @@
         <v>1138</v>
       </c>
       <c r="AN25" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
       <c r="AO25">
-        <v>0.9859891893004602</v>
+        <v>0.98555037049604</v>
       </c>
       <c r="AP25">
-        <v>256.8648628248954</v>
+        <v>264.90987423926674</v>
       </c>
       <c r="AR25" t="s">
         <v>562</v>
@@ -12491,13 +12491,13 @@
         <v>1319</v>
       </c>
       <c r="BB25" t="s">
-        <v>890</v>
+        <v>862</v>
       </c>
       <c r="BC25">
-        <v>0.98758818560479655</v>
+        <v>0.90514503736235263</v>
       </c>
       <c r="BD25">
-        <v>579.64647014885406</v>
+        <v>1229.5732887934535</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12562,16 +12562,16 @@
         <v>595</v>
       </c>
       <c r="Y26" t="s">
-        <v>437</v>
+        <v>517</v>
       </c>
       <c r="Z26" t="s">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="AA26">
-        <v>0.95765547041534393</v>
+        <v>0.98884641033160892</v>
       </c>
       <c r="AB26">
-        <v>776.31637571869453</v>
+        <v>204.48247725383573</v>
       </c>
       <c r="AD26" t="s">
         <v>562</v>
@@ -12601,13 +12601,13 @@
         <v>1139</v>
       </c>
       <c r="AN26" t="s">
-        <v>870</v>
+        <v>855</v>
       </c>
       <c r="AO26">
-        <v>0.98980378364600918</v>
+        <v>0.98040327309339681</v>
       </c>
       <c r="AP26">
-        <v>186.93063315649889</v>
+        <v>359.27332662105931</v>
       </c>
       <c r="AR26" t="s">
         <v>562</v>
@@ -12637,13 +12637,13 @@
         <v>1320</v>
       </c>
       <c r="BB26" t="s">
-        <v>849</v>
+        <v>878</v>
       </c>
       <c r="BC26">
-        <v>0.97985329377358876</v>
+        <v>0.99613925038938234</v>
       </c>
       <c r="BD26">
-        <v>640.6232007515423</v>
+        <v>322.44811734269933</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12708,16 +12708,16 @@
         <v>597</v>
       </c>
       <c r="Y27" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
       <c r="Z27" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AA27">
-        <v>0.98394190948405269</v>
+        <v>0.98971858307134875</v>
       </c>
       <c r="AB27">
-        <v>294.3983261257012</v>
+        <v>188.49264369194051</v>
       </c>
       <c r="AD27" t="s">
         <v>562</v>
@@ -12747,13 +12747,13 @@
         <v>1140</v>
       </c>
       <c r="AN27" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="AO27">
-        <v>0.99069539601336043</v>
+        <v>0.99177071872011402</v>
       </c>
       <c r="AP27">
-        <v>170.5844064217261</v>
+        <v>150.87015679790983</v>
       </c>
       <c r="AR27" t="s">
         <v>562</v>
@@ -12783,13 +12783,13 @@
         <v>1321</v>
       </c>
       <c r="BB27" t="s">
-        <v>851</v>
+        <v>887</v>
       </c>
       <c r="BC27">
-        <v>0.98556171669906312</v>
+        <v>0.97775230782134392</v>
       </c>
       <c r="BD27">
-        <v>595.62180002238608</v>
+        <v>657.18597334173887</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12854,16 +12854,16 @@
         <v>599</v>
       </c>
       <c r="Y28" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="Z28" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="AA28">
-        <v>0.97498879609676647</v>
+        <v>0.98974367616617376</v>
       </c>
       <c r="AB28">
-        <v>458.53873822594755</v>
+        <v>188.03260362014854</v>
       </c>
       <c r="AD28" t="s">
         <v>562</v>
@@ -12893,13 +12893,13 @@
         <v>1141</v>
       </c>
       <c r="AN28" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="AO28">
-        <v>0.98658832734700097</v>
+        <v>0.9871975802659102</v>
       </c>
       <c r="AP28">
-        <v>245.88066530498185</v>
+        <v>234.7110284583128</v>
       </c>
       <c r="AR28" t="s">
         <v>562</v>
@@ -12929,13 +12929,13 @@
         <v>1322</v>
       </c>
       <c r="BB28" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="BC28">
-        <v>0.99041503856315227</v>
+        <v>0.97884476097844741</v>
       </c>
       <c r="BD28">
-        <v>557.36144599381669</v>
+        <v>648.57380095323958</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -13000,16 +13000,16 @@
         <v>601</v>
       </c>
       <c r="Y29" t="s">
-        <v>533</v>
+        <v>446</v>
       </c>
       <c r="Z29" t="s">
         <v>853</v>
       </c>
       <c r="AA29">
-        <v>0.9903652333518761</v>
+        <v>0.98950135873743683</v>
       </c>
       <c r="AB29">
-        <v>176.63738854893887</v>
+        <v>192.47508981365891</v>
       </c>
       <c r="AD29" t="s">
         <v>562</v>
@@ -13039,13 +13039,13 @@
         <v>1142</v>
       </c>
       <c r="AN29" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AO29">
-        <v>0.97263268500799516</v>
+        <v>0.99140701799255504</v>
       </c>
       <c r="AP29">
-        <v>501.73410818675478</v>
+        <v>157.53800346982385</v>
       </c>
       <c r="AR29" t="s">
         <v>562</v>
@@ -13075,13 +13075,13 @@
         <v>1323</v>
       </c>
       <c r="BB29" t="s">
-        <v>839</v>
+        <v>856</v>
       </c>
       <c r="BC29">
-        <v>0.98222546540109945</v>
+        <v>0.96340904814790773</v>
       </c>
       <c r="BD29">
-        <v>621.92258108799922</v>
+        <v>770.2586704339941</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -13146,16 +13146,16 @@
         <v>603</v>
       </c>
       <c r="Y30" t="s">
-        <v>539</v>
+        <v>450</v>
       </c>
       <c r="Z30" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="AA30">
-        <v>0.98359157932992225</v>
+        <v>0.99488206120957279</v>
       </c>
       <c r="AB30">
-        <v>300.82104561809257</v>
+        <v>93.828877824498619</v>
       </c>
       <c r="AD30" t="s">
         <v>562</v>
@@ -13185,13 +13185,13 @@
         <v>1143</v>
       </c>
       <c r="AN30" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AO30">
-        <v>0.99099526421280915</v>
+        <v>0.98565286420409937</v>
       </c>
       <c r="AP30">
-        <v>165.08682276516558</v>
+        <v>263.03082292484481</v>
       </c>
       <c r="AR30" t="s">
         <v>562</v>
@@ -13221,13 +13221,13 @@
         <v>1324</v>
       </c>
       <c r="BB30" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
       <c r="BC30">
-        <v>0.90514503736235263</v>
+        <v>0.97671054233736465</v>
       </c>
       <c r="BD30">
-        <v>1229.5732887934535</v>
+        <v>665.39855790710828</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -13292,16 +13292,16 @@
         <v>605</v>
       </c>
       <c r="Y31" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Z31" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="AA31">
-        <v>0.98602445832668828</v>
+        <v>0.98929007854358664</v>
       </c>
       <c r="AB31">
-        <v>256.2182640107153</v>
+        <v>196.34856003424409</v>
       </c>
       <c r="AD31" t="s">
         <v>562</v>
@@ -13331,13 +13331,13 @@
         <v>1144</v>
       </c>
       <c r="AN31" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="AO31">
-        <v>0.99072339258685749</v>
+        <v>0.98600984216520959</v>
       </c>
       <c r="AP31">
-        <v>170.07113590761304</v>
+        <v>256.48622697115769</v>
       </c>
       <c r="AR31" t="s">
         <v>562</v>
@@ -13367,13 +13367,13 @@
         <v>1325</v>
       </c>
       <c r="BB31" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="BC31">
-        <v>0.99613925038938234</v>
+        <v>0.98758818560479655</v>
       </c>
       <c r="BD31">
-        <v>322.44811734269933</v>
+        <v>579.64647014885406</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13438,16 +13438,16 @@
         <v>607</v>
       </c>
       <c r="Y32" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="Z32" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="AA32">
-        <v>0.98274955259938535</v>
+        <v>0.9692587148013998</v>
       </c>
       <c r="AB32">
-        <v>316.25820234460127</v>
+        <v>563.59022864100291</v>
       </c>
       <c r="AD32" t="s">
         <v>562</v>
@@ -13477,13 +13477,13 @@
         <v>1145</v>
       </c>
       <c r="AN32" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="AO32">
-        <v>0.98702528039583703</v>
+        <v>0.9913968450205024</v>
       </c>
       <c r="AP32">
-        <v>237.86985940965451</v>
+        <v>157.72450795745584</v>
       </c>
       <c r="AR32" t="s">
         <v>562</v>
@@ -13513,13 +13513,13 @@
         <v>1326</v>
       </c>
       <c r="BB32" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="BC32">
-        <v>0.96340904814790773</v>
+        <v>0.97985329377358876</v>
       </c>
       <c r="BD32">
-        <v>770.2586704339941</v>
+        <v>640.6232007515423</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13584,16 +13584,16 @@
         <v>609</v>
       </c>
       <c r="Y33" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="Z33" t="s">
         <v>855</v>
       </c>
       <c r="AA33">
-        <v>0.99368873088044474</v>
+        <v>0.99120757651401414</v>
       </c>
       <c r="AB33">
-        <v>115.70660052517967</v>
+        <v>161.19443057640677</v>
       </c>
       <c r="AD33" t="s">
         <v>562</v>
@@ -13623,13 +13623,13 @@
         <v>1146</v>
       </c>
       <c r="AN33" t="s">
-        <v>861</v>
+        <v>893</v>
       </c>
       <c r="AO33">
-        <v>0.99511776358677106</v>
+        <v>0.98662924242305594</v>
       </c>
       <c r="AP33">
-        <v>89.507667575863124</v>
+        <v>245.13055557730874</v>
       </c>
       <c r="AR33" t="s">
         <v>562</v>
@@ -13659,13 +13659,13 @@
         <v>1327</v>
       </c>
       <c r="BB33" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="BC33">
-        <v>0.97748676055693473</v>
+        <v>0.98029614417839783</v>
       </c>
       <c r="BD33">
-        <v>659.27937094283163</v>
+        <v>637.13206339363023</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13730,16 +13730,16 @@
         <v>611</v>
       </c>
       <c r="Y34" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="Z34" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AA34">
-        <v>0.99323001255738197</v>
+        <v>0.98661661227366804</v>
       </c>
       <c r="AB34">
-        <v>124.11643644799697</v>
+        <v>245.36210831608693</v>
       </c>
       <c r="AD34" t="s">
         <v>562</v>
@@ -13769,13 +13769,13 @@
         <v>1147</v>
       </c>
       <c r="AN34" t="s">
-        <v>862</v>
+        <v>844</v>
       </c>
       <c r="AO34">
-        <v>0.99298280898033964</v>
+        <v>0.99375979852043306</v>
       </c>
       <c r="AP34">
-        <v>128.64850202710696</v>
+        <v>114.40369379206156</v>
       </c>
       <c r="AR34" t="s">
         <v>562</v>
@@ -13805,13 +13805,13 @@
         <v>1328</v>
       </c>
       <c r="BB34" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="BC34">
-        <v>0.98661815843628831</v>
+        <v>0.98865855459335616</v>
       </c>
       <c r="BD34">
-        <v>587.29351766059415</v>
+        <v>571.20839462237564</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13876,16 +13876,16 @@
         <v>613</v>
       </c>
       <c r="Y35" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="Z35" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AA35">
-        <v>0.99148244782956252</v>
+        <v>0.98939469221283771</v>
       </c>
       <c r="AB35">
-        <v>156.15512312468667</v>
+        <v>194.43064276464273</v>
       </c>
       <c r="AD35" t="s">
         <v>562</v>
@@ -13915,13 +13915,13 @@
         <v>1148</v>
       </c>
       <c r="AN35" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="AO35">
-        <v>0.99562564597459979</v>
+        <v>0.9935955776192904</v>
       </c>
       <c r="AP35">
-        <v>80.196490465669797</v>
+        <v>117.41441031301009</v>
       </c>
       <c r="AR35" t="s">
         <v>562</v>
@@ -13951,13 +13951,13 @@
         <v>1329</v>
       </c>
       <c r="BB35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="BC35">
-        <v>0.99038640993878491</v>
+        <v>0.9808842004636289</v>
       </c>
       <c r="BD35">
-        <v>557.58713498257862</v>
+        <v>632.49621967839255</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -14022,16 +14022,16 @@
         <v>615</v>
       </c>
       <c r="Y36" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="Z36" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="AA36">
-        <v>0.96906520826310416</v>
+        <v>0.99170776895032964</v>
       </c>
       <c r="AB36">
-        <v>567.13784850975708</v>
+        <v>152.02423591062336</v>
       </c>
       <c r="AD36" t="s">
         <v>562</v>
@@ -14061,13 +14061,13 @@
         <v>1149</v>
       </c>
       <c r="AN36" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="AO36">
-        <v>0.9864929875546109</v>
+        <v>0.9895134548380341</v>
       </c>
       <c r="AP36">
-        <v>247.62856149880113</v>
+        <v>192.25332796937471</v>
       </c>
       <c r="AR36" t="s">
         <v>562</v>
@@ -14097,13 +14097,13 @@
         <v>1330</v>
       </c>
       <c r="BB36" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="BC36">
-        <v>0.97776667041974696</v>
+        <v>0.97529697423998973</v>
       </c>
       <c r="BD36">
-        <v>657.0727481909945</v>
+        <v>676.54218640808119</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -14168,16 +14168,16 @@
         <v>617</v>
       </c>
       <c r="Y37" t="s">
-        <v>436</v>
+        <v>546</v>
       </c>
       <c r="Z37" t="s">
-        <v>840</v>
+        <v>859</v>
       </c>
       <c r="AA37">
-        <v>0.98213469589758429</v>
+        <v>0.99042342806455907</v>
       </c>
       <c r="AB37">
-        <v>327.53057521095576</v>
+        <v>175.57048548308435</v>
       </c>
       <c r="AD37" t="s">
         <v>562</v>
@@ -14207,13 +14207,13 @@
         <v>1150</v>
       </c>
       <c r="AN37" t="s">
-        <v>842</v>
+        <v>874</v>
       </c>
       <c r="AO37">
-        <v>0.99214368255188645</v>
+        <v>0.98960179851646224</v>
       </c>
       <c r="AP37">
-        <v>144.03248654874827</v>
+        <v>190.63369386485829</v>
       </c>
       <c r="AR37" t="s">
         <v>562</v>
@@ -14243,13 +14243,13 @@
         <v>1331</v>
       </c>
       <c r="BB37" t="s">
-        <v>886</v>
+        <v>851</v>
       </c>
       <c r="BC37">
-        <v>0.98620687652221406</v>
+        <v>0.97190684035904551</v>
       </c>
       <c r="BD37">
-        <v>590.53579008321287</v>
+        <v>703.26774183619148</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14314,16 +14314,16 @@
         <v>619</v>
       </c>
       <c r="Y38" t="s">
-        <v>439</v>
+        <v>557</v>
       </c>
       <c r="Z38" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="AA38">
-        <v>0.98161750782838286</v>
+        <v>0.99253864063271646</v>
       </c>
       <c r="AB38">
-        <v>337.01235647964734</v>
+        <v>136.79158840019849</v>
       </c>
       <c r="AD38" t="s">
         <v>562</v>
@@ -14353,13 +14353,13 @@
         <v>1151</v>
       </c>
       <c r="AN38" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="AO38">
-        <v>0.9928290104176094</v>
+        <v>0.99430130634228164</v>
       </c>
       <c r="AP38">
-        <v>131.46814234382811</v>
+        <v>104.47605039150224</v>
       </c>
       <c r="AR38" t="s">
         <v>562</v>
@@ -14389,13 +14389,13 @@
         <v>1332</v>
       </c>
       <c r="BB38" t="s">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="BC38">
-        <v>0.97563785990108609</v>
+        <v>0.99063171688389717</v>
       </c>
       <c r="BD38">
-        <v>673.85487111310465</v>
+        <v>548.62415996795482</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14460,16 +14460,16 @@
         <v>621</v>
       </c>
       <c r="Y39" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="Z39" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="AA39">
-        <v>0.98975592846808447</v>
+        <v>0.99495645179599901</v>
       </c>
       <c r="AB39">
-        <v>187.80797808511727</v>
+        <v>92.465050406684512</v>
       </c>
       <c r="AD39" t="s">
         <v>562</v>
@@ -14499,13 +14499,13 @@
         <v>1152</v>
       </c>
       <c r="AN39" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="AO39">
-        <v>0.97791499844986385</v>
+        <v>0.99215445883125275</v>
       </c>
       <c r="AP39">
-        <v>404.89169508582842</v>
+        <v>143.83492142703278</v>
       </c>
       <c r="AR39" t="s">
         <v>562</v>
@@ -14535,13 +14535,13 @@
         <v>1333</v>
       </c>
       <c r="BB39" t="s">
-        <v>869</v>
+        <v>851</v>
       </c>
       <c r="BC39">
-        <v>0.97060428364656626</v>
+        <v>0.97543237988175824</v>
       </c>
       <c r="BD39">
-        <v>713.53623058623612</v>
+        <v>675.47473859880586</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14606,16 +14606,16 @@
         <v>623</v>
       </c>
       <c r="Y40" t="s">
-        <v>480</v>
+        <v>451</v>
       </c>
       <c r="Z40" t="s">
-        <v>843</v>
+        <v>861</v>
       </c>
       <c r="AA40">
-        <v>0.97312873356481211</v>
+        <v>0.99335434882803453</v>
       </c>
       <c r="AB40">
-        <v>492.63988464511067</v>
+        <v>121.83693815269984</v>
       </c>
       <c r="AD40" t="s">
         <v>562</v>
@@ -14645,13 +14645,13 @@
         <v>1153</v>
       </c>
       <c r="AN40" t="s">
-        <v>871</v>
+        <v>849</v>
       </c>
       <c r="AO40">
-        <v>0.977944947494224</v>
+        <v>0.97814391961975855</v>
       </c>
       <c r="AP40">
-        <v>404.34262927256032</v>
+        <v>400.69480697109378</v>
       </c>
       <c r="AR40" t="s">
         <v>562</v>
@@ -14681,13 +14681,13 @@
         <v>1334</v>
       </c>
       <c r="BB40" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="BC40">
-        <v>0.98574293134283075</v>
+        <v>0.9783099865431607</v>
       </c>
       <c r="BD40">
-        <v>594.19322458068439</v>
+        <v>652.78960608475018</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14752,16 +14752,16 @@
         <v>625</v>
       </c>
       <c r="Y41" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="Z41" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="AA41">
-        <v>0.98977266598403368</v>
+        <v>0.97858303227439647</v>
       </c>
       <c r="AB41">
-        <v>187.50112362604992</v>
+        <v>392.64440830273202</v>
       </c>
       <c r="AD41" t="s">
         <v>562</v>
@@ -14791,13 +14791,13 @@
         <v>1154</v>
       </c>
       <c r="AN41" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="AO41">
-        <v>0.99502057695725243</v>
+        <v>0.99224639661619274</v>
       </c>
       <c r="AP41">
-        <v>91.289422450372911</v>
+        <v>142.14939536980046</v>
       </c>
       <c r="AR41" t="s">
         <v>562</v>
@@ -14827,13 +14827,13 @@
         <v>1335</v>
       </c>
       <c r="BB41" t="s">
-        <v>872</v>
+        <v>856</v>
       </c>
       <c r="BC41">
-        <v>0.98120414321706895</v>
+        <v>0.91905535977869501</v>
       </c>
       <c r="BD41">
-        <v>629.97400430543962</v>
+        <v>1119.9135804112877</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14898,16 +14898,16 @@
         <v>627</v>
       </c>
       <c r="Y42" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="Z42" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="AA42">
-        <v>0.99537444599393454</v>
+        <v>0.99121272120977255</v>
       </c>
       <c r="AB42">
-        <v>84.801823444534008</v>
+        <v>161.10011115417001</v>
       </c>
       <c r="AD42" t="s">
         <v>562</v>
@@ -14937,13 +14937,13 @@
         <v>1155</v>
       </c>
       <c r="AN42" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="AO42">
-        <v>0.9742069477253853</v>
+        <v>0.98477063994548064</v>
       </c>
       <c r="AP42">
-        <v>472.87262503460209</v>
+        <v>279.20493433285503</v>
       </c>
       <c r="AR42" t="s">
         <v>562</v>
@@ -15044,16 +15044,16 @@
         <v>629</v>
       </c>
       <c r="Y43" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="Z43" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="AA43">
-        <v>0.99218262773253396</v>
+        <v>0.98955141276769387</v>
       </c>
       <c r="AB43">
-        <v>143.31849157021014</v>
+        <v>191.55743259227802</v>
       </c>
       <c r="AD43" t="s">
         <v>562</v>
@@ -15083,13 +15083,13 @@
         <v>1156</v>
       </c>
       <c r="AN43" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="AO43">
-        <v>0.99090442938878043</v>
+        <v>0.98880526729129725</v>
       </c>
       <c r="AP43">
-        <v>166.75212787235887</v>
+        <v>205.23676632621752</v>
       </c>
       <c r="AR43" t="s">
         <v>562</v>
@@ -15119,7 +15119,7 @@
         <v>1337</v>
       </c>
       <c r="BB43" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="BC43">
         <v>0.97987853234085787</v>
@@ -15190,16 +15190,16 @@
         <v>631</v>
       </c>
       <c r="Y44" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="Z44" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="AA44">
-        <v>0.99477407524212647</v>
+        <v>0.97668119298957756</v>
       </c>
       <c r="AB44">
-        <v>95.808620561014351</v>
+        <v>427.51146185774559</v>
       </c>
       <c r="AD44" t="s">
         <v>562</v>
@@ -15229,13 +15229,13 @@
         <v>1157</v>
       </c>
       <c r="AN44" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="AO44">
-        <v>0.99222882711684135</v>
+        <v>0.98562926828922137</v>
       </c>
       <c r="AP44">
-        <v>142.4715028579086</v>
+        <v>263.46341469760875</v>
       </c>
       <c r="AR44" t="s">
         <v>562</v>
@@ -15265,7 +15265,7 @@
         <v>1338</v>
       </c>
       <c r="BB44" t="s">
-        <v>872</v>
+        <v>850</v>
       </c>
       <c r="BC44">
         <v>0.97542834759532293</v>
@@ -15336,16 +15336,16 @@
         <v>633</v>
       </c>
       <c r="Y45" t="s">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="Z45" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="AA45">
-        <v>0.99340406403388481</v>
+        <v>0.98845897140196071</v>
       </c>
       <c r="AB45">
-        <v>120.92549271211209</v>
+        <v>211.58552429738629</v>
       </c>
       <c r="AD45" t="s">
         <v>562</v>
@@ -15375,13 +15375,13 @@
         <v>1158</v>
       </c>
       <c r="AN45" t="s">
-        <v>863</v>
+        <v>845</v>
       </c>
       <c r="AO45">
-        <v>0.99423394997920433</v>
+        <v>0.98557285435300757</v>
       </c>
       <c r="AP45">
-        <v>105.71091704792103</v>
+        <v>264.4976701948608</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15446,16 +15446,16 @@
         <v>635</v>
       </c>
       <c r="Y46" t="s">
-        <v>431</v>
+        <v>528</v>
       </c>
       <c r="Z46" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="AA46">
-        <v>0.99217497048797409</v>
+        <v>0.98629851964686077</v>
       </c>
       <c r="AB46">
-        <v>143.45887438714203</v>
+        <v>251.19380647421841</v>
       </c>
       <c r="AD46" t="s">
         <v>562</v>
@@ -15485,13 +15485,13 @@
         <v>1159</v>
       </c>
       <c r="AN46" t="s">
-        <v>894</v>
+        <v>866</v>
       </c>
       <c r="AO46">
-        <v>0.99467731181029251</v>
+        <v>0.99063307902321618</v>
       </c>
       <c r="AP46">
-        <v>97.582616811304106</v>
+        <v>171.72688457437104</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15556,16 +15556,16 @@
         <v>637</v>
       </c>
       <c r="Y47" t="s">
-        <v>441</v>
+        <v>552</v>
       </c>
       <c r="Z47" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AA47">
-        <v>0.99688734285602987</v>
+        <v>0.98289372536542474</v>
       </c>
       <c r="AB47">
-        <v>57.065380972786443</v>
+        <v>313.61503496721377</v>
       </c>
       <c r="AD47" t="s">
         <v>562</v>
@@ -15595,13 +15595,13 @@
         <v>1160</v>
       </c>
       <c r="AN47" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="AO47">
-        <v>0.97803634076421897</v>
+        <v>0.99317814360692358</v>
       </c>
       <c r="AP47">
-        <v>402.6670859893182</v>
+        <v>125.06736720640154</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15666,16 +15666,16 @@
         <v>639</v>
       </c>
       <c r="Y48" t="s">
-        <v>444</v>
+        <v>558</v>
       </c>
       <c r="Z48" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="AA48">
-        <v>0.99243001465918479</v>
+        <v>0.99506342503584544</v>
       </c>
       <c r="AB48">
-        <v>138.78306458161211</v>
+        <v>90.503874342833086</v>
       </c>
       <c r="AD48" t="s">
         <v>562</v>
@@ -15705,13 +15705,13 @@
         <v>1161</v>
       </c>
       <c r="AN48" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="AO48">
-        <v>0.99267357107797494</v>
+        <v>0.99086943207021283</v>
       </c>
       <c r="AP48">
-        <v>134.31786357045974</v>
+        <v>167.3937453794307</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15776,16 +15776,16 @@
         <v>641</v>
       </c>
       <c r="Y49" t="s">
-        <v>484</v>
+        <v>427</v>
       </c>
       <c r="Z49" t="s">
-        <v>843</v>
+        <v>868</v>
       </c>
       <c r="AA49">
-        <v>0.96964927506180898</v>
+        <v>0.9941804823678142</v>
       </c>
       <c r="AB49">
-        <v>556.42995720016825</v>
+        <v>106.6911565900724</v>
       </c>
       <c r="AD49" t="s">
         <v>562</v>
@@ -15815,13 +15815,13 @@
         <v>1162</v>
       </c>
       <c r="AN49" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="AO49">
-        <v>0.98837316480290893</v>
+        <v>0.99302300928376919</v>
       </c>
       <c r="AP49">
-        <v>213.15864528000296</v>
+        <v>127.91149646423172</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15886,16 +15886,16 @@
         <v>643</v>
       </c>
       <c r="Y50" t="s">
-        <v>495</v>
+        <v>433</v>
       </c>
       <c r="Z50" t="s">
-        <v>852</v>
+        <v>869</v>
       </c>
       <c r="AA50">
-        <v>0.9741863781992316</v>
+        <v>0.99511659056551938</v>
       </c>
       <c r="AB50">
-        <v>473.24973301408767</v>
+        <v>89.52917296547848</v>
       </c>
       <c r="AD50" t="s">
         <v>562</v>
@@ -15925,13 +15925,13 @@
         <v>1163</v>
       </c>
       <c r="AN50" t="s">
-        <v>885</v>
+        <v>841</v>
       </c>
       <c r="AO50">
-        <v>0.9924503916821712</v>
+        <v>0.99011319269869458</v>
       </c>
       <c r="AP50">
-        <v>138.40948582686161</v>
+        <v>181.25813385726678</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15996,16 +15996,16 @@
         <v>645</v>
       </c>
       <c r="Y51" t="s">
-        <v>545</v>
+        <v>438</v>
       </c>
       <c r="Z51" t="s">
-        <v>866</v>
+        <v>840</v>
       </c>
       <c r="AA51">
-        <v>0.99407588262977375</v>
+        <v>0.96952136011150125</v>
       </c>
       <c r="AB51">
-        <v>108.60881845414757</v>
+        <v>558.77506462247754</v>
       </c>
       <c r="AD51" t="s">
         <v>562</v>
@@ -16035,13 +16035,13 @@
         <v>1164</v>
       </c>
       <c r="AN51" t="s">
-        <v>864</v>
+        <v>842</v>
       </c>
       <c r="AO51">
-        <v>0.99702387631899381</v>
+        <v>0.99448552674849922</v>
       </c>
       <c r="AP51">
-        <v>54.562267485114141</v>
+        <v>101.09867627751461</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -16106,16 +16106,16 @@
         <v>647</v>
       </c>
       <c r="Y52" t="s">
-        <v>547</v>
+        <v>478</v>
       </c>
       <c r="Z52" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="AA52">
-        <v>0.97256549686216975</v>
+        <v>0.98977876009625232</v>
       </c>
       <c r="AB52">
-        <v>502.96589086022118</v>
+        <v>187.38939823537481</v>
       </c>
       <c r="AD52" t="s">
         <v>562</v>
@@ -16145,13 +16145,13 @@
         <v>1165</v>
       </c>
       <c r="AN52" t="s">
-        <v>865</v>
+        <v>843</v>
       </c>
       <c r="AO52">
-        <v>0.99193693152956208</v>
+        <v>0.98107014020732863</v>
       </c>
       <c r="AP52">
-        <v>147.8229219580285</v>
+        <v>347.04742953230885</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -16216,16 +16216,16 @@
         <v>649</v>
       </c>
       <c r="Y53" t="s">
-        <v>428</v>
+        <v>498</v>
       </c>
       <c r="Z53" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="AA53">
-        <v>0.99495645179599901</v>
+        <v>0.99133392870479353</v>
       </c>
       <c r="AB53">
-        <v>92.465050406684512</v>
+        <v>158.87797374545147</v>
       </c>
       <c r="AD53" t="s">
         <v>562</v>
@@ -16255,13 +16255,13 @@
         <v>1166</v>
       </c>
       <c r="AN53" t="s">
-        <v>852</v>
+        <v>882</v>
       </c>
       <c r="AO53">
-        <v>0.99063792186488431</v>
+        <v>0.99547447105677267</v>
       </c>
       <c r="AP53">
-        <v>171.63809914378689</v>
+        <v>82.96803062583389</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -16326,16 +16326,16 @@
         <v>651</v>
       </c>
       <c r="Y54" t="s">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="Z54" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="AA54">
-        <v>0.99335434882803453</v>
+        <v>0.9810875794416769</v>
       </c>
       <c r="AB54">
-        <v>121.83693815269984</v>
+        <v>346.72771023592401</v>
       </c>
       <c r="AD54" t="s">
         <v>562</v>
@@ -16365,13 +16365,13 @@
         <v>1167</v>
       </c>
       <c r="AN54" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="AO54">
-        <v>0.9898048456745685</v>
+        <v>0.98690358786307586</v>
       </c>
       <c r="AP54">
-        <v>186.91116263291045</v>
+        <v>240.10088917694185</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16436,16 +16436,16 @@
         <v>653</v>
       </c>
       <c r="Y55" t="s">
-        <v>471</v>
+        <v>514</v>
       </c>
       <c r="Z55" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
       <c r="AA55">
-        <v>0.97858303227439647</v>
+        <v>0.99206450778354704</v>
       </c>
       <c r="AB55">
-        <v>392.64440830273202</v>
+        <v>145.4840239683044</v>
       </c>
       <c r="AD55" t="s">
         <v>562</v>
@@ -16475,13 +16475,13 @@
         <v>1168</v>
       </c>
       <c r="AN55" t="s">
-        <v>840</v>
+        <v>875</v>
       </c>
       <c r="AO55">
-        <v>0.96363263183226566</v>
+        <v>0.9941444177652955</v>
       </c>
       <c r="AP55">
-        <v>666.73508307513055</v>
+        <v>107.35234096958277</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16546,16 +16546,16 @@
         <v>655</v>
       </c>
       <c r="Y56" t="s">
-        <v>490</v>
+        <v>525</v>
       </c>
       <c r="Z56" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="AA56">
-        <v>0.99121272120977255</v>
+        <v>0.98787020216528199</v>
       </c>
       <c r="AB56">
-        <v>161.10011115417001</v>
+        <v>222.37962696982947</v>
       </c>
       <c r="AD56" t="s">
         <v>562</v>
@@ -16585,13 +16585,13 @@
         <v>1169</v>
       </c>
       <c r="AN56" t="s">
-        <v>891</v>
+        <v>853</v>
       </c>
       <c r="AO56">
-        <v>0.99153439104508034</v>
+        <v>0.9733086107906429</v>
       </c>
       <c r="AP56">
-        <v>155.20283084019445</v>
+        <v>489.34213550487942</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16656,16 +16656,16 @@
         <v>657</v>
       </c>
       <c r="Y57" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="Z57" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="AA57">
-        <v>0.98955141276769387</v>
+        <v>0.98780336216423326</v>
       </c>
       <c r="AB57">
-        <v>191.55743259227802</v>
+        <v>223.60502698905651</v>
       </c>
       <c r="AD57" t="s">
         <v>562</v>
@@ -16695,13 +16695,13 @@
         <v>1170</v>
       </c>
       <c r="AN57" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="AO57">
-        <v>0.98940041671700285</v>
+        <v>0.9839431789633305</v>
       </c>
       <c r="AP57">
-        <v>194.32569352161357</v>
+        <v>294.37505233894177</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16766,16 +16766,16 @@
         <v>659</v>
       </c>
       <c r="Y58" t="s">
-        <v>516</v>
+        <v>559</v>
       </c>
       <c r="Z58" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="AA58">
-        <v>0.97668119298957756</v>
+        <v>0.9935358987764813</v>
       </c>
       <c r="AB58">
-        <v>427.51146185774559</v>
+        <v>118.50852243117704</v>
       </c>
       <c r="AD58" t="s">
         <v>562</v>
@@ -16805,13 +16805,13 @@
         <v>1171</v>
       </c>
       <c r="AN58" t="s">
-        <v>873</v>
+        <v>848</v>
       </c>
       <c r="AO58">
-        <v>0.98639521029542421</v>
+        <v>0.96950481457473103</v>
       </c>
       <c r="AP58">
-        <v>249.42114458389037</v>
+        <v>559.0783994632643</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16876,16 +16876,16 @@
         <v>661</v>
       </c>
       <c r="Y59" t="s">
-        <v>518</v>
+        <v>449</v>
       </c>
       <c r="Z59" t="s">
-        <v>872</v>
+        <v>853</v>
       </c>
       <c r="AA59">
-        <v>0.98845897140196071</v>
+        <v>0.97583059150286178</v>
       </c>
       <c r="AB59">
-        <v>211.58552429738629</v>
+        <v>443.10582244753374</v>
       </c>
       <c r="AD59" t="s">
         <v>562</v>
@@ -16915,13 +16915,13 @@
         <v>1172</v>
       </c>
       <c r="AN59" t="s">
-        <v>876</v>
+        <v>890</v>
       </c>
       <c r="AO59">
-        <v>0.9913968450205024</v>
+        <v>0.99331955625657153</v>
       </c>
       <c r="AP59">
-        <v>157.72450795745584</v>
+        <v>122.47480196285512</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16986,16 +16986,16 @@
         <v>663</v>
       </c>
       <c r="Y60" t="s">
-        <v>528</v>
+        <v>452</v>
       </c>
       <c r="Z60" t="s">
-        <v>848</v>
+        <v>876</v>
       </c>
       <c r="AA60">
-        <v>0.98629851964686077</v>
+        <v>0.98625550635031922</v>
       </c>
       <c r="AB60">
-        <v>251.19380647421841</v>
+        <v>251.98238357748133</v>
       </c>
       <c r="AD60" t="s">
         <v>562</v>
@@ -17025,13 +17025,13 @@
         <v>1173</v>
       </c>
       <c r="AN60" t="s">
-        <v>857</v>
+        <v>892</v>
       </c>
       <c r="AO60">
-        <v>0.98662924242305594</v>
+        <v>0.99328472140937729</v>
       </c>
       <c r="AP60">
-        <v>245.13055557730874</v>
+        <v>123.11344082808277</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -17096,16 +17096,16 @@
         <v>665</v>
       </c>
       <c r="Y61" t="s">
-        <v>552</v>
+        <v>501</v>
       </c>
       <c r="Z61" t="s">
-        <v>873</v>
+        <v>844</v>
       </c>
       <c r="AA61">
-        <v>0.98289372536542474</v>
+        <v>0.99445721337660409</v>
       </c>
       <c r="AB61">
-        <v>313.61503496721377</v>
+        <v>101.61775476225793</v>
       </c>
       <c r="AD61" t="s">
         <v>562</v>
@@ -17135,13 +17135,13 @@
         <v>1174</v>
       </c>
       <c r="AN61" t="s">
-        <v>844</v>
+        <v>886</v>
       </c>
       <c r="AO61">
-        <v>0.99375979852043306</v>
+        <v>0.99702387631899381</v>
       </c>
       <c r="AP61">
-        <v>114.40369379206156</v>
+        <v>54.562267485114141</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -17206,16 +17206,16 @@
         <v>667</v>
       </c>
       <c r="Y62" t="s">
-        <v>558</v>
+        <v>503</v>
       </c>
       <c r="Z62" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="AA62">
-        <v>0.99506342503584544</v>
+        <v>0.99323673511280519</v>
       </c>
       <c r="AB62">
-        <v>90.503874342833086</v>
+        <v>123.99318959857249</v>
       </c>
       <c r="AD62" t="s">
         <v>562</v>
@@ -17248,10 +17248,10 @@
         <v>846</v>
       </c>
       <c r="AO62">
-        <v>0.9935955776192904</v>
+        <v>0.99193693152956208</v>
       </c>
       <c r="AP62">
-        <v>117.41441031301009</v>
+        <v>147.8229219580285</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -17316,16 +17316,16 @@
         <v>669</v>
       </c>
       <c r="Y63" t="s">
-        <v>427</v>
+        <v>513</v>
       </c>
       <c r="Z63" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="AA63">
-        <v>0.9941804823678142</v>
+        <v>0.98413237776361673</v>
       </c>
       <c r="AB63">
-        <v>106.6911565900724</v>
+        <v>290.90640766702762</v>
       </c>
       <c r="AD63" t="s">
         <v>562</v>
@@ -17355,13 +17355,13 @@
         <v>1176</v>
       </c>
       <c r="AN63" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="AO63">
-        <v>0.9895134548380341</v>
+        <v>0.99063792186488431</v>
       </c>
       <c r="AP63">
-        <v>192.25332796937471</v>
+        <v>171.63809914378689</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17426,16 +17426,16 @@
         <v>671</v>
       </c>
       <c r="Y64" t="s">
-        <v>433</v>
+        <v>522</v>
       </c>
       <c r="Z64" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="AA64">
-        <v>0.99511659056551938</v>
+        <v>0.99131351134049961</v>
       </c>
       <c r="AB64">
-        <v>89.52917296547848</v>
+        <v>159.25229209083986</v>
       </c>
       <c r="AD64" t="s">
         <v>562</v>
@@ -17465,13 +17465,13 @@
         <v>1177</v>
       </c>
       <c r="AN64" t="s">
-        <v>880</v>
+        <v>851</v>
       </c>
       <c r="AO64">
-        <v>0.98960179851646224</v>
+        <v>0.9898048456745685</v>
       </c>
       <c r="AP64">
-        <v>190.63369386485829</v>
+        <v>186.91116263291045</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17536,16 +17536,16 @@
         <v>673</v>
       </c>
       <c r="Y65" t="s">
-        <v>438</v>
+        <v>544</v>
       </c>
       <c r="Z65" t="s">
-        <v>840</v>
+        <v>859</v>
       </c>
       <c r="AA65">
-        <v>0.96952136011150125</v>
+        <v>0.98661257708946326</v>
       </c>
       <c r="AB65">
-        <v>558.77506462247754</v>
+        <v>245.43608669317408</v>
       </c>
       <c r="AD65" t="s">
         <v>562</v>
@@ -17575,13 +17575,13 @@
         <v>1178</v>
       </c>
       <c r="AN65" t="s">
-        <v>851</v>
+        <v>879</v>
       </c>
       <c r="AO65">
-        <v>0.99388898978830953</v>
+        <v>0.99270552118216204</v>
       </c>
       <c r="AP65">
-        <v>112.03518721432623</v>
+        <v>133.73211166036262</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17646,16 +17646,16 @@
         <v>675</v>
       </c>
       <c r="Y66" t="s">
-        <v>478</v>
+        <v>560</v>
       </c>
       <c r="Z66" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="AA66">
-        <v>0.98977876009625232</v>
+        <v>0.99314801780790185</v>
       </c>
       <c r="AB66">
-        <v>187.38939823537481</v>
+        <v>125.61967352179877</v>
       </c>
       <c r="AD66" t="s">
         <v>562</v>
@@ -17685,13 +17685,13 @@
         <v>1179</v>
       </c>
       <c r="AN66" t="s">
-        <v>840</v>
+        <v>869</v>
       </c>
       <c r="AO66">
-        <v>0.98965200571238932</v>
+        <v>0.99077061821894719</v>
       </c>
       <c r="AP66">
-        <v>189.71322860619625</v>
+        <v>169.20533265263529</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17756,16 +17756,16 @@
         <v>677</v>
       </c>
       <c r="Y67" t="s">
-        <v>498</v>
+        <v>426</v>
       </c>
       <c r="Z67" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="AA67">
-        <v>0.99133392870479353</v>
+        <v>0.99359770729841634</v>
       </c>
       <c r="AB67">
-        <v>158.87797374545147</v>
+        <v>117.37536619570103</v>
       </c>
       <c r="AD67" t="s">
         <v>562</v>
@@ -17795,13 +17795,13 @@
         <v>1180</v>
       </c>
       <c r="AN67" t="s">
-        <v>877</v>
+        <v>840</v>
       </c>
       <c r="AO67">
-        <v>0.9865110114696487</v>
+        <v>0.97911240890549023</v>
       </c>
       <c r="AP67">
-        <v>247.29812305643949</v>
+        <v>382.93917006601345</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17866,16 +17866,16 @@
         <v>679</v>
       </c>
       <c r="Y68" t="s">
-        <v>511</v>
+        <v>432</v>
       </c>
       <c r="Z68" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="AA68">
-        <v>0.9810875794416769</v>
+        <v>0.99364006102472313</v>
       </c>
       <c r="AB68">
-        <v>346.72771023592401</v>
+        <v>116.59888121340903</v>
       </c>
       <c r="AD68" t="s">
         <v>562</v>
@@ -17905,13 +17905,13 @@
         <v>1181</v>
       </c>
       <c r="AN68" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AO68">
-        <v>0.98499499268435309</v>
+        <v>0.98540042793923122</v>
       </c>
       <c r="AP68">
-        <v>275.09180078686103</v>
+        <v>267.65882111409439</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17976,16 +17976,16 @@
         <v>681</v>
       </c>
       <c r="Y69" t="s">
-        <v>514</v>
+        <v>447</v>
       </c>
       <c r="Z69" t="s">
-        <v>878</v>
+        <v>853</v>
       </c>
       <c r="AA69">
-        <v>0.99206450778354704</v>
+        <v>0.96029753299263365</v>
       </c>
       <c r="AB69">
-        <v>145.4840239683044</v>
+        <v>727.87856180171616</v>
       </c>
       <c r="AD69" t="s">
         <v>562</v>
@@ -18015,13 +18015,13 @@
         <v>1182</v>
       </c>
       <c r="AN69" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="AO69">
-        <v>0.99401320046908392</v>
+        <v>0.99328745157332987</v>
       </c>
       <c r="AP69">
-        <v>109.75799140012764</v>
+        <v>123.06338782228508</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -18086,16 +18086,16 @@
         <v>683</v>
       </c>
       <c r="Y70" t="s">
-        <v>525</v>
+        <v>462</v>
       </c>
       <c r="Z70" t="s">
-        <v>879</v>
+        <v>848</v>
       </c>
       <c r="AA70">
-        <v>0.98787020216528199</v>
+        <v>0.97893171539705459</v>
       </c>
       <c r="AB70">
-        <v>222.37962696982947</v>
+        <v>386.25188438733272</v>
       </c>
       <c r="AD70" t="s">
         <v>562</v>
@@ -18125,13 +18125,13 @@
         <v>1183</v>
       </c>
       <c r="AN70" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="AO70">
-        <v>0.99317814360692358</v>
+        <v>0.97466160251195344</v>
       </c>
       <c r="AP70">
-        <v>125.06736720640154</v>
+        <v>464.53728728085309</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -18196,16 +18196,16 @@
         <v>685</v>
       </c>
       <c r="Y71" t="s">
-        <v>536</v>
+        <v>463</v>
       </c>
       <c r="Z71" t="s">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="AA71">
-        <v>0.98780336216423326</v>
+        <v>0.99099682968404001</v>
       </c>
       <c r="AB71">
-        <v>223.60502698905651</v>
+        <v>165.05812245926603</v>
       </c>
       <c r="AD71" t="s">
         <v>562</v>
@@ -18235,13 +18235,13 @@
         <v>1184</v>
       </c>
       <c r="AN71" t="s">
-        <v>865</v>
+        <v>897</v>
       </c>
       <c r="AO71">
-        <v>0.99086943207021283</v>
+        <v>0.99748710010368635</v>
       </c>
       <c r="AP71">
-        <v>167.3937453794307</v>
+        <v>46.069831432417168</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -18306,16 +18306,16 @@
         <v>687</v>
       </c>
       <c r="Y72" t="s">
-        <v>559</v>
+        <v>466</v>
       </c>
       <c r="Z72" t="s">
-        <v>881</v>
+        <v>848</v>
       </c>
       <c r="AA72">
-        <v>0.9935358987764813</v>
+        <v>0.97972538426958966</v>
       </c>
       <c r="AB72">
-        <v>118.50852243117704</v>
+        <v>371.70128839085726</v>
       </c>
       <c r="AD72" t="s">
         <v>562</v>
@@ -18345,13 +18345,13 @@
         <v>1185</v>
       </c>
       <c r="AN72" t="s">
-        <v>868</v>
+        <v>885</v>
       </c>
       <c r="AO72">
-        <v>0.99302300928376919</v>
+        <v>0.99472130687422744</v>
       </c>
       <c r="AP72">
-        <v>127.91149646423172</v>
+        <v>96.776040639162858</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -18416,16 +18416,16 @@
         <v>689</v>
       </c>
       <c r="Y73" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="Z73" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="AA73">
-        <v>0.97154747480032433</v>
+        <v>0.98785527533632433</v>
       </c>
       <c r="AB73">
-        <v>521.62962866072098</v>
+        <v>222.65328550072056</v>
       </c>
       <c r="AD73" t="s">
         <v>562</v>
@@ -18455,13 +18455,13 @@
         <v>1186</v>
       </c>
       <c r="AN73" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="AO73">
-        <v>0.99011319269869458</v>
+        <v>0.99387886431172578</v>
       </c>
       <c r="AP73">
-        <v>181.25813385726678</v>
+        <v>112.22082095169485</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -18526,16 +18526,16 @@
         <v>691</v>
       </c>
       <c r="Y74" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="Z74" t="s">
-        <v>882</v>
+        <v>843</v>
       </c>
       <c r="AA74">
-        <v>0.9790049953928549</v>
+        <v>0.98415070826722661</v>
       </c>
       <c r="AB74">
-        <v>384.908417797661</v>
+        <v>290.5703484341791</v>
       </c>
       <c r="AD74" t="s">
         <v>562</v>
@@ -18565,13 +18565,13 @@
         <v>1187</v>
       </c>
       <c r="AN74" t="s">
-        <v>842</v>
+        <v>855</v>
       </c>
       <c r="AO74">
-        <v>0.99448552674849922</v>
+        <v>0.9864929875546109</v>
       </c>
       <c r="AP74">
-        <v>101.09867627751461</v>
+        <v>247.62856149880113</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18636,16 +18636,16 @@
         <v>693</v>
       </c>
       <c r="Y75" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="Z75" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="AA75">
-        <v>0.99512310450028352</v>
+        <v>0.9922931816569136</v>
       </c>
       <c r="AB75">
-        <v>89.409750828135486</v>
+        <v>141.29166962325118</v>
       </c>
       <c r="AD75" t="s">
         <v>562</v>
@@ -18675,13 +18675,13 @@
         <v>1188</v>
       </c>
       <c r="AN75" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AO75">
-        <v>0.98107014020732863</v>
+        <v>0.99214368255188645</v>
       </c>
       <c r="AP75">
-        <v>347.04742953230885</v>
+        <v>144.03248654874827</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18746,16 +18746,16 @@
         <v>695</v>
       </c>
       <c r="Y76" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Z76" t="s">
-        <v>848</v>
+        <v>874</v>
       </c>
       <c r="AA76">
-        <v>0.99180643818152092</v>
+        <v>0.99053483022914257</v>
       </c>
       <c r="AB76">
-        <v>150.21530000545005</v>
+        <v>173.52811246571903</v>
       </c>
       <c r="AD76" t="s">
         <v>562</v>
@@ -18785,13 +18785,13 @@
         <v>1189</v>
       </c>
       <c r="AN76" t="s">
-        <v>849</v>
+        <v>894</v>
       </c>
       <c r="AO76">
-        <v>0.99547447105677267</v>
+        <v>0.9928290104176094</v>
       </c>
       <c r="AP76">
-        <v>82.96803062583389</v>
+        <v>131.46814234382811</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18856,16 +18856,16 @@
         <v>697</v>
       </c>
       <c r="Y77" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="Z77" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="AA77">
-        <v>0.97919938492738179</v>
+        <v>0.98320360732321854</v>
       </c>
       <c r="AB77">
-        <v>381.34460966466662</v>
+        <v>307.93386574099321</v>
       </c>
       <c r="AD77" t="s">
         <v>562</v>
@@ -18895,13 +18895,13 @@
         <v>1190</v>
       </c>
       <c r="AN77" t="s">
-        <v>866</v>
+        <v>849</v>
       </c>
       <c r="AO77">
-        <v>0.98690358786307586</v>
+        <v>0.97791499844986385</v>
       </c>
       <c r="AP77">
-        <v>240.10088917694185</v>
+        <v>404.89169508582842</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18966,16 +18966,16 @@
         <v>699</v>
       </c>
       <c r="Y78" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="Z78" t="s">
-        <v>866</v>
+        <v>845</v>
       </c>
       <c r="AA78">
-        <v>0.98325714881672288</v>
+        <v>0.98897406466844573</v>
       </c>
       <c r="AB78">
-        <v>306.95227169341439</v>
+        <v>202.14214774516236</v>
       </c>
       <c r="AD78" t="s">
         <v>562</v>
@@ -19005,13 +19005,13 @@
         <v>1191</v>
       </c>
       <c r="AN78" t="s">
-        <v>881</v>
+        <v>864</v>
       </c>
       <c r="AO78">
-        <v>0.9941444177652955</v>
+        <v>0.977944947494224</v>
       </c>
       <c r="AP78">
-        <v>107.35234096958277</v>
+        <v>404.34262927256032</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -19076,16 +19076,16 @@
         <v>701</v>
       </c>
       <c r="Y79" t="s">
-        <v>429</v>
+        <v>554</v>
       </c>
       <c r="Z79" t="s">
-        <v>839</v>
+        <v>881</v>
       </c>
       <c r="AA79">
-        <v>0.99232963975206445</v>
+        <v>0.99152145048007134</v>
       </c>
       <c r="AB79">
-        <v>140.62327121215228</v>
+        <v>155.44007453202627</v>
       </c>
       <c r="AD79" t="s">
         <v>562</v>
@@ -19115,13 +19115,13 @@
         <v>1192</v>
       </c>
       <c r="AN79" t="s">
-        <v>840</v>
+        <v>889</v>
       </c>
       <c r="AO79">
-        <v>0.98896692202674552</v>
+        <v>0.99502057695725243</v>
       </c>
       <c r="AP79">
-        <v>202.27309617633225</v>
+        <v>91.289422450372911</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -19186,16 +19186,16 @@
         <v>703</v>
       </c>
       <c r="Y80" t="s">
-        <v>443</v>
+        <v>502</v>
       </c>
       <c r="Z80" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="AA80">
-        <v>0.98863637284234351</v>
+        <v>0.99142410630444711</v>
       </c>
       <c r="AB80">
-        <v>208.33316455703533</v>
+        <v>157.22471775180347</v>
       </c>
       <c r="AD80" t="s">
         <v>562</v>
@@ -19225,13 +19225,13 @@
         <v>1193</v>
       </c>
       <c r="AN80" t="s">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="AO80">
-        <v>0.99224743662419923</v>
+        <v>0.9742069477253853</v>
       </c>
       <c r="AP80">
-        <v>142.13032855634668</v>
+        <v>472.87262503460209</v>
       </c>
     </row>
     <row r="81" spans="2:42">
@@ -19296,16 +19296,16 @@
         <v>705</v>
       </c>
       <c r="Y81" t="s">
-        <v>454</v>
+        <v>523</v>
       </c>
       <c r="Z81" t="s">
-        <v>884</v>
+        <v>851</v>
       </c>
       <c r="AA81">
-        <v>0.99016939403137849</v>
+        <v>0.99218904910018979</v>
       </c>
       <c r="AB81">
-        <v>180.22777609139402</v>
+        <v>143.20076649652023</v>
       </c>
       <c r="AD81" t="s">
         <v>562</v>
@@ -19338,10 +19338,10 @@
         <v>888</v>
       </c>
       <c r="AO81">
-        <v>0.96642968891663028</v>
+        <v>0.99090442938878043</v>
       </c>
       <c r="AP81">
-        <v>615.45570319511182</v>
+        <v>166.75212787235887</v>
       </c>
     </row>
     <row r="82" spans="2:42">
@@ -19406,16 +19406,16 @@
         <v>707</v>
       </c>
       <c r="Y82" t="s">
-        <v>461</v>
+        <v>527</v>
       </c>
       <c r="Z82" t="s">
-        <v>882</v>
+        <v>865</v>
       </c>
       <c r="AA82">
-        <v>0.9849937388690081</v>
+        <v>0.97564251840922733</v>
       </c>
       <c r="AB82">
-        <v>275.11478740151779</v>
+        <v>446.55382916416522</v>
       </c>
       <c r="AD82" t="s">
         <v>562</v>
@@ -19445,13 +19445,13 @@
         <v>1195</v>
       </c>
       <c r="AN82" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="AO82">
-        <v>0.97580462137033996</v>
+        <v>0.99222882711684135</v>
       </c>
       <c r="AP82">
-        <v>443.58194154376798</v>
+        <v>142.4715028579086</v>
       </c>
     </row>
     <row r="83" spans="2:42">
@@ -19516,16 +19516,16 @@
         <v>709</v>
       </c>
       <c r="Y83" t="s">
-        <v>465</v>
+        <v>534</v>
       </c>
       <c r="Z83" t="s">
         <v>882</v>
       </c>
       <c r="AA83">
-        <v>0.96879824550148963</v>
+        <v>0.9954097472817981</v>
       </c>
       <c r="AB83">
-        <v>572.03216580602339</v>
+        <v>84.154633167035314</v>
       </c>
       <c r="AD83" t="s">
         <v>562</v>
@@ -19555,13 +19555,13 @@
         <v>1196</v>
       </c>
       <c r="AN83" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="AO83">
-        <v>0.98941824689872981</v>
+        <v>0.97263268500799516</v>
       </c>
       <c r="AP83">
-        <v>193.99880685662112</v>
+        <v>501.73410818675478</v>
       </c>
     </row>
     <row r="84" spans="2:42">
@@ -19626,16 +19626,16 @@
         <v>711</v>
       </c>
       <c r="Y84" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="Z84" t="s">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="AA84">
-        <v>0.99058937597842778</v>
+        <v>0.98928836714403978</v>
       </c>
       <c r="AB84">
-        <v>172.52810706215647</v>
+        <v>196.37993569260354</v>
       </c>
       <c r="AD84" t="s">
         <v>562</v>
@@ -19665,13 +19665,13 @@
         <v>1197</v>
       </c>
       <c r="AN84" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="AO84">
-        <v>0.9911899510437201</v>
+        <v>0.99099526421280915</v>
       </c>
       <c r="AP84">
-        <v>161.51756419846544</v>
+        <v>165.08682276516558</v>
       </c>
     </row>
     <row r="85" spans="2:42">
@@ -19736,16 +19736,16 @@
         <v>713</v>
       </c>
       <c r="Y85" t="s">
-        <v>517</v>
+        <v>434</v>
       </c>
       <c r="Z85" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="AA85">
-        <v>0.98884641033160892</v>
+        <v>0.98994820353208668</v>
       </c>
       <c r="AB85">
-        <v>204.48247725383573</v>
+        <v>184.28293524507683</v>
       </c>
       <c r="AD85" t="s">
         <v>562</v>
@@ -19775,13 +19775,13 @@
         <v>1198</v>
       </c>
       <c r="AN85" t="s">
-        <v>848</v>
+        <v>884</v>
       </c>
       <c r="AO85">
-        <v>0.97139194185607003</v>
+        <v>0.99072339258685749</v>
       </c>
       <c r="AP85">
-        <v>524.48106597204946</v>
+        <v>170.07113590761304</v>
       </c>
     </row>
     <row r="86" spans="2:42">
@@ -19846,16 +19846,16 @@
         <v>715</v>
       </c>
       <c r="Y86" t="s">
-        <v>524</v>
+        <v>475</v>
       </c>
       <c r="Z86" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="AA86">
-        <v>0.98971858307134875</v>
+        <v>0.99211578471201944</v>
       </c>
       <c r="AB86">
-        <v>188.49264369194051</v>
+        <v>144.54394694630997</v>
       </c>
       <c r="AD86" t="s">
         <v>562</v>
@@ -19885,13 +19885,13 @@
         <v>1199</v>
       </c>
       <c r="AN86" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="AO86">
-        <v>0.98117052771194446</v>
+        <v>0.98702528039583703</v>
       </c>
       <c r="AP86">
-        <v>345.20699194768525</v>
+        <v>237.86985940965451</v>
       </c>
     </row>
     <row r="87" spans="2:42">
@@ -19956,16 +19956,16 @@
         <v>717</v>
       </c>
       <c r="Y87" t="s">
-        <v>556</v>
+        <v>477</v>
       </c>
       <c r="Z87" t="s">
-        <v>885</v>
+        <v>870</v>
       </c>
       <c r="AA87">
-        <v>0.98974367616617376</v>
+        <v>0.99243446061187979</v>
       </c>
       <c r="AB87">
-        <v>188.03260362014854</v>
+        <v>138.70155544887155</v>
       </c>
       <c r="AD87" t="s">
         <v>562</v>
@@ -19995,13 +19995,13 @@
         <v>1200</v>
       </c>
       <c r="AN87" t="s">
-        <v>848</v>
+        <v>895</v>
       </c>
       <c r="AO87">
-        <v>0.98127559165304223</v>
+        <v>0.99511776358677106</v>
       </c>
       <c r="AP87">
-        <v>343.28081969422635</v>
+        <v>89.507667575863124</v>
       </c>
     </row>
     <row r="88" spans="2:42">
@@ -20066,16 +20066,16 @@
         <v>719</v>
       </c>
       <c r="Y88" t="s">
-        <v>434</v>
+        <v>489</v>
       </c>
       <c r="Z88" t="s">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="AA88">
-        <v>0.98994820353208668</v>
+        <v>0.98250540566262157</v>
       </c>
       <c r="AB88">
-        <v>184.28293524507683</v>
+        <v>320.7342295186051</v>
       </c>
       <c r="AD88" t="s">
         <v>562</v>
@@ -20105,13 +20105,13 @@
         <v>1201</v>
       </c>
       <c r="AN88" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="AO88">
-        <v>0.9733086107906429</v>
+        <v>0.99298280898033964</v>
       </c>
       <c r="AP88">
-        <v>489.34213550487942</v>
+        <v>128.64850202710696</v>
       </c>
     </row>
     <row r="89" spans="2:42">
@@ -20176,16 +20176,16 @@
         <v>721</v>
       </c>
       <c r="Y89" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="Z89" t="s">
-        <v>886</v>
+        <v>849</v>
       </c>
       <c r="AA89">
-        <v>0.99211578471201944</v>
+        <v>0.97974410411433677</v>
       </c>
       <c r="AB89">
-        <v>144.54394694630997</v>
+        <v>371.35809123716024</v>
       </c>
       <c r="AD89" t="s">
         <v>562</v>
@@ -20215,13 +20215,13 @@
         <v>1202</v>
       </c>
       <c r="AN89" t="s">
-        <v>889</v>
+        <v>867</v>
       </c>
       <c r="AO89">
-        <v>0.9839431789633305</v>
+        <v>0.99562564597459979</v>
       </c>
       <c r="AP89">
-        <v>294.37505233894177</v>
+        <v>80.196490465669797</v>
       </c>
     </row>
     <row r="90" spans="2:42">
@@ -20286,16 +20286,16 @@
         <v>723</v>
       </c>
       <c r="Y90" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="Z90" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="AA90">
-        <v>0.99243446061187979</v>
+        <v>0.98904809077723221</v>
       </c>
       <c r="AB90">
-        <v>138.70155544887155</v>
+        <v>200.7850024174094</v>
       </c>
       <c r="AD90" t="s">
         <v>562</v>
@@ -20325,13 +20325,13 @@
         <v>1203</v>
       </c>
       <c r="AN90" t="s">
-        <v>882</v>
+        <v>839</v>
       </c>
       <c r="AO90">
-        <v>0.96950481457473103</v>
+        <v>0.99304329114881718</v>
       </c>
       <c r="AP90">
-        <v>559.0783994632643</v>
+        <v>127.53966227168546</v>
       </c>
     </row>
     <row r="91" spans="2:42">
@@ -20396,16 +20396,16 @@
         <v>725</v>
       </c>
       <c r="Y91" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="Z91" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="AA91">
-        <v>0.98250540566262157</v>
+        <v>0.992383122341708</v>
       </c>
       <c r="AB91">
-        <v>320.7342295186051</v>
+        <v>139.64275706868568</v>
       </c>
       <c r="AD91" t="s">
         <v>562</v>
@@ -20435,13 +20435,13 @@
         <v>1204</v>
       </c>
       <c r="AN91" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="AO91">
-        <v>0.99331955625657153</v>
+        <v>0.99264385543323097</v>
       </c>
       <c r="AP91">
-        <v>122.47480196285512</v>
+        <v>134.8626503907652</v>
       </c>
     </row>
     <row r="92" spans="2:42">
@@ -20506,16 +20506,16 @@
         <v>727</v>
       </c>
       <c r="Y92" t="s">
-        <v>496</v>
+        <v>551</v>
       </c>
       <c r="Z92" t="s">
-        <v>852</v>
+        <v>866</v>
       </c>
       <c r="AA92">
-        <v>0.97974410411433677</v>
+        <v>0.98782738263402425</v>
       </c>
       <c r="AB92">
-        <v>371.35809123716024</v>
+        <v>223.16465170955473</v>
       </c>
       <c r="AD92" t="s">
         <v>562</v>
@@ -20545,13 +20545,13 @@
         <v>1205</v>
       </c>
       <c r="AN92" t="s">
-        <v>897</v>
+        <v>853</v>
       </c>
       <c r="AO92">
-        <v>0.99328472140937729</v>
+        <v>0.98530274641518678</v>
       </c>
       <c r="AP92">
-        <v>123.11344082808277</v>
+        <v>269.44964905490986</v>
       </c>
     </row>
     <row r="93" spans="2:42">
@@ -20616,16 +20616,16 @@
         <v>729</v>
       </c>
       <c r="Y93" t="s">
-        <v>504</v>
+        <v>553</v>
       </c>
       <c r="Z93" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="AA93">
-        <v>0.98904809077723221</v>
+        <v>0.9912814094707586</v>
       </c>
       <c r="AB93">
-        <v>200.7850024174094</v>
+        <v>159.84082636942577</v>
       </c>
       <c r="AD93" t="s">
         <v>562</v>
@@ -20655,13 +20655,13 @@
         <v>1206</v>
       </c>
       <c r="AN93" t="s">
-        <v>867</v>
+        <v>847</v>
       </c>
       <c r="AO93">
-        <v>0.99518979370471228</v>
+        <v>0.98558146952732006</v>
       </c>
       <c r="AP93">
-        <v>88.187115413608197</v>
+        <v>264.33972533246634</v>
       </c>
     </row>
     <row r="94" spans="2:42">
@@ -20726,16 +20726,16 @@
         <v>731</v>
       </c>
       <c r="Y94" t="s">
-        <v>521</v>
+        <v>431</v>
       </c>
       <c r="Z94" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="AA94">
-        <v>0.992383122341708</v>
+        <v>0.99217497048797409</v>
       </c>
       <c r="AB94">
-        <v>139.64275706868568</v>
+        <v>143.45887438714203</v>
       </c>
       <c r="AD94" t="s">
         <v>562</v>
@@ -20765,13 +20765,13 @@
         <v>1207</v>
       </c>
       <c r="AN94" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="AO94">
-        <v>0.99193701535303302</v>
+        <v>0.98563706266808038</v>
       </c>
       <c r="AP94">
-        <v>147.82138519439451</v>
+        <v>263.32051775185897</v>
       </c>
     </row>
     <row r="95" spans="2:42">
@@ -20836,16 +20836,16 @@
         <v>733</v>
       </c>
       <c r="Y95" t="s">
-        <v>551</v>
+        <v>441</v>
       </c>
       <c r="Z95" t="s">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="AA95">
-        <v>0.98782738263402425</v>
+        <v>0.99688734285602987</v>
       </c>
       <c r="AB95">
-        <v>223.16465170955473</v>
+        <v>57.065380972786443</v>
       </c>
       <c r="AD95" t="s">
         <v>562</v>
@@ -20875,13 +20875,13 @@
         <v>1208</v>
       </c>
       <c r="AN95" t="s">
-        <v>888</v>
+        <v>862</v>
       </c>
       <c r="AO95">
-        <v>0.98119061265866536</v>
+        <v>0.9859891893004602</v>
       </c>
       <c r="AP95">
-        <v>344.8387679244683</v>
+        <v>256.8648628248954</v>
       </c>
     </row>
     <row r="96" spans="2:42">
@@ -20946,16 +20946,16 @@
         <v>735</v>
       </c>
       <c r="Y96" t="s">
-        <v>553</v>
+        <v>444</v>
       </c>
       <c r="Z96" t="s">
-        <v>873</v>
+        <v>846</v>
       </c>
       <c r="AA96">
-        <v>0.9912814094707586</v>
+        <v>0.99243001465918479</v>
       </c>
       <c r="AB96">
-        <v>159.84082636942577</v>
+        <v>138.78306458161211</v>
       </c>
       <c r="AD96" t="s">
         <v>562</v>
@@ -20985,13 +20985,13 @@
         <v>1209</v>
       </c>
       <c r="AN96" t="s">
-        <v>841</v>
+        <v>863</v>
       </c>
       <c r="AO96">
-        <v>0.98974332571937795</v>
+        <v>0.98980378364600918</v>
       </c>
       <c r="AP96">
-        <v>188.03902847807063</v>
+        <v>186.93063315649889</v>
       </c>
     </row>
     <row r="97" spans="2:42">
@@ -21056,16 +21056,16 @@
         <v>737</v>
       </c>
       <c r="Y97" t="s">
-        <v>449</v>
+        <v>484</v>
       </c>
       <c r="Z97" t="s">
-        <v>888</v>
+        <v>843</v>
       </c>
       <c r="AA97">
-        <v>0.97583059150286178</v>
+        <v>0.96964927506180898</v>
       </c>
       <c r="AB97">
-        <v>443.10582244753374</v>
+        <v>556.42995720016825</v>
       </c>
       <c r="AD97" t="s">
         <v>562</v>
@@ -21095,13 +21095,13 @@
         <v>1210</v>
       </c>
       <c r="AN97" t="s">
-        <v>877</v>
+        <v>845</v>
       </c>
       <c r="AO97">
-        <v>0.99413168612390446</v>
+        <v>0.99069539601336043</v>
       </c>
       <c r="AP97">
-        <v>107.58575439508574</v>
+        <v>170.5844064217261</v>
       </c>
     </row>
     <row r="98" spans="2:42">
@@ -21166,16 +21166,16 @@
         <v>739</v>
       </c>
       <c r="Y98" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="Z98" t="s">
-        <v>889</v>
+        <v>849</v>
       </c>
       <c r="AA98">
-        <v>0.98625550635031922</v>
+        <v>0.9741863781992316</v>
       </c>
       <c r="AB98">
-        <v>251.98238357748133</v>
+        <v>473.24973301408767</v>
       </c>
       <c r="AD98" t="s">
         <v>562</v>
@@ -21205,13 +21205,13 @@
         <v>1211</v>
       </c>
       <c r="AN98" t="s">
-        <v>843</v>
+        <v>859</v>
       </c>
       <c r="AO98">
-        <v>0.96802468703178957</v>
+        <v>0.98658832734700097</v>
       </c>
       <c r="AP98">
-        <v>586.21407108385756</v>
+        <v>245.88066530498185</v>
       </c>
     </row>
     <row r="99" spans="2:42">
@@ -21276,16 +21276,16 @@
         <v>741</v>
       </c>
       <c r="Y99" t="s">
-        <v>501</v>
+        <v>545</v>
       </c>
       <c r="Z99" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="AA99">
-        <v>0.99445721337660409</v>
+        <v>0.99407588262977375</v>
       </c>
       <c r="AB99">
-        <v>101.61775476225793</v>
+        <v>108.60881845414757</v>
       </c>
       <c r="AD99" t="s">
         <v>562</v>
@@ -21315,13 +21315,13 @@
         <v>1212</v>
       </c>
       <c r="AN99" t="s">
-        <v>843</v>
+        <v>879</v>
       </c>
       <c r="AO99">
-        <v>0.97711913570486986</v>
+        <v>0.99423394997920433</v>
       </c>
       <c r="AP99">
-        <v>419.48251207738639</v>
+        <v>105.71091704792103</v>
       </c>
     </row>
     <row r="100" spans="2:42">
@@ -21386,16 +21386,16 @@
         <v>743</v>
       </c>
       <c r="Y100" t="s">
-        <v>503</v>
+        <v>547</v>
       </c>
       <c r="Z100" t="s">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="AA100">
-        <v>0.99323673511280519</v>
+        <v>0.97256549686216975</v>
       </c>
       <c r="AB100">
-        <v>123.99318959857249</v>
+        <v>502.96589086022118</v>
       </c>
       <c r="AD100" t="s">
         <v>562</v>
@@ -21425,13 +21425,13 @@
         <v>1213</v>
       </c>
       <c r="AN100" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="AO100">
-        <v>0.97535827976293088</v>
+        <v>0.99467731181029251</v>
       </c>
       <c r="AP100">
-        <v>451.76487101293469</v>
+        <v>97.582616811304106</v>
       </c>
     </row>
     <row r="101" spans="2:42">
@@ -21496,16 +21496,16 @@
         <v>745</v>
       </c>
       <c r="Y101" t="s">
-        <v>513</v>
+        <v>425</v>
       </c>
       <c r="Z101" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="AA101">
-        <v>0.98413237776361673</v>
+        <v>0.99579045202592908</v>
       </c>
       <c r="AB101">
-        <v>290.90640766702762</v>
+        <v>77.175046191301078</v>
       </c>
       <c r="AD101" t="s">
         <v>562</v>
@@ -21535,13 +21535,13 @@
         <v>1214</v>
       </c>
       <c r="AN101" t="s">
-        <v>866</v>
+        <v>849</v>
       </c>
       <c r="AO101">
-        <v>0.9754113935826384</v>
+        <v>0.97803634076421897</v>
       </c>
       <c r="AP101">
-        <v>450.79111765163026</v>
+        <v>402.6670859893182</v>
       </c>
     </row>
     <row r="102" spans="2:42">
@@ -21606,16 +21606,16 @@
         <v>747</v>
       </c>
       <c r="Y102" t="s">
-        <v>522</v>
+        <v>437</v>
       </c>
       <c r="Z102" t="s">
-        <v>890</v>
+        <v>840</v>
       </c>
       <c r="AA102">
-        <v>0.99131351134049961</v>
+        <v>0.95765547041534393</v>
       </c>
       <c r="AB102">
-        <v>159.25229209083986</v>
+        <v>776.31637571869453</v>
       </c>
       <c r="AD102" t="s">
         <v>562</v>
@@ -21645,13 +21645,13 @@
         <v>1215</v>
       </c>
       <c r="AN102" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="AO102">
-        <v>0.99270552118216204</v>
+        <v>0.99267357107797494</v>
       </c>
       <c r="AP102">
-        <v>133.73211166036262</v>
+        <v>134.31786357045974</v>
       </c>
     </row>
     <row r="103" spans="2:42">
@@ -21716,16 +21716,16 @@
         <v>749</v>
       </c>
       <c r="Y103" t="s">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="Z103" t="s">
-        <v>866</v>
+        <v>849</v>
       </c>
       <c r="AA103">
-        <v>0.98661257708946326</v>
+        <v>0.98394190948405269</v>
       </c>
       <c r="AB103">
-        <v>245.43608669317408</v>
+        <v>294.3983261257012</v>
       </c>
       <c r="AD103" t="s">
         <v>562</v>
@@ -21755,13 +21755,13 @@
         <v>1216</v>
       </c>
       <c r="AN103" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="AO103">
-        <v>0.99077061821894719</v>
+        <v>0.98837316480290893</v>
       </c>
       <c r="AP103">
-        <v>169.20533265263529</v>
+        <v>213.15864528000296</v>
       </c>
     </row>
     <row r="104" spans="2:42">
@@ -21826,16 +21826,16 @@
         <v>751</v>
       </c>
       <c r="Y104" t="s">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="Z104" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="AA104">
-        <v>0.99314801780790185</v>
+        <v>0.97498879609676647</v>
       </c>
       <c r="AB104">
-        <v>125.61967352179877</v>
+        <v>458.53873822594755</v>
       </c>
       <c r="AD104" t="s">
         <v>562</v>
@@ -21865,13 +21865,13 @@
         <v>1217</v>
       </c>
       <c r="AN104" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="AO104">
-        <v>0.97911240890549023</v>
+        <v>0.9924503916821712</v>
       </c>
       <c r="AP104">
-        <v>382.93917006601345</v>
+        <v>138.40948582686161</v>
       </c>
     </row>
     <row r="105" spans="2:42">
@@ -21936,16 +21936,16 @@
         <v>753</v>
       </c>
       <c r="Y105" t="s">
-        <v>426</v>
+        <v>533</v>
       </c>
       <c r="Z105" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
       <c r="AA105">
-        <v>0.99359770729841634</v>
+        <v>0.9903652333518761</v>
       </c>
       <c r="AB105">
-        <v>117.37536619570103</v>
+        <v>176.63738854893887</v>
       </c>
       <c r="AD105" t="s">
         <v>562</v>
@@ -21975,13 +21975,13 @@
         <v>1218</v>
       </c>
       <c r="AN105" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="AO105">
-        <v>0.98540042793923122</v>
+        <v>0.99388898978830953</v>
       </c>
       <c r="AP105">
-        <v>267.65882111409439</v>
+        <v>112.03518721432623</v>
       </c>
     </row>
     <row r="106" spans="2:42">
@@ -22046,16 +22046,16 @@
         <v>755</v>
       </c>
       <c r="Y106" t="s">
-        <v>432</v>
+        <v>539</v>
       </c>
       <c r="Z106" t="s">
-        <v>863</v>
+        <v>883</v>
       </c>
       <c r="AA106">
-        <v>0.99364006102472313</v>
+        <v>0.98359157932992225</v>
       </c>
       <c r="AB106">
-        <v>116.59888121340903</v>
+        <v>300.82104561809257</v>
       </c>
       <c r="AD106" t="s">
         <v>562</v>
@@ -22085,13 +22085,13 @@
         <v>1219</v>
       </c>
       <c r="AN106" t="s">
-        <v>878</v>
+        <v>840</v>
       </c>
       <c r="AO106">
-        <v>0.99328745157332987</v>
+        <v>0.98965200571238932</v>
       </c>
       <c r="AP106">
-        <v>123.06338782228508</v>
+        <v>189.71322860619625</v>
       </c>
     </row>
     <row r="107" spans="2:42">
@@ -22156,16 +22156,16 @@
         <v>757</v>
       </c>
       <c r="Y107" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="Z107" t="s">
-        <v>888</v>
+        <v>848</v>
       </c>
       <c r="AA107">
-        <v>0.96029753299263365</v>
+        <v>0.97154747480032433</v>
       </c>
       <c r="AB107">
-        <v>727.87856180171616</v>
+        <v>521.62962866072098</v>
       </c>
       <c r="AD107" t="s">
         <v>562</v>
@@ -22195,13 +22195,13 @@
         <v>1220</v>
       </c>
       <c r="AN107" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AO107">
-        <v>0.97466160251195344</v>
+        <v>0.9865110114696487</v>
       </c>
       <c r="AP107">
-        <v>464.53728728085309</v>
+        <v>247.29812305643949</v>
       </c>
     </row>
     <row r="108" spans="2:42">
@@ -22266,16 +22266,16 @@
         <v>759</v>
       </c>
       <c r="Y108" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="Z108" t="s">
-        <v>882</v>
+        <v>848</v>
       </c>
       <c r="AA108">
-        <v>0.97893171539705459</v>
+        <v>0.9790049953928549</v>
       </c>
       <c r="AB108">
-        <v>386.25188438733272</v>
+        <v>384.908417797661</v>
       </c>
       <c r="AD108" t="s">
         <v>562</v>
@@ -22305,13 +22305,13 @@
         <v>1221</v>
       </c>
       <c r="AN108" t="s">
-        <v>893</v>
+        <v>849</v>
       </c>
       <c r="AO108">
-        <v>0.99748710010368635</v>
+        <v>0.98499499268435309</v>
       </c>
       <c r="AP108">
-        <v>46.069831432417168</v>
+        <v>275.09180078686103</v>
       </c>
     </row>
     <row r="109" spans="2:42">
@@ -22376,16 +22376,16 @@
         <v>761</v>
       </c>
       <c r="Y109" t="s">
-        <v>463</v>
+        <v>519</v>
       </c>
       <c r="Z109" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="AA109">
-        <v>0.99099682968404001</v>
+        <v>0.99512310450028352</v>
       </c>
       <c r="AB109">
-        <v>165.05812245926603</v>
+        <v>89.409750828135486</v>
       </c>
       <c r="AD109" t="s">
         <v>562</v>
@@ -22415,13 +22415,13 @@
         <v>1222</v>
       </c>
       <c r="AN109" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="AO109">
-        <v>0.99472130687422744</v>
+        <v>0.99401320046908392</v>
       </c>
       <c r="AP109">
-        <v>96.776040639162858</v>
+        <v>109.75799140012764</v>
       </c>
     </row>
     <row r="110" spans="2:42">
@@ -22486,16 +22486,16 @@
         <v>763</v>
       </c>
       <c r="Y110" t="s">
-        <v>466</v>
+        <v>531</v>
       </c>
       <c r="Z110" t="s">
-        <v>882</v>
+        <v>865</v>
       </c>
       <c r="AA110">
-        <v>0.97972538426958966</v>
+        <v>0.99180643818152092</v>
       </c>
       <c r="AB110">
-        <v>371.70128839085726</v>
+        <v>150.21530000545005</v>
       </c>
       <c r="AD110" t="s">
         <v>562</v>
@@ -22525,13 +22525,13 @@
         <v>1223</v>
       </c>
       <c r="AN110" t="s">
-        <v>885</v>
+        <v>840</v>
       </c>
       <c r="AO110">
-        <v>0.99387886431172578</v>
+        <v>0.97986124669518093</v>
       </c>
       <c r="AP110">
-        <v>112.22082095169485</v>
+        <v>369.21047725501711</v>
       </c>
     </row>
     <row r="111" spans="2:42">
@@ -22596,16 +22596,16 @@
         <v>765</v>
       </c>
       <c r="Y111" t="s">
-        <v>476</v>
+        <v>532</v>
       </c>
       <c r="Z111" t="s">
-        <v>891</v>
+        <v>865</v>
       </c>
       <c r="AA111">
-        <v>0.98785527533632433</v>
+        <v>0.97919938492738179</v>
       </c>
       <c r="AB111">
-        <v>222.65328550072056</v>
+        <v>381.34460966466662</v>
       </c>
       <c r="AD111" t="s">
         <v>562</v>
@@ -22635,13 +22635,13 @@
         <v>1224</v>
       </c>
       <c r="AN111" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AO111">
-        <v>0.98086141539930738</v>
+        <v>0.99347009078887716</v>
       </c>
       <c r="AP111">
-        <v>350.87405101269854</v>
+        <v>119.71500220391977</v>
       </c>
     </row>
     <row r="112" spans="2:42">
@@ -22706,16 +22706,16 @@
         <v>767</v>
       </c>
       <c r="Y112" t="s">
-        <v>486</v>
+        <v>548</v>
       </c>
       <c r="Z112" t="s">
-        <v>843</v>
+        <v>859</v>
       </c>
       <c r="AA112">
-        <v>0.98415070826722661</v>
+        <v>0.98325714881672288</v>
       </c>
       <c r="AB112">
-        <v>290.5703484341791</v>
+        <v>306.95227169341439</v>
       </c>
       <c r="AD112" t="s">
         <v>562</v>
@@ -22745,13 +22745,13 @@
         <v>1225</v>
       </c>
       <c r="AN112" t="s">
-        <v>882</v>
+        <v>863</v>
       </c>
       <c r="AO112">
-        <v>0.98555037049604</v>
+        <v>0.98231817048454484</v>
       </c>
       <c r="AP112">
-        <v>264.90987423926674</v>
+        <v>324.16687445001179</v>
       </c>
     </row>
     <row r="113" spans="2:42">
@@ -22816,16 +22816,16 @@
         <v>769</v>
       </c>
       <c r="Y113" t="s">
-        <v>506</v>
+        <v>456</v>
       </c>
       <c r="Z113" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="AA113">
-        <v>0.9922931816569136</v>
+        <v>0.98602445832668828</v>
       </c>
       <c r="AB113">
-        <v>141.29166962325118</v>
+        <v>256.2182640107153</v>
       </c>
       <c r="AD113" t="s">
         <v>562</v>
@@ -22855,13 +22855,13 @@
         <v>1226</v>
       </c>
       <c r="AN113" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="AO113">
-        <v>0.98040327309339681</v>
+        <v>0.99390376443666895</v>
       </c>
       <c r="AP113">
-        <v>359.27332662105931</v>
+        <v>111.76431866107015</v>
       </c>
     </row>
     <row r="114" spans="2:42">
@@ -22926,16 +22926,16 @@
         <v>771</v>
       </c>
       <c r="Y114" t="s">
-        <v>535</v>
+        <v>470</v>
       </c>
       <c r="Z114" t="s">
-        <v>880</v>
+        <v>855</v>
       </c>
       <c r="AA114">
-        <v>0.99053483022914257</v>
+        <v>0.98274955259938535</v>
       </c>
       <c r="AB114">
-        <v>173.52811246571903</v>
+        <v>316.25820234460127</v>
       </c>
       <c r="AD114" t="s">
         <v>562</v>
@@ -22965,13 +22965,13 @@
         <v>1227</v>
       </c>
       <c r="AN114" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="AO114">
-        <v>0.99177071872011402</v>
+        <v>0.98228212315007546</v>
       </c>
       <c r="AP114">
-        <v>150.87015679790983</v>
+        <v>324.82774224861657</v>
       </c>
     </row>
     <row r="115" spans="2:42">
@@ -23036,16 +23036,16 @@
         <v>773</v>
       </c>
       <c r="Y115" t="s">
-        <v>540</v>
+        <v>491</v>
       </c>
       <c r="Z115" t="s">
-        <v>845</v>
+        <v>890</v>
       </c>
       <c r="AA115">
-        <v>0.98320360732321854</v>
+        <v>0.99368873088044474</v>
       </c>
       <c r="AB115">
-        <v>307.93386574099321</v>
+        <v>115.70660052517967</v>
       </c>
       <c r="AD115" t="s">
         <v>562</v>
@@ -23075,13 +23075,13 @@
         <v>1228</v>
       </c>
       <c r="AN115" t="s">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="AO115">
-        <v>0.9871975802659102</v>
+        <v>0.99518979370471228</v>
       </c>
       <c r="AP115">
-        <v>234.7110284583128</v>
+        <v>88.187115413608197</v>
       </c>
     </row>
     <row r="116" spans="2:42">
@@ -23146,16 +23146,16 @@
         <v>775</v>
       </c>
       <c r="Y116" t="s">
-        <v>542</v>
+        <v>492</v>
       </c>
       <c r="Z116" t="s">
-        <v>845</v>
+        <v>890</v>
       </c>
       <c r="AA116">
-        <v>0.98897406466844573</v>
+        <v>0.99323001255738197</v>
       </c>
       <c r="AB116">
-        <v>202.14214774516236</v>
+        <v>124.11643644799697</v>
       </c>
       <c r="AD116" t="s">
         <v>562</v>
@@ -23185,13 +23185,13 @@
         <v>1229</v>
       </c>
       <c r="AN116" t="s">
-        <v>850</v>
+        <v>893</v>
       </c>
       <c r="AO116">
-        <v>0.99140701799255504</v>
+        <v>0.99193701535303302</v>
       </c>
       <c r="AP116">
-        <v>157.53800346982385</v>
+        <v>147.82138519439451</v>
       </c>
     </row>
     <row r="117" spans="2:42">
@@ -23256,16 +23256,16 @@
         <v>777</v>
       </c>
       <c r="Y117" t="s">
-        <v>554</v>
+        <v>508</v>
       </c>
       <c r="Z117" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="AA117">
-        <v>0.99152145048007134</v>
+        <v>0.99148244782956252</v>
       </c>
       <c r="AB117">
-        <v>155.44007453202627</v>
+        <v>156.15512312468667</v>
       </c>
       <c r="AD117" t="s">
         <v>562</v>
@@ -23295,13 +23295,13 @@
         <v>1230</v>
       </c>
       <c r="AN117" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="AO117">
-        <v>0.98565286420409937</v>
+        <v>0.98119061265866536</v>
       </c>
       <c r="AP117">
-        <v>263.03082292484481</v>
+        <v>344.8387679244683</v>
       </c>
     </row>
     <row r="118" spans="2:42">
@@ -23366,16 +23366,16 @@
         <v>779</v>
       </c>
       <c r="Y118" t="s">
-        <v>440</v>
+        <v>530</v>
       </c>
       <c r="Z118" t="s">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="AA118">
-        <v>0.98669711903630763</v>
+        <v>0.96906520826310416</v>
       </c>
       <c r="AB118">
-        <v>243.88615100102712</v>
+        <v>567.13784850975708</v>
       </c>
       <c r="AD118" t="s">
         <v>562</v>
@@ -23405,13 +23405,13 @@
         <v>1231</v>
       </c>
       <c r="AN118" t="s">
-        <v>873</v>
+        <v>841</v>
       </c>
       <c r="AO118">
-        <v>0.98600984216520959</v>
+        <v>0.98974332571937795</v>
       </c>
       <c r="AP118">
-        <v>256.48622697115769</v>
+        <v>188.03902847807063</v>
       </c>
     </row>
     <row r="119" spans="2:42">
@@ -23476,16 +23476,16 @@
         <v>781</v>
       </c>
       <c r="Y119" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="Z119" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="AA119">
-        <v>0.98530250408542552</v>
+        <v>0.98379026718553741</v>
       </c>
       <c r="AB119">
-        <v>269.45409176719892</v>
+        <v>297.17843493181346</v>
       </c>
       <c r="AD119" t="s">
         <v>562</v>
@@ -23515,13 +23515,13 @@
         <v>1232</v>
       </c>
       <c r="AN119" t="s">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="AO119">
-        <v>0.97986124669518093</v>
+        <v>0.99413168612390446</v>
       </c>
       <c r="AP119">
-        <v>369.21047725501711</v>
+        <v>107.58575439508574</v>
       </c>
     </row>
     <row r="120" spans="2:42">
@@ -23586,16 +23586,16 @@
         <v>783</v>
       </c>
       <c r="Y120" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="Z120" t="s">
-        <v>888</v>
+        <v>848</v>
       </c>
       <c r="AA120">
-        <v>0.98165693570331325</v>
+        <v>0.98593186434108759</v>
       </c>
       <c r="AB120">
-        <v>336.28951210592464</v>
+        <v>257.91582041339416</v>
       </c>
       <c r="AD120" t="s">
         <v>562</v>
@@ -23625,13 +23625,13 @@
         <v>1233</v>
       </c>
       <c r="AN120" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="AO120">
-        <v>0.99347009078887716</v>
+        <v>0.96802468703178957</v>
       </c>
       <c r="AP120">
-        <v>119.71500220391977</v>
+        <v>586.21407108385756</v>
       </c>
     </row>
     <row r="121" spans="2:42">
@@ -23696,16 +23696,16 @@
         <v>785</v>
       </c>
       <c r="Y121" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="Z121" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="AA121">
-        <v>0.98743360691918236</v>
+        <v>0.97774932819141058</v>
       </c>
       <c r="AB121">
-        <v>230.38387314832264</v>
+        <v>407.92898315747328</v>
       </c>
       <c r="AD121" t="s">
         <v>562</v>
@@ -23735,13 +23735,13 @@
         <v>1234</v>
       </c>
       <c r="AN121" t="s">
-        <v>870</v>
+        <v>843</v>
       </c>
       <c r="AO121">
-        <v>0.98231817048454484</v>
+        <v>0.97711913570486986</v>
       </c>
       <c r="AP121">
-        <v>324.16687445001179</v>
+        <v>419.48251207738639</v>
       </c>
     </row>
     <row r="122" spans="2:42">
@@ -23806,16 +23806,16 @@
         <v>787</v>
       </c>
       <c r="Y122" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
       <c r="Z122" t="s">
-        <v>892</v>
+        <v>848</v>
       </c>
       <c r="AA122">
-        <v>0.98216618059133565</v>
+        <v>0.97689468820002234</v>
       </c>
       <c r="AB122">
-        <v>326.95335582551394</v>
+        <v>423.59738299959002</v>
       </c>
       <c r="AD122" t="s">
         <v>562</v>
@@ -23845,13 +23845,13 @@
         <v>1235</v>
       </c>
       <c r="AN122" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="AO122">
-        <v>0.99390376443666895</v>
+        <v>0.97535827976293088</v>
       </c>
       <c r="AP122">
-        <v>111.76431866107015</v>
+        <v>451.76487101293469</v>
       </c>
     </row>
     <row r="123" spans="2:42">
@@ -23916,16 +23916,16 @@
         <v>789</v>
       </c>
       <c r="Y123" t="s">
-        <v>512</v>
+        <v>469</v>
       </c>
       <c r="Z123" t="s">
-        <v>870</v>
+        <v>848</v>
       </c>
       <c r="AA123">
-        <v>0.98720259752020922</v>
+        <v>0.96097855629761675</v>
       </c>
       <c r="AB123">
-        <v>234.61904546283111</v>
+        <v>715.39313454369221</v>
       </c>
       <c r="AD123" t="s">
         <v>562</v>
@@ -23955,13 +23955,13 @@
         <v>1236</v>
       </c>
       <c r="AN123" t="s">
-        <v>873</v>
+        <v>859</v>
       </c>
       <c r="AO123">
-        <v>0.98228212315007546</v>
+        <v>0.9754113935826384</v>
       </c>
       <c r="AP123">
-        <v>324.82774224861657</v>
+        <v>450.79111765163026</v>
       </c>
     </row>
     <row r="124" spans="2:42">
@@ -24026,16 +24026,16 @@
         <v>791</v>
       </c>
       <c r="Y124" t="s">
-        <v>515</v>
+        <v>485</v>
       </c>
       <c r="Z124" t="s">
-        <v>871</v>
+        <v>843</v>
       </c>
       <c r="AA124">
-        <v>0.99047826508727854</v>
+        <v>0.97961944565164727</v>
       </c>
       <c r="AB124">
-        <v>174.56514006656096</v>
+        <v>373.64349638646644</v>
       </c>
     </row>
     <row r="125" spans="2:42">
@@ -24100,16 +24100,16 @@
         <v>793</v>
       </c>
       <c r="Y125" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="Z125" t="s">
-        <v>893</v>
+        <v>849</v>
       </c>
       <c r="AA125">
-        <v>0.99738810274021905</v>
+        <v>0.97558364374549811</v>
       </c>
       <c r="AB125">
-        <v>47.884783095983913</v>
+        <v>447.63319799920112</v>
       </c>
     </row>
     <row r="126" spans="2:42">
@@ -24174,16 +24174,16 @@
         <v>795</v>
       </c>
       <c r="Y126" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="Z126" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="AA126">
-        <v>0.99098265052846923</v>
+        <v>0.98695232420711065</v>
       </c>
       <c r="AB126">
-        <v>165.31807364473053</v>
+        <v>239.2073895363051</v>
       </c>
     </row>
     <row r="127" spans="2:42">
@@ -24248,16 +24248,16 @@
         <v>797</v>
       </c>
       <c r="Y127" t="s">
-        <v>446</v>
+        <v>537</v>
       </c>
       <c r="Z127" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="AA127">
-        <v>0.98950135873743683</v>
+        <v>0.99609138632252892</v>
       </c>
       <c r="AB127">
-        <v>192.47508981365891</v>
+        <v>71.657917420303932</v>
       </c>
     </row>
     <row r="128" spans="2:42">
@@ -24322,16 +24322,16 @@
         <v>799</v>
       </c>
       <c r="Y128" t="s">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="Z128" t="s">
-        <v>894</v>
+        <v>866</v>
       </c>
       <c r="AA128">
-        <v>0.99488206120957279</v>
+        <v>0.97457415963573191</v>
       </c>
       <c r="AB128">
-        <v>93.828877824498619</v>
+        <v>466.14040667824753</v>
       </c>
     </row>
     <row r="129" spans="2:28">
@@ -24396,16 +24396,16 @@
         <v>801</v>
       </c>
       <c r="Y129" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="Z129" t="s">
-        <v>884</v>
+        <v>840</v>
       </c>
       <c r="AA129">
-        <v>0.98929007854358664</v>
+        <v>0.98213469589758429</v>
       </c>
       <c r="AB129">
-        <v>196.34856003424409</v>
+        <v>327.53057521095576</v>
       </c>
     </row>
     <row r="130" spans="2:28">
@@ -24470,16 +24470,16 @@
         <v>803</v>
       </c>
       <c r="Y130" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="Z130" t="s">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="AA130">
-        <v>0.9692587148013998</v>
+        <v>0.98161750782838286</v>
       </c>
       <c r="AB130">
-        <v>563.59022864100291</v>
+        <v>337.01235647964734</v>
       </c>
     </row>
     <row r="131" spans="2:28">
@@ -24544,16 +24544,16 @@
         <v>805</v>
       </c>
       <c r="Y131" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="Z131" t="s">
-        <v>854</v>
+        <v>893</v>
       </c>
       <c r="AA131">
-        <v>0.99120757651401414</v>
+        <v>0.98975592846808447</v>
       </c>
       <c r="AB131">
-        <v>161.19443057640677</v>
+        <v>187.80797808511727</v>
       </c>
     </row>
     <row r="132" spans="2:28">
@@ -24618,16 +24618,16 @@
         <v>807</v>
       </c>
       <c r="Y132" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="Z132" t="s">
-        <v>886</v>
+        <v>843</v>
       </c>
       <c r="AA132">
-        <v>0.98661661227366804</v>
+        <v>0.97312873356481211</v>
       </c>
       <c r="AB132">
-        <v>245.36210831608693</v>
+        <v>492.63988464511067</v>
       </c>
     </row>
     <row r="133" spans="2:28">
@@ -24692,16 +24692,16 @@
         <v>809</v>
       </c>
       <c r="Y133" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="Z133" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="AA133">
-        <v>0.98939469221283771</v>
+        <v>0.98977266598403368</v>
       </c>
       <c r="AB133">
-        <v>194.43064276464273</v>
+        <v>187.50112362604992</v>
       </c>
     </row>
     <row r="134" spans="2:28">
@@ -24766,16 +24766,16 @@
         <v>811</v>
       </c>
       <c r="Y134" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="Z134" t="s">
-        <v>856</v>
+        <v>871</v>
       </c>
       <c r="AA134">
-        <v>0.99170776895032964</v>
+        <v>0.99537444599393454</v>
       </c>
       <c r="AB134">
-        <v>152.02423591062336</v>
+        <v>84.801823444534008</v>
       </c>
     </row>
     <row r="135" spans="2:28">
@@ -24840,16 +24840,16 @@
         <v>813</v>
       </c>
       <c r="Y135" t="s">
-        <v>546</v>
+        <v>505</v>
       </c>
       <c r="Z135" t="s">
-        <v>866</v>
+        <v>884</v>
       </c>
       <c r="AA135">
-        <v>0.99042342806455907</v>
+        <v>0.99218262773253396</v>
       </c>
       <c r="AB135">
-        <v>175.57048548308435</v>
+        <v>143.31849157021014</v>
       </c>
     </row>
     <row r="136" spans="2:28">
@@ -24914,16 +24914,16 @@
         <v>815</v>
       </c>
       <c r="Y136" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="Z136" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="AA136">
-        <v>0.99253864063271646</v>
+        <v>0.99477407524212647</v>
       </c>
       <c r="AB136">
-        <v>136.79158840019849</v>
+        <v>95.808620561014351</v>
       </c>
     </row>
     <row r="137" spans="2:28">
@@ -24988,16 +24988,16 @@
         <v>817</v>
       </c>
       <c r="Y137" t="s">
-        <v>455</v>
+        <v>555</v>
       </c>
       <c r="Z137" t="s">
-        <v>896</v>
+        <v>881</v>
       </c>
       <c r="AA137">
-        <v>0.98379026718553741</v>
+        <v>0.99340406403388481</v>
       </c>
       <c r="AB137">
-        <v>297.17843493181346</v>
+        <v>120.92549271211209</v>
       </c>
     </row>
     <row r="138" spans="2:28">
@@ -25062,16 +25062,16 @@
         <v>819</v>
       </c>
       <c r="Y138" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="Z138" t="s">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="AA138">
-        <v>0.98593186434108759</v>
+        <v>0.98669711903630763</v>
       </c>
       <c r="AB138">
-        <v>257.91582041339416</v>
+        <v>243.88615100102712</v>
       </c>
     </row>
     <row r="139" spans="2:28">
@@ -25136,16 +25136,16 @@
         <v>821</v>
       </c>
       <c r="Y139" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="Z139" t="s">
-        <v>882</v>
+        <v>853</v>
       </c>
       <c r="AA139">
-        <v>0.97774932819141058</v>
+        <v>0.98530250408542552</v>
       </c>
       <c r="AB139">
-        <v>407.92898315747328</v>
+        <v>269.45409176719892</v>
       </c>
     </row>
     <row r="140" spans="2:28">
@@ -25210,16 +25210,16 @@
         <v>823</v>
       </c>
       <c r="Y140" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="Z140" t="s">
-        <v>882</v>
+        <v>853</v>
       </c>
       <c r="AA140">
-        <v>0.97689468820002234</v>
+        <v>0.98165693570331325</v>
       </c>
       <c r="AB140">
-        <v>423.59738299959002</v>
+        <v>336.28951210592464</v>
       </c>
     </row>
     <row r="141" spans="2:28">
@@ -25284,16 +25284,16 @@
         <v>825</v>
       </c>
       <c r="Y141" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="Z141" t="s">
-        <v>882</v>
+        <v>843</v>
       </c>
       <c r="AA141">
-        <v>0.96097855629761675</v>
+        <v>0.98743360691918236</v>
       </c>
       <c r="AB141">
-        <v>715.39313454369221</v>
+        <v>230.38387314832264</v>
       </c>
     </row>
     <row r="142" spans="2:28">
@@ -25358,16 +25358,16 @@
         <v>827</v>
       </c>
       <c r="Y142" t="s">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="Z142" t="s">
-        <v>843</v>
+        <v>896</v>
       </c>
       <c r="AA142">
-        <v>0.97961944565164727</v>
+        <v>0.98216618059133565</v>
       </c>
       <c r="AB142">
-        <v>373.64349638646644</v>
+        <v>326.95335582551394</v>
       </c>
     </row>
     <row r="143" spans="2:28">
@@ -25432,16 +25432,16 @@
         <v>829</v>
       </c>
       <c r="Y143" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="Z143" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="AA143">
-        <v>0.97558364374549811</v>
+        <v>0.98720259752020922</v>
       </c>
       <c r="AB143">
-        <v>447.63319799920112</v>
+        <v>234.61904546283111</v>
       </c>
     </row>
     <row r="144" spans="2:28">
@@ -25506,16 +25506,16 @@
         <v>831</v>
       </c>
       <c r="Y144" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="Z144" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="AA144">
-        <v>0.98695232420711065</v>
+        <v>0.99047826508727854</v>
       </c>
       <c r="AB144">
-        <v>239.2073895363051</v>
+        <v>174.56514006656096</v>
       </c>
     </row>
     <row r="145" spans="2:28">
@@ -25580,16 +25580,16 @@
         <v>833</v>
       </c>
       <c r="Y145" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="Z145" t="s">
         <v>897</v>
       </c>
       <c r="AA145">
-        <v>0.99609138632252892</v>
+        <v>0.99738810274021905</v>
       </c>
       <c r="AB145">
-        <v>71.657917420303932</v>
+        <v>47.884783095983913</v>
       </c>
     </row>
     <row r="146" spans="2:28">
@@ -25654,16 +25654,16 @@
         <v>835</v>
       </c>
       <c r="Y146" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="Z146" t="s">
-        <v>873</v>
+        <v>845</v>
       </c>
       <c r="AA146">
-        <v>0.97457415963573191</v>
+        <v>0.99098265052846923</v>
       </c>
       <c r="AB146">
-        <v>466.14040667824753</v>
+        <v>165.31807364473053</v>
       </c>
     </row>
   </sheetData>
@@ -25672,7 +25672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E8E3FA-7540-4505-AA1B-89F493530825}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{784B0D07-BF27-4DCF-91A0-A5BC3B1520B9}">
   <dimension ref="B9:Z123"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -25784,7 +25784,7 @@
         <v>1339</v>
       </c>
       <c r="K11" t="s">
-        <v>1178</v>
+        <v>1218</v>
       </c>
       <c r="L11">
         <v>27.051418854318303</v>
@@ -25817,7 +25817,7 @@
         <v>1565</v>
       </c>
       <c r="X11" t="s">
-        <v>1327</v>
+        <v>1306</v>
       </c>
       <c r="Y11">
         <v>52.78875</v>
@@ -25852,7 +25852,7 @@
         <v>1341</v>
       </c>
       <c r="K12" t="s">
-        <v>1183</v>
+        <v>1160</v>
       </c>
       <c r="L12">
         <v>57.614147689498935</v>
@@ -25885,7 +25885,7 @@
         <v>1567</v>
       </c>
       <c r="X12" t="s">
-        <v>1330</v>
+        <v>1310</v>
       </c>
       <c r="Y12">
         <v>71.001750000000001</v>
@@ -25920,7 +25920,7 @@
         <v>1343</v>
       </c>
       <c r="K13" t="s">
-        <v>1206</v>
+        <v>1228</v>
       </c>
       <c r="L13">
         <v>25.242848867026897</v>
@@ -25953,7 +25953,7 @@
         <v>1569</v>
       </c>
       <c r="X13" t="s">
-        <v>1316</v>
+        <v>1334</v>
       </c>
       <c r="Y13">
         <v>24.94275</v>
@@ -25988,7 +25988,7 @@
         <v>1345</v>
       </c>
       <c r="K14" t="s">
-        <v>1133</v>
+        <v>1203</v>
       </c>
       <c r="L14">
         <v>43.902302147039038</v>
@@ -26021,7 +26021,7 @@
         <v>1571</v>
       </c>
       <c r="X14" t="s">
-        <v>1308</v>
+        <v>1321</v>
       </c>
       <c r="Y14">
         <v>17.73075</v>
@@ -26056,7 +26056,7 @@
         <v>1347</v>
       </c>
       <c r="K15" t="s">
-        <v>1134</v>
+        <v>1204</v>
       </c>
       <c r="L15">
         <v>32.44184075061812</v>
@@ -26089,7 +26089,7 @@
         <v>1573</v>
       </c>
       <c r="X15" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="Y15">
         <v>23.870999999999999</v>
@@ -26124,7 +26124,7 @@
         <v>1349</v>
       </c>
       <c r="K16" t="s">
-        <v>1158</v>
+        <v>1212</v>
       </c>
       <c r="L16">
         <v>14.992230227018849</v>
@@ -26192,7 +26192,7 @@
         <v>1351</v>
       </c>
       <c r="K17" t="s">
-        <v>1215</v>
+        <v>1178</v>
       </c>
       <c r="L17">
         <v>56.364601686534712</v>
@@ -26225,7 +26225,7 @@
         <v>1577</v>
       </c>
       <c r="X17" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="Y17">
         <v>1.7999999999999999E-2</v>
@@ -26260,7 +26260,7 @@
         <v>1353</v>
       </c>
       <c r="K18" t="s">
-        <v>1172</v>
+        <v>1145</v>
       </c>
       <c r="L18">
         <v>84.735566295985308</v>
@@ -26293,7 +26293,7 @@
         <v>1579</v>
       </c>
       <c r="X18" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="Y18">
         <v>59.504249999999999</v>
@@ -26328,7 +26328,7 @@
         <v>1355</v>
       </c>
       <c r="K19" t="s">
-        <v>1216</v>
+        <v>1179</v>
       </c>
       <c r="L19">
         <v>28.608114870958335</v>
@@ -26396,7 +26396,7 @@
         <v>1357</v>
       </c>
       <c r="K20" t="s">
-        <v>1168</v>
+        <v>1124</v>
       </c>
       <c r="L20">
         <v>86.169947952833951</v>
@@ -26429,7 +26429,7 @@
         <v>1583</v>
       </c>
       <c r="X20" t="s">
-        <v>1328</v>
+        <v>1307</v>
       </c>
       <c r="Y20">
         <v>2.29725</v>
@@ -26464,7 +26464,7 @@
         <v>1359</v>
       </c>
       <c r="K21" t="s">
-        <v>1217</v>
+        <v>1180</v>
       </c>
       <c r="L21">
         <v>135.76851915542863</v>
@@ -26497,7 +26497,7 @@
         <v>1585</v>
       </c>
       <c r="X21" t="s">
-        <v>1318</v>
+        <v>1305</v>
       </c>
       <c r="Y21">
         <v>4.3282499999999997</v>
@@ -26532,7 +26532,7 @@
         <v>1361</v>
       </c>
       <c r="K22" t="s">
-        <v>1232</v>
+        <v>1223</v>
       </c>
       <c r="L22">
         <v>75.454555795713105</v>
@@ -26565,7 +26565,7 @@
         <v>1587</v>
       </c>
       <c r="X22" t="s">
-        <v>1317</v>
+        <v>1335</v>
       </c>
       <c r="Y22">
         <v>15.962249999999999</v>
@@ -26600,7 +26600,7 @@
         <v>1363</v>
       </c>
       <c r="K23" t="s">
-        <v>1192</v>
+        <v>1128</v>
       </c>
       <c r="L23">
         <v>108.040942281193</v>
@@ -26633,7 +26633,7 @@
         <v>1589</v>
       </c>
       <c r="X23" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="Y23">
         <v>42.801749999999998</v>
@@ -26668,7 +26668,7 @@
         <v>1365</v>
       </c>
       <c r="K24" t="s">
-        <v>1179</v>
+        <v>1219</v>
       </c>
       <c r="L24">
         <v>94.096948686413384</v>
@@ -26701,7 +26701,7 @@
         <v>1591</v>
       </c>
       <c r="X24" t="s">
-        <v>1312</v>
+        <v>1329</v>
       </c>
       <c r="Y24">
         <v>99.272000000000006</v>
@@ -26736,7 +26736,7 @@
         <v>1367</v>
       </c>
       <c r="K25" t="s">
-        <v>1164</v>
+        <v>1174</v>
       </c>
       <c r="L25">
         <v>8.9494246845612864</v>
@@ -26769,7 +26769,7 @@
         <v>1593</v>
       </c>
       <c r="X25" t="s">
-        <v>1306</v>
+        <v>1327</v>
       </c>
       <c r="Y25">
         <v>91.025999999999996</v>
@@ -26804,7 +26804,7 @@
         <v>1369</v>
       </c>
       <c r="K26" t="s">
-        <v>1173</v>
+        <v>1146</v>
       </c>
       <c r="L26">
         <v>33.544698798614917</v>
@@ -26837,7 +26837,7 @@
         <v>1595</v>
       </c>
       <c r="X26" t="s">
-        <v>1331</v>
+        <v>1311</v>
       </c>
       <c r="Y26">
         <v>12.12725</v>
@@ -26872,7 +26872,7 @@
         <v>1371</v>
       </c>
       <c r="K27" t="s">
-        <v>1207</v>
+        <v>1229</v>
       </c>
       <c r="L27">
         <v>106.84696382448234</v>
@@ -26905,7 +26905,7 @@
         <v>1597</v>
       </c>
       <c r="X27" t="s">
-        <v>1307</v>
+        <v>1328</v>
       </c>
       <c r="Y27">
         <v>45.726999999999997</v>
@@ -26940,7 +26940,7 @@
         <v>1373</v>
       </c>
       <c r="K28" t="s">
-        <v>1184</v>
+        <v>1161</v>
       </c>
       <c r="L28">
         <v>52.9204127043377</v>
@@ -26973,7 +26973,7 @@
         <v>1599</v>
       </c>
       <c r="X28" t="s">
-        <v>1332</v>
+        <v>1312</v>
       </c>
       <c r="Y28">
         <v>34.919249999999998</v>
@@ -27008,7 +27008,7 @@
         <v>1375</v>
       </c>
       <c r="K29" t="s">
-        <v>1165</v>
+        <v>1175</v>
       </c>
       <c r="L29">
         <v>55.916621965246243</v>
@@ -27041,7 +27041,7 @@
         <v>1601</v>
       </c>
       <c r="X29" t="s">
-        <v>1329</v>
+        <v>1308</v>
       </c>
       <c r="Y29">
         <v>40.524250000000002</v>
@@ -27076,7 +27076,7 @@
         <v>1377</v>
       </c>
       <c r="K30" t="s">
-        <v>1193</v>
+        <v>1129</v>
       </c>
       <c r="L30">
         <v>87.443747963825231</v>
@@ -27109,7 +27109,7 @@
         <v>1603</v>
       </c>
       <c r="X30" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="Y30">
         <v>0.98775000000000002</v>
@@ -27144,7 +27144,7 @@
         <v>1379</v>
       </c>
       <c r="K31" t="s">
-        <v>1218</v>
+        <v>1181</v>
       </c>
       <c r="L31">
         <v>172.5523017705126</v>
@@ -27177,7 +27177,7 @@
         <v>1605</v>
       </c>
       <c r="X31" t="s">
-        <v>1333</v>
+        <v>1313</v>
       </c>
       <c r="Y31">
         <v>48.910499999999999</v>
@@ -27212,7 +27212,7 @@
         <v>1381</v>
       </c>
       <c r="K32" t="s">
-        <v>1135</v>
+        <v>1205</v>
       </c>
       <c r="L32">
         <v>102.98555875333584</v>
@@ -27245,7 +27245,7 @@
         <v>1607</v>
       </c>
       <c r="X32" t="s">
-        <v>1334</v>
+        <v>1314</v>
       </c>
       <c r="Y32">
         <v>36.347749999999998</v>
@@ -27280,7 +27280,7 @@
         <v>1383</v>
       </c>
       <c r="K33" t="s">
-        <v>1201</v>
+        <v>1169</v>
       </c>
       <c r="L33">
         <v>85.200664877226515</v>
@@ -27313,7 +27313,7 @@
         <v>1609</v>
       </c>
       <c r="X33" t="s">
-        <v>1313</v>
+        <v>1330</v>
       </c>
       <c r="Y33">
         <v>67.007249999999999</v>
@@ -27348,7 +27348,7 @@
         <v>1385</v>
       </c>
       <c r="K34" t="s">
-        <v>1194</v>
+        <v>1130</v>
       </c>
       <c r="L34">
         <v>177.8003763762469</v>
@@ -27381,7 +27381,7 @@
         <v>1611</v>
       </c>
       <c r="X34" t="s">
-        <v>1335</v>
+        <v>1315</v>
       </c>
       <c r="Y34">
         <v>1.5687500000000001</v>
@@ -27416,7 +27416,7 @@
         <v>1387</v>
       </c>
       <c r="K35" t="s">
-        <v>1224</v>
+        <v>1137</v>
       </c>
       <c r="L35">
         <v>65.743485434259441</v>
@@ -27484,7 +27484,7 @@
         <v>1389</v>
       </c>
       <c r="K36" t="s">
-        <v>1208</v>
+        <v>1230</v>
       </c>
       <c r="L36">
         <v>115.09990295278101</v>
@@ -27517,7 +27517,7 @@
         <v>1615</v>
       </c>
       <c r="X36" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="Y36">
         <v>47.134250000000002</v>
@@ -27552,7 +27552,7 @@
         <v>1391</v>
       </c>
       <c r="K37" t="s">
-        <v>1159</v>
+        <v>1213</v>
       </c>
       <c r="L37">
         <v>51.347810077174991</v>
@@ -27585,7 +27585,7 @@
         <v>1617</v>
       </c>
       <c r="X37" t="s">
-        <v>1310</v>
+        <v>1324</v>
       </c>
       <c r="Y37">
         <v>55.260750000000002</v>
@@ -27620,7 +27620,7 @@
         <v>1393</v>
       </c>
       <c r="K38" t="s">
-        <v>1185</v>
+        <v>1162</v>
       </c>
       <c r="L38">
         <v>39.896721906351679</v>
@@ -27653,7 +27653,7 @@
         <v>1619</v>
       </c>
       <c r="X38" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="Y38">
         <v>0.16950000000000001</v>
@@ -27688,7 +27688,7 @@
         <v>1395</v>
       </c>
       <c r="K39" t="s">
-        <v>1202</v>
+        <v>1170</v>
       </c>
       <c r="L39">
         <v>12.342304500833409</v>
@@ -27721,7 +27721,7 @@
         <v>1621</v>
       </c>
       <c r="X39" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="Y39">
         <v>39.408499999999997</v>
@@ -27756,7 +27756,7 @@
         <v>1397</v>
       </c>
       <c r="K40" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="L40">
         <v>10.648262891289743</v>
@@ -27789,7 +27789,7 @@
         <v>1623</v>
       </c>
       <c r="X40" t="s">
-        <v>1314</v>
+        <v>1331</v>
       </c>
       <c r="Y40">
         <v>45.729750000000003</v>
@@ -27824,7 +27824,7 @@
         <v>1399</v>
       </c>
       <c r="K41" t="s">
-        <v>1186</v>
+        <v>1163</v>
       </c>
       <c r="L41">
         <v>11.96428491306677</v>
@@ -27857,7 +27857,7 @@
         <v>1625</v>
       </c>
       <c r="X41" t="s">
-        <v>1309</v>
+        <v>1322</v>
       </c>
       <c r="Y41">
         <v>20.15625</v>
@@ -27892,7 +27892,7 @@
         <v>1401</v>
       </c>
       <c r="K42" t="s">
-        <v>1209</v>
+        <v>1231</v>
       </c>
       <c r="L42">
         <v>100.17368030050729</v>
@@ -27925,7 +27925,7 @@
         <v>1627</v>
       </c>
       <c r="X42" t="s">
-        <v>1311</v>
+        <v>1333</v>
       </c>
       <c r="Y42">
         <v>13.438750000000001</v>
@@ -27960,7 +27960,7 @@
         <v>1403</v>
       </c>
       <c r="K43" t="s">
-        <v>1195</v>
+        <v>1131</v>
       </c>
       <c r="L43">
         <v>140.78744799166597</v>
@@ -27993,7 +27993,7 @@
         <v>1629</v>
       </c>
       <c r="X43" t="s">
-        <v>1315</v>
+        <v>1332</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -28028,7 +28028,7 @@
         <v>1405</v>
       </c>
       <c r="K44" t="s">
-        <v>1225</v>
+        <v>1138</v>
       </c>
       <c r="L44">
         <v>95.626237386807603</v>
@@ -28061,7 +28061,7 @@
         <v>1631</v>
       </c>
       <c r="X44" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="Y44">
         <v>3.5819999999999999</v>
@@ -28096,7 +28096,7 @@
         <v>1407</v>
       </c>
       <c r="K45" t="s">
-        <v>1142</v>
+        <v>1196</v>
       </c>
       <c r="L45">
         <v>34.163999190511113</v>
@@ -28131,7 +28131,7 @@
         <v>1409</v>
       </c>
       <c r="K46" t="s">
-        <v>1203</v>
+        <v>1171</v>
       </c>
       <c r="L46">
         <v>207.1481757149796</v>
@@ -28166,7 +28166,7 @@
         <v>1411</v>
       </c>
       <c r="K47" t="s">
-        <v>1226</v>
+        <v>1139</v>
       </c>
       <c r="L47">
         <v>111.12738154265756</v>
@@ -28201,7 +28201,7 @@
         <v>1413</v>
       </c>
       <c r="K48" t="s">
-        <v>1149</v>
+        <v>1187</v>
       </c>
       <c r="L48">
         <v>98.095071240233523</v>
@@ -28236,7 +28236,7 @@
         <v>1415</v>
       </c>
       <c r="K49" t="s">
-        <v>1124</v>
+        <v>1151</v>
       </c>
       <c r="L49">
         <v>64.315635873076587</v>
@@ -28271,7 +28271,7 @@
         <v>1417</v>
       </c>
       <c r="K50" t="s">
-        <v>1150</v>
+        <v>1188</v>
       </c>
       <c r="L50">
         <v>45.702226228379438</v>
@@ -28306,7 +28306,7 @@
         <v>1419</v>
       </c>
       <c r="K51" t="s">
-        <v>1187</v>
+        <v>1164</v>
       </c>
       <c r="L51">
         <v>59.22613388284995</v>
@@ -28341,7 +28341,7 @@
         <v>1421</v>
       </c>
       <c r="K52" t="s">
-        <v>1227</v>
+        <v>1140</v>
       </c>
       <c r="L52">
         <v>66.961183738536505</v>
@@ -28376,7 +28376,7 @@
         <v>1423</v>
       </c>
       <c r="K53" t="s">
-        <v>1169</v>
+        <v>1125</v>
       </c>
       <c r="L53">
         <v>44.273024128052612</v>
@@ -28411,7 +28411,7 @@
         <v>1425</v>
       </c>
       <c r="K54" t="s">
-        <v>1180</v>
+        <v>1220</v>
       </c>
       <c r="L54">
         <v>46.793995714201756</v>
@@ -28446,7 +28446,7 @@
         <v>1427</v>
       </c>
       <c r="K55" t="s">
-        <v>1210</v>
+        <v>1232</v>
       </c>
       <c r="L55">
         <v>59.530532128881013</v>
@@ -28481,7 +28481,7 @@
         <v>1429</v>
       </c>
       <c r="K56" t="s">
-        <v>1211</v>
+        <v>1233</v>
       </c>
       <c r="L56">
         <v>89.411053786052506</v>
@@ -28516,7 +28516,7 @@
         <v>1431</v>
       </c>
       <c r="K57" t="s">
-        <v>1212</v>
+        <v>1234</v>
       </c>
       <c r="L57">
         <v>108.09584041406336</v>
@@ -28551,7 +28551,7 @@
         <v>1433</v>
       </c>
       <c r="K58" t="s">
-        <v>1137</v>
+        <v>1207</v>
       </c>
       <c r="L58">
         <v>91.237739856046062</v>
@@ -28586,7 +28586,7 @@
         <v>1435</v>
       </c>
       <c r="K59" t="s">
-        <v>1188</v>
+        <v>1165</v>
       </c>
       <c r="L59">
         <v>192.9650320730417</v>
@@ -28621,7 +28621,7 @@
         <v>1437</v>
       </c>
       <c r="K60" t="s">
-        <v>1151</v>
+        <v>1189</v>
       </c>
       <c r="L60">
         <v>25.232461853069559</v>
@@ -28656,7 +28656,7 @@
         <v>1439</v>
       </c>
       <c r="K61" t="s">
-        <v>1125</v>
+        <v>1152</v>
       </c>
       <c r="L61">
         <v>39.902969803255665</v>
@@ -28691,7 +28691,7 @@
         <v>1441</v>
       </c>
       <c r="K62" t="s">
-        <v>1138</v>
+        <v>1208</v>
       </c>
       <c r="L62">
         <v>39.915995812987873</v>
@@ -28726,7 +28726,7 @@
         <v>1443</v>
       </c>
       <c r="K63" t="s">
-        <v>1204</v>
+        <v>1172</v>
       </c>
       <c r="L63">
         <v>34.696565986692178</v>
@@ -28761,7 +28761,7 @@
         <v>1445</v>
       </c>
       <c r="K64" t="s">
-        <v>1233</v>
+        <v>1224</v>
       </c>
       <c r="L64">
         <v>48.227180082759602</v>
@@ -28796,7 +28796,7 @@
         <v>1447</v>
       </c>
       <c r="K65" t="s">
-        <v>1152</v>
+        <v>1190</v>
       </c>
       <c r="L65">
         <v>64.191891810077777</v>
@@ -28831,7 +28831,7 @@
         <v>1449</v>
       </c>
       <c r="K66" t="s">
-        <v>1181</v>
+        <v>1221</v>
       </c>
       <c r="L66">
         <v>80.212558918950478</v>
@@ -28866,7 +28866,7 @@
         <v>1451</v>
       </c>
       <c r="K67" t="s">
-        <v>1196</v>
+        <v>1132</v>
       </c>
       <c r="L67">
         <v>144.2227931240181</v>
@@ -28901,7 +28901,7 @@
         <v>1453</v>
       </c>
       <c r="K68" t="s">
-        <v>1160</v>
+        <v>1214</v>
       </c>
       <c r="L68">
         <v>204.53213654986922</v>
@@ -28936,7 +28936,7 @@
         <v>1455</v>
       </c>
       <c r="K69" t="s">
-        <v>1126</v>
+        <v>1153</v>
       </c>
       <c r="L69">
         <v>72.404673370923575</v>
@@ -28971,7 +28971,7 @@
         <v>1457</v>
       </c>
       <c r="K70" t="s">
-        <v>1166</v>
+        <v>1176</v>
       </c>
       <c r="L70">
         <v>64.954594485891391</v>
@@ -29006,7 +29006,7 @@
         <v>1459</v>
       </c>
       <c r="K71" t="s">
-        <v>1182</v>
+        <v>1222</v>
       </c>
       <c r="L71">
         <v>61.916146181403967</v>
@@ -29041,7 +29041,7 @@
         <v>1461</v>
       </c>
       <c r="K72" t="s">
-        <v>1174</v>
+        <v>1147</v>
       </c>
       <c r="L72">
         <v>53.406412652926484</v>
@@ -29076,7 +29076,7 @@
         <v>1463</v>
       </c>
       <c r="K73" t="s">
-        <v>1175</v>
+        <v>1148</v>
       </c>
       <c r="L73">
         <v>37.750501639222641</v>
@@ -29111,7 +29111,7 @@
         <v>1465</v>
       </c>
       <c r="K74" t="s">
-        <v>1143</v>
+        <v>1197</v>
       </c>
       <c r="L74">
         <v>48.128176812360053</v>
@@ -29146,7 +29146,7 @@
         <v>1467</v>
       </c>
       <c r="K75" t="s">
-        <v>1161</v>
+        <v>1215</v>
       </c>
       <c r="L75">
         <v>35.264260528801714</v>
@@ -29181,7 +29181,7 @@
         <v>1469</v>
       </c>
       <c r="K76" t="s">
-        <v>1144</v>
+        <v>1198</v>
       </c>
       <c r="L76">
         <v>48.935077389045837</v>
@@ -29216,7 +29216,7 @@
         <v>1471</v>
       </c>
       <c r="K77" t="s">
-        <v>1127</v>
+        <v>1154</v>
       </c>
       <c r="L77">
         <v>8.0094170122860895</v>
@@ -29251,7 +29251,7 @@
         <v>1473</v>
       </c>
       <c r="K78" t="s">
-        <v>1234</v>
+        <v>1225</v>
       </c>
       <c r="L78">
         <v>109.65079318086688</v>
@@ -29286,7 +29286,7 @@
         <v>1475</v>
       </c>
       <c r="K79" t="s">
-        <v>1176</v>
+        <v>1149</v>
       </c>
       <c r="L79">
         <v>77.803564600712548</v>
@@ -29321,7 +29321,7 @@
         <v>1477</v>
       </c>
       <c r="K80" t="s">
-        <v>1139</v>
+        <v>1209</v>
       </c>
       <c r="L80">
         <v>67.474115268645178</v>
@@ -29356,7 +29356,7 @@
         <v>1479</v>
       </c>
       <c r="K81" t="s">
-        <v>1128</v>
+        <v>1155</v>
       </c>
       <c r="L81">
         <v>65.312013184050656</v>
@@ -29391,7 +29391,7 @@
         <v>1481</v>
       </c>
       <c r="K82" t="s">
-        <v>1219</v>
+        <v>1182</v>
       </c>
       <c r="L82">
         <v>75.218591396116096</v>
@@ -29426,7 +29426,7 @@
         <v>1483</v>
       </c>
       <c r="K83" t="s">
-        <v>1153</v>
+        <v>1191</v>
       </c>
       <c r="L83">
         <v>17.521750000000001</v>
@@ -29461,7 +29461,7 @@
         <v>1485</v>
       </c>
       <c r="K84" t="s">
-        <v>1220</v>
+        <v>1183</v>
       </c>
       <c r="L84">
         <v>52.234770000197621</v>
@@ -29496,7 +29496,7 @@
         <v>1487</v>
       </c>
       <c r="K85" t="s">
-        <v>1162</v>
+        <v>1216</v>
       </c>
       <c r="L85">
         <v>45.76084342305311</v>
@@ -29531,7 +29531,7 @@
         <v>1489</v>
       </c>
       <c r="K86" t="s">
-        <v>1129</v>
+        <v>1156</v>
       </c>
       <c r="L86">
         <v>49.108938806553653</v>
@@ -29566,7 +29566,7 @@
         <v>1491</v>
       </c>
       <c r="K87" t="s">
-        <v>1154</v>
+        <v>1192</v>
       </c>
       <c r="L87">
         <v>26.261957058240878</v>
@@ -29601,7 +29601,7 @@
         <v>1493</v>
       </c>
       <c r="K88" t="s">
-        <v>1221</v>
+        <v>1184</v>
       </c>
       <c r="L88">
         <v>13.244256296686441</v>
@@ -29636,7 +29636,7 @@
         <v>1495</v>
       </c>
       <c r="K89" t="s">
-        <v>1222</v>
+        <v>1185</v>
       </c>
       <c r="L89">
         <v>26.625616712501689</v>
@@ -29671,7 +29671,7 @@
         <v>1497</v>
       </c>
       <c r="K90" t="s">
-        <v>1170</v>
+        <v>1126</v>
       </c>
       <c r="L90">
         <v>49.153745052732859</v>
@@ -29706,7 +29706,7 @@
         <v>1499</v>
       </c>
       <c r="K91" t="s">
-        <v>1197</v>
+        <v>1133</v>
       </c>
       <c r="L91">
         <v>15.55402548304518</v>
@@ -29741,7 +29741,7 @@
         <v>1501</v>
       </c>
       <c r="K92" t="s">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="L92">
         <v>62.003939746896343</v>
@@ -29776,7 +29776,7 @@
         <v>1503</v>
       </c>
       <c r="K93" t="s">
-        <v>1145</v>
+        <v>1199</v>
       </c>
       <c r="L93">
         <v>16.014965255639893</v>
@@ -29811,7 +29811,7 @@
         <v>1505</v>
       </c>
       <c r="K94" t="s">
-        <v>1155</v>
+        <v>1193</v>
       </c>
       <c r="L94">
         <v>38.584000000000003</v>
@@ -29846,7 +29846,7 @@
         <v>1507</v>
       </c>
       <c r="K95" t="s">
-        <v>1198</v>
+        <v>1134</v>
       </c>
       <c r="L95">
         <v>140.43602248182191</v>
@@ -29881,7 +29881,7 @@
         <v>1509</v>
       </c>
       <c r="K96" t="s">
-        <v>1199</v>
+        <v>1135</v>
       </c>
       <c r="L96">
         <v>150.99747268719702</v>
@@ -29916,7 +29916,7 @@
         <v>1511</v>
       </c>
       <c r="K97" t="s">
-        <v>1213</v>
+        <v>1235</v>
       </c>
       <c r="L97">
         <v>44.73673083293798</v>
@@ -29951,7 +29951,7 @@
         <v>1513</v>
       </c>
       <c r="K98" t="s">
-        <v>1200</v>
+        <v>1136</v>
       </c>
       <c r="L98">
         <v>226.25148836074212</v>
@@ -29986,7 +29986,7 @@
         <v>1515</v>
       </c>
       <c r="K99" t="s">
-        <v>1156</v>
+        <v>1194</v>
       </c>
       <c r="L99">
         <v>18.646473949300262</v>
@@ -30021,7 +30021,7 @@
         <v>1517</v>
       </c>
       <c r="K100" t="s">
-        <v>1189</v>
+        <v>1166</v>
       </c>
       <c r="L100">
         <v>26.04488435253138</v>
@@ -30056,7 +30056,7 @@
         <v>1519</v>
       </c>
       <c r="K101" t="s">
-        <v>1177</v>
+        <v>1150</v>
       </c>
       <c r="L101">
         <v>90.393333069959539</v>
@@ -30091,7 +30091,7 @@
         <v>1521</v>
       </c>
       <c r="K102" t="s">
-        <v>1228</v>
+        <v>1141</v>
       </c>
       <c r="L102">
         <v>113.2451692674213</v>
@@ -30126,7 +30126,7 @@
         <v>1523</v>
       </c>
       <c r="K103" t="s">
-        <v>1205</v>
+        <v>1173</v>
       </c>
       <c r="L103">
         <v>45.474002071914207</v>
@@ -30161,7 +30161,7 @@
         <v>1525</v>
       </c>
       <c r="K104" t="s">
-        <v>1130</v>
+        <v>1157</v>
       </c>
       <c r="L104">
         <v>101.1351044976128</v>
@@ -30196,7 +30196,7 @@
         <v>1527</v>
       </c>
       <c r="K105" t="s">
-        <v>1229</v>
+        <v>1142</v>
       </c>
       <c r="L105">
         <v>48.32858989272242</v>
@@ -30231,7 +30231,7 @@
         <v>1529</v>
       </c>
       <c r="K106" t="s">
-        <v>1230</v>
+        <v>1143</v>
       </c>
       <c r="L106">
         <v>139.37189500220191</v>
@@ -30266,7 +30266,7 @@
         <v>1531</v>
       </c>
       <c r="K107" t="s">
-        <v>1131</v>
+        <v>1158</v>
       </c>
       <c r="L107">
         <v>61.671957239760111</v>
@@ -30301,7 +30301,7 @@
         <v>1533</v>
       </c>
       <c r="K108" t="s">
-        <v>1140</v>
+        <v>1210</v>
       </c>
       <c r="L108">
         <v>105.33147698141694</v>
@@ -30336,7 +30336,7 @@
         <v>1535</v>
       </c>
       <c r="K109" t="s">
-        <v>1235</v>
+        <v>1226</v>
       </c>
       <c r="L109">
         <v>36.210317598354067</v>
@@ -30371,7 +30371,7 @@
         <v>1537</v>
       </c>
       <c r="K110" t="s">
-        <v>1141</v>
+        <v>1211</v>
       </c>
       <c r="L110">
         <v>90.092175297443433</v>
@@ -30406,7 +30406,7 @@
         <v>1539</v>
       </c>
       <c r="K111" t="s">
-        <v>1214</v>
+        <v>1236</v>
       </c>
       <c r="L111">
         <v>110.96409224017792</v>
@@ -30441,7 +30441,7 @@
         <v>1541</v>
       </c>
       <c r="K112" t="s">
-        <v>1190</v>
+        <v>1167</v>
       </c>
       <c r="L112">
         <v>113.43792605984484</v>
@@ -30476,7 +30476,7 @@
         <v>1543</v>
       </c>
       <c r="K113" t="s">
-        <v>1146</v>
+        <v>1200</v>
       </c>
       <c r="L113">
         <v>31.78765414876472</v>
@@ -30511,7 +30511,7 @@
         <v>1545</v>
       </c>
       <c r="K114" t="s">
-        <v>1236</v>
+        <v>1227</v>
       </c>
       <c r="L114">
         <v>71.274548031134074</v>
@@ -30546,7 +30546,7 @@
         <v>1547</v>
       </c>
       <c r="K115" t="s">
-        <v>1132</v>
+        <v>1159</v>
       </c>
       <c r="L115">
         <v>96.887432705643064</v>
@@ -30581,7 +30581,7 @@
         <v>1549</v>
       </c>
       <c r="K116" t="s">
-        <v>1231</v>
+        <v>1144</v>
       </c>
       <c r="L116">
         <v>66.898902254497202</v>
@@ -30616,7 +30616,7 @@
         <v>1551</v>
       </c>
       <c r="K117" t="s">
-        <v>1171</v>
+        <v>1127</v>
       </c>
       <c r="L117">
         <v>114.06234142107614</v>
@@ -30651,7 +30651,7 @@
         <v>1553</v>
       </c>
       <c r="K118" t="s">
-        <v>1147</v>
+        <v>1201</v>
       </c>
       <c r="L118">
         <v>51.576115979506419</v>
@@ -30686,7 +30686,7 @@
         <v>1555</v>
       </c>
       <c r="K119" t="s">
-        <v>1157</v>
+        <v>1195</v>
       </c>
       <c r="L119">
         <v>41.324901461177753</v>
@@ -30721,7 +30721,7 @@
         <v>1557</v>
       </c>
       <c r="K120" t="s">
-        <v>1163</v>
+        <v>1217</v>
       </c>
       <c r="L120">
         <v>38.777240522327702</v>
@@ -30756,7 +30756,7 @@
         <v>1559</v>
       </c>
       <c r="K121" t="s">
-        <v>1223</v>
+        <v>1186</v>
       </c>
       <c r="L121">
         <v>36.792797269437031</v>
@@ -30791,7 +30791,7 @@
         <v>1561</v>
       </c>
       <c r="K122" t="s">
-        <v>1148</v>
+        <v>1202</v>
       </c>
       <c r="L122">
         <v>30.189135355473383</v>
@@ -30826,7 +30826,7 @@
         <v>1563</v>
       </c>
       <c r="K123" t="s">
-        <v>1191</v>
+        <v>1168</v>
       </c>
       <c r="L123">
         <v>50.047283123236681</v>
@@ -30841,7 +30841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8392DEF-D09C-4059-A594-2A447455FFBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D49D7E-7664-4C1E-9483-602F0F9E28A3}">
   <dimension ref="B9:Y151"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -35661,7 +35661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CCB0A8-A53A-4506-82D9-9BA49636B908}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEEC3B71-FF41-4040-934B-297D067F9E44}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CHN_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan60\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88AB956-5AA1-4B61-912D-3975EF50FF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1287D6B-0CD9-4C96-BCCF-4484C49FC88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1755,18 +1755,162 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_CHN_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_125</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 125</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_131</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 131</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_122</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 122</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_133</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 133</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_CHN_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_CHN_011</t>
   </si>
   <si>
@@ -1815,6 +1959,282 @@
     <t>connecting solar to buses in cluster 119</t>
   </si>
   <si>
+    <t>distr_solelc_spv_CHN_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_124</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 124</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_127</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 127</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_129</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 129</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_135</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 135</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_120</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 120</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_136</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 136</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_121</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 121</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_123</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 123</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_CHN_005</t>
   </si>
   <si>
@@ -1869,66 +2289,6 @@
     <t>connecting solar to buses in cluster 132</t>
   </si>
   <si>
-    <t>distr_solelc_spv_CHN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_122</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 122</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_133</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 133</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_CHN_004</t>
   </si>
   <si>
@@ -1989,112 +2349,40 @@
     <t>connecting solar to buses in cluster 134</t>
   </si>
   <si>
-    <t>distr_solelc_spv_CHN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_135</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 135</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_120</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 120</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_136</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 136</t>
+    <t>distr_solelc_spv_CHN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_CHN_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
   </si>
   <si>
     <t>distr_solelc_spv_CHN_002</t>
@@ -2175,240 +2463,6 @@
     <t>connecting solar to buses in cluster 130</t>
   </si>
   <si>
-    <t>distr_solelc_spv_CHN_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_127</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 127</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_129</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 129</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_121</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 121</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_123</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 123</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_124</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 124</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_CHN_031</t>
   </si>
   <si>
@@ -2469,60 +2523,6 @@
     <t>connecting solar to buses in cluster 126</t>
   </si>
   <si>
-    <t>distr_solelc_spv_CHN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_125</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 125</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_CHN_131</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 131</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_CHN_016</t>
   </si>
   <si>
@@ -2583,183 +2583,267 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Luohe_CHN</t>
+  </si>
+  <si>
+    <t>e_Rizhao_CHN</t>
+  </si>
+  <si>
+    <t>e_Yuanquan_CHN</t>
+  </si>
+  <si>
+    <t>e_Nantong_CHN</t>
+  </si>
+  <si>
+    <t>e_Hejin_CHN</t>
+  </si>
+  <si>
+    <t>e_Harbin_CHN</t>
+  </si>
+  <si>
+    <t>e_Anshun_CHN</t>
+  </si>
+  <si>
+    <t>e_CHN44p7N89p1E_CHN</t>
+  </si>
+  <si>
+    <t>e_Putian_CHN</t>
+  </si>
+  <si>
+    <t>e_Jingling_CHN</t>
+  </si>
+  <si>
+    <t>e_Fuzhou_CHN</t>
+  </si>
+  <si>
+    <t>e_Yangzhou_CHN</t>
+  </si>
+  <si>
+    <t>e_Tongshan_CHN</t>
+  </si>
+  <si>
+    <t>e_Yakeshi_CHN</t>
+  </si>
+  <si>
+    <t>e_Linyi_CHN</t>
+  </si>
+  <si>
+    <t>e_Chongqing_CHN</t>
+  </si>
+  <si>
+    <t>e_Kuqa_CHN</t>
+  </si>
+  <si>
+    <t>e_Wulan_CHN</t>
+  </si>
+  <si>
+    <t>e_Yangjiang_CHN</t>
+  </si>
+  <si>
+    <t>e_Xichang_CHN</t>
+  </si>
+  <si>
+    <t>e_Mianyang_CHN</t>
+  </si>
+  <si>
+    <t>e_Sizhan_CHN</t>
+  </si>
+  <si>
+    <t>e_Wuan_CHN</t>
+  </si>
+  <si>
     <t>e_Anshan_CHN</t>
   </si>
   <si>
-    <t>e_Harbin_CHN</t>
-  </si>
-  <si>
     <t>e_Shahezhai_CHN</t>
   </si>
   <si>
     <t>e_ZhongdongShequ_CHN</t>
   </si>
   <si>
-    <t>e_CHN44p7N89p1E_CHN</t>
-  </si>
-  <si>
     <t>e_Yingchuan_CHN</t>
   </si>
   <si>
     <t>e_CHN44p4N121p8E_CHN</t>
   </si>
   <si>
+    <t>e_Nanjing_CHN</t>
+  </si>
+  <si>
+    <t>e_Sanhe_CHN</t>
+  </si>
+  <si>
+    <t>e_Liuzhou_CHN</t>
+  </si>
+  <si>
+    <t>e_Fangchenggang_CHN</t>
+  </si>
+  <si>
+    <t>e_CHN45p9N129p3E_CHN</t>
+  </si>
+  <si>
+    <t>e_Xiaoyi_CHN</t>
+  </si>
+  <si>
+    <t>e_CHN44p2N116p5E_CHN</t>
+  </si>
+  <si>
+    <t>e_Shijiazhuang_CHN</t>
+  </si>
+  <si>
+    <t>e_Hohhot_CHN</t>
+  </si>
+  <si>
+    <t>e_Beichengqu_CHN</t>
+  </si>
+  <si>
+    <t>e_Yanggezhuang_CHN</t>
+  </si>
+  <si>
+    <t>e_Liaoyang_CHN</t>
+  </si>
+  <si>
+    <t>e_Anqing_CHN</t>
+  </si>
+  <si>
+    <t>e_Manlin_CHN</t>
+  </si>
+  <si>
+    <t>e_Ningde_CHN</t>
+  </si>
+  <si>
+    <t>e_Zouping_CHN</t>
+  </si>
+  <si>
+    <t>e_Wuhan_CHN</t>
+  </si>
+  <si>
+    <t>e_Changzhou_CHN</t>
+  </si>
+  <si>
     <t>e_Yiyang_CHN</t>
   </si>
   <si>
-    <t>e_Chongqing_CHN</t>
-  </si>
-  <si>
-    <t>e_Kuqa_CHN</t>
-  </si>
-  <si>
-    <t>e_CHN45p9N129p3E_CHN</t>
-  </si>
-  <si>
     <t>e_Shaoguan_CHN</t>
   </si>
   <si>
-    <t>e_Rizhao_CHN</t>
-  </si>
-  <si>
-    <t>e_Wuan_CHN</t>
-  </si>
-  <si>
-    <t>e_Yakeshi_CHN</t>
-  </si>
-  <si>
-    <t>e_Linyi_CHN</t>
-  </si>
-  <si>
-    <t>e_Wulan_CHN</t>
-  </si>
-  <si>
-    <t>e_Yangjiang_CHN</t>
-  </si>
-  <si>
-    <t>e_Xichang_CHN</t>
-  </si>
-  <si>
-    <t>e_Mianyang_CHN</t>
-  </si>
-  <si>
-    <t>e_Sizhan_CHN</t>
-  </si>
-  <si>
     <t>e_Tianjin_CHN</t>
   </si>
   <si>
     <t>e_Hangzhou_CHN</t>
   </si>
   <si>
-    <t>e_Fangchenggang_CHN</t>
-  </si>
-  <si>
-    <t>e_Hohhot_CHN</t>
-  </si>
-  <si>
     <t>e_Qabqa_CHN</t>
   </si>
   <si>
-    <t>e_Yuanquan_CHN</t>
-  </si>
-  <si>
-    <t>e_CHN44p2N116p5E_CHN</t>
-  </si>
-  <si>
     <t>e_Tongling_CHN</t>
   </si>
   <si>
-    <t>e_Shijiazhuang_CHN</t>
-  </si>
-  <si>
-    <t>e_Sanhe_CHN</t>
-  </si>
-  <si>
-    <t>e_Liuzhou_CHN</t>
-  </si>
-  <si>
-    <t>e_Jingling_CHN</t>
-  </si>
-  <si>
-    <t>e_Beichengqu_CHN</t>
-  </si>
-  <si>
-    <t>e_Yanggezhuang_CHN</t>
-  </si>
-  <si>
-    <t>e_Liaoyang_CHN</t>
-  </si>
-  <si>
-    <t>e_Anqing_CHN</t>
-  </si>
-  <si>
-    <t>e_Manlin_CHN</t>
-  </si>
-  <si>
-    <t>e_Luohe_CHN</t>
-  </si>
-  <si>
-    <t>e_Ningde_CHN</t>
-  </si>
-  <si>
-    <t>e_Wuhan_CHN</t>
+    <t>e_Shanghai_CHN</t>
+  </si>
+  <si>
+    <t>e_Xiaoxita_CHN</t>
   </si>
   <si>
     <t>e_Jinbi_CHN</t>
   </si>
   <si>
-    <t>e_Tongshan_CHN</t>
-  </si>
-  <si>
-    <t>e_Nantong_CHN</t>
-  </si>
-  <si>
-    <t>e_Hejin_CHN</t>
-  </si>
-  <si>
-    <t>e_Fuzhou_CHN</t>
-  </si>
-  <si>
-    <t>e_Xiaoyi_CHN</t>
-  </si>
-  <si>
-    <t>e_Changzhou_CHN</t>
-  </si>
-  <si>
-    <t>e_Shanghai_CHN</t>
-  </si>
-  <si>
-    <t>e_Xiaoxita_CHN</t>
-  </si>
-  <si>
-    <t>e_Nanjing_CHN</t>
-  </si>
-  <si>
-    <t>e_Zouping_CHN</t>
-  </si>
-  <si>
     <t>e_Dayan_CHN</t>
   </si>
   <si>
     <t>e_Tangshan_CHN</t>
   </si>
   <si>
-    <t>e_Anshun_CHN</t>
-  </si>
-  <si>
-    <t>e_Putian_CHN</t>
-  </si>
-  <si>
-    <t>e_Yangzhou_CHN</t>
-  </si>
-  <si>
     <t>e_Bayi_CHN</t>
   </si>
   <si>
     <t>e_Yicheng_CHN</t>
   </si>
   <si>
+    <t>distr_wonelc_won_CHN_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_071</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_076</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_094</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_097</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_105</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_093</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 93</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_CHN_010</t>
   </si>
   <si>
@@ -2784,6 +2868,234 @@
     <t>connecting wind onshore to buses in cluster 107</t>
   </si>
   <si>
+    <t>distr_wonelc_won_CHN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_072</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_074</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_078</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_079</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_111</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_073</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_077</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_084</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_089</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_109</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_099</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_104</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_092</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_095</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_096</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_106</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_083</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_103</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_108</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_112</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 112</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_CHN_013</t>
   </si>
   <si>
@@ -2838,52 +3150,82 @@
     <t>connecting wind onshore to buses in cluster 88</t>
   </si>
   <si>
-    <t>distr_wonelc_won_CHN_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_092</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_095</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_096</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_106</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 106</t>
+    <t>distr_wonelc_won_CHN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_070</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_098</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_100</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_082</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 82</t>
   </si>
   <si>
     <t>distr_wonelc_won_CHN_008</t>
@@ -2922,60 +3264,6 @@
     <t>connecting wind onshore to buses in cluster 91</t>
   </si>
   <si>
-    <t>distr_wonelc_won_CHN_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_071</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_076</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_094</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_097</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_105</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 105</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_CHN_002</t>
   </si>
   <si>
@@ -3030,262 +3318,88 @@
     <t>connecting wind onshore to buses in cluster 113</t>
   </si>
   <si>
-    <t>distr_wonelc_won_CHN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_093</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_082</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_072</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_074</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_078</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_079</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_111</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_073</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_077</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_084</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_089</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_109</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_083</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_103</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_108</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_112</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_070</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_098</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_100</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 100</t>
+    <t>distr_wonelc_won_CHN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_087</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_CHN_101</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 101</t>
   </si>
   <si>
     <t>distr_wonelc_won_CHN_006</t>
@@ -3324,118 +3438,46 @@
     <t>connecting wind onshore to buses in cluster 110</t>
   </si>
   <si>
-    <t>distr_wonelc_won_CHN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_099</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_104</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_087</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_CHN_101</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 101</t>
+    <t>elc_won_CHN_039</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_051</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_059</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_067</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_071</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_076</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_094</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_097</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_105</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_023</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_029</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_036</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_053</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_093</t>
   </si>
   <si>
     <t>elc_won_CHN_010</t>
@@ -3450,6 +3492,120 @@
     <t>elc_won_CHN_107</t>
   </si>
   <si>
+    <t>elc_won_CHN_007</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_009</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_011</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_021</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_072</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_074</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_078</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_079</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_111</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_038</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_040</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_050</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_055</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_073</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_077</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_084</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_089</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_109</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_012</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_054</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_068</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_099</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_104</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_025</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_034</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_037</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_042</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_092</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_095</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_096</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_106</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_035</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_064</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_066</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_083</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_103</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_108</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_112</t>
+  </si>
+  <si>
     <t>elc_won_CHN_013</t>
   </si>
   <si>
@@ -3477,28 +3633,43 @@
     <t>elc_won_CHN_088</t>
   </si>
   <si>
-    <t>elc_won_CHN_025</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_034</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_037</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_042</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_092</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_095</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_096</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_106</t>
+    <t>elc_won_CHN_004</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_005</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_022</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_030</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_048</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_052</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_070</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_098</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_100</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_015</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_019</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_060</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_082</t>
   </si>
   <si>
     <t>elc_won_CHN_008</t>
@@ -3519,33 +3690,6 @@
     <t>elc_won_CHN_091</t>
   </si>
   <si>
-    <t>elc_won_CHN_039</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_051</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_059</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_067</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_071</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_076</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_094</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_097</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_105</t>
-  </si>
-  <si>
     <t>elc_won_CHN_002</t>
   </si>
   <si>
@@ -3573,133 +3717,46 @@
     <t>elc_won_CHN_113</t>
   </si>
   <si>
-    <t>elc_won_CHN_023</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_029</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_036</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_053</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_093</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_015</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_019</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_060</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_082</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_007</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_009</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_011</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_021</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_072</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_074</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_078</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_079</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_111</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_038</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_040</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_050</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_055</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_073</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_077</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_084</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_089</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_109</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_035</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_064</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_066</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_083</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_103</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_108</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_112</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_004</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_005</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_022</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_030</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_048</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_052</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_070</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_098</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_100</t>
+    <t>elc_won_CHN_001</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_014</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_044</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_056</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_061</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_003</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_017</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_026</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_032</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_045</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_046</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_047</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_087</t>
+  </si>
+  <si>
+    <t>elc_won_CHN_101</t>
   </si>
   <si>
     <t>elc_won_CHN_006</t>
@@ -3720,61 +3777,16 @@
     <t>elc_won_CHN_110</t>
   </si>
   <si>
-    <t>elc_won_CHN_001</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_014</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_044</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_056</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_061</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_012</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_054</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_068</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_099</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_104</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_003</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_017</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_026</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_032</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_045</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_046</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_047</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_087</t>
-  </si>
-  <si>
-    <t>elc_won_CHN_101</t>
+    <t>distr_wofelc_wof_CHN_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
   </si>
   <si>
     <t>distr_wofelc_wof_CHN_011</t>
@@ -3783,6 +3795,144 @@
     <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_CHN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_CHN_001</t>
   </si>
   <si>
@@ -3801,94 +3951,28 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_CHN_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
+    <t>distr_wofelc_wof_CHN_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_CHN_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
   </si>
   <si>
     <t>distr_wofelc_wof_CHN_027</t>
@@ -3897,93 +3981,84 @@
     <t>connecting wind offshore to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_CHN_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_CHN_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
+    <t>elc_wof_CHN_029</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_032</t>
   </si>
   <si>
     <t>elc_wof_CHN_011</t>
   </si>
   <si>
+    <t>elc_wof_CHN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_016</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_018</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_021</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_022</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_024</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_004</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_031</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_012</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_014</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_023</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_005</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_008</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_020</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_028</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_013</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_015</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_017</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_006</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_009</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_025</t>
+  </si>
+  <si>
     <t>elc_wof_CHN_001</t>
   </si>
   <si>
@@ -3993,94 +4068,19 @@
     <t>elc_wof_CHN_019</t>
   </si>
   <si>
-    <t>elc_wof_CHN_029</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_016</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_018</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_021</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_022</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_024</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_005</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_007</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_008</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_020</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_028</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_004</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_031</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_013</t>
+    <t>elc_wof_CHN_030</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_033</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_026</t>
+  </si>
+  <si>
+    <t>elc_wof_CHN_034</t>
   </si>
   <si>
     <t>elc_wof_CHN_027</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_026</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_034</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_015</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_017</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_014</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_023</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_030</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_033</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_032</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_012</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_006</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_009</t>
-  </si>
-  <si>
-    <t>elc_wof_CHN_025</t>
   </si>
   <si>
     <t>e_won_CHN_001</t>
@@ -10134,7 +10134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194A03C1-1F29-4B4E-9021-2234FCFF78A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBA58CB-6CBC-4DCC-9405-3F96B1D05E4B}">
   <dimension ref="B9:BD146"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10372,16 +10372,16 @@
         <v>563</v>
       </c>
       <c r="Y11" t="s">
-        <v>430</v>
+        <v>502</v>
       </c>
       <c r="Z11" t="s">
         <v>839</v>
       </c>
       <c r="AA11">
-        <v>0.9925555661059412</v>
+        <v>0.99142410630444711</v>
       </c>
       <c r="AB11">
-        <v>136.48128805774428</v>
+        <v>157.22471775180347</v>
       </c>
       <c r="AD11" t="s">
         <v>562</v>
@@ -10411,13 +10411,13 @@
         <v>1124</v>
       </c>
       <c r="AN11" t="s">
-        <v>840</v>
+        <v>856</v>
       </c>
       <c r="AO11">
-        <v>0.96363263183226566</v>
+        <v>0.99430130634228164</v>
       </c>
       <c r="AP11">
-        <v>666.73508307513055</v>
+        <v>104.47605039150224</v>
       </c>
       <c r="AR11" t="s">
         <v>562</v>
@@ -10447,13 +10447,13 @@
         <v>1305</v>
       </c>
       <c r="BB11" t="s">
-        <v>856</v>
+        <v>881</v>
       </c>
       <c r="BC11">
-        <v>0.90777469227524876</v>
+        <v>0.98475443499607906</v>
       </c>
       <c r="BD11">
-        <v>1208.8428425634561</v>
+        <v>601.9858707809102</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10518,16 +10518,16 @@
         <v>567</v>
       </c>
       <c r="Y12" t="s">
-        <v>435</v>
+        <v>523</v>
       </c>
       <c r="Z12" t="s">
         <v>840</v>
       </c>
       <c r="AA12">
-        <v>0.99065873626587397</v>
+        <v>0.99218904910018979</v>
       </c>
       <c r="AB12">
-        <v>171.25650179230999</v>
+        <v>143.20076649652023</v>
       </c>
       <c r="AD12" t="s">
         <v>562</v>
@@ -10557,13 +10557,13 @@
         <v>1125</v>
       </c>
       <c r="AN12" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="AO12">
-        <v>0.99153439104508034</v>
+        <v>0.99215445883125275</v>
       </c>
       <c r="AP12">
-        <v>155.20283084019445</v>
+        <v>143.83492142703278</v>
       </c>
       <c r="AR12" t="s">
         <v>562</v>
@@ -10593,13 +10593,13 @@
         <v>1306</v>
       </c>
       <c r="BB12" t="s">
-        <v>887</v>
+        <v>840</v>
       </c>
       <c r="BC12">
-        <v>0.97748676055693473</v>
+        <v>0.97543237988175824</v>
       </c>
       <c r="BD12">
-        <v>659.27937094283163</v>
+        <v>675.47473859880586</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10664,16 +10664,16 @@
         <v>569</v>
       </c>
       <c r="Y13" t="s">
-        <v>457</v>
+        <v>527</v>
       </c>
       <c r="Z13" t="s">
         <v>841</v>
       </c>
       <c r="AA13">
-        <v>0.98938807156910591</v>
+        <v>0.97564251840922733</v>
       </c>
       <c r="AB13">
-        <v>194.55202123305756</v>
+        <v>446.55382916416522</v>
       </c>
       <c r="AD13" t="s">
         <v>562</v>
@@ -10703,13 +10703,13 @@
         <v>1126</v>
       </c>
       <c r="AN13" t="s">
-        <v>885</v>
+        <v>871</v>
       </c>
       <c r="AO13">
-        <v>0.98940041671700285</v>
+        <v>0.97814391961975855</v>
       </c>
       <c r="AP13">
-        <v>194.32569352161357</v>
+        <v>400.69480697109378</v>
       </c>
       <c r="AR13" t="s">
         <v>562</v>
@@ -10739,13 +10739,13 @@
         <v>1307</v>
       </c>
       <c r="BB13" t="s">
-        <v>841</v>
+        <v>857</v>
       </c>
       <c r="BC13">
-        <v>0.98661815843628831</v>
+        <v>0.90777469227524876</v>
       </c>
       <c r="BD13">
-        <v>587.29351766059415</v>
+        <v>1208.8428425634561</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10810,16 +10810,16 @@
         <v>571</v>
       </c>
       <c r="Y14" t="s">
-        <v>473</v>
+        <v>534</v>
       </c>
       <c r="Z14" t="s">
         <v>842</v>
       </c>
       <c r="AA14">
-        <v>0.99343882906134406</v>
+        <v>0.9954097472817981</v>
       </c>
       <c r="AB14">
-        <v>120.28813387535965</v>
+        <v>84.154633167035314</v>
       </c>
       <c r="AD14" t="s">
         <v>562</v>
@@ -10849,13 +10849,13 @@
         <v>1127</v>
       </c>
       <c r="AN14" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="AO14">
-        <v>0.98639521029542421</v>
+        <v>0.99224639661619274</v>
       </c>
       <c r="AP14">
-        <v>249.42114458389037</v>
+        <v>142.14939536980046</v>
       </c>
       <c r="AR14" t="s">
         <v>562</v>
@@ -10885,13 +10885,13 @@
         <v>1308</v>
       </c>
       <c r="BB14" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="BC14">
-        <v>0.99038640993878491</v>
+        <v>0.97776667041974696</v>
       </c>
       <c r="BD14">
-        <v>557.58713498257862</v>
+        <v>657.0727481909945</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10956,16 +10956,16 @@
         <v>573</v>
       </c>
       <c r="Y15" t="s">
-        <v>481</v>
+        <v>538</v>
       </c>
       <c r="Z15" t="s">
         <v>843</v>
       </c>
       <c r="AA15">
-        <v>0.98651074125865823</v>
+        <v>0.98928836714403978</v>
       </c>
       <c r="AB15">
-        <v>247.30307692459905</v>
+        <v>196.37993569260354</v>
       </c>
       <c r="AD15" t="s">
         <v>562</v>
@@ -10995,13 +10995,13 @@
         <v>1128</v>
       </c>
       <c r="AN15" t="s">
-        <v>840</v>
+        <v>876</v>
       </c>
       <c r="AO15">
-        <v>0.98896692202674552</v>
+        <v>0.98477063994548064</v>
       </c>
       <c r="AP15">
-        <v>202.27309617633225</v>
+        <v>279.20493433285503</v>
       </c>
       <c r="AR15" t="s">
         <v>562</v>
@@ -11031,13 +11031,13 @@
         <v>1309</v>
       </c>
       <c r="BB15" t="s">
-        <v>878</v>
+        <v>857</v>
       </c>
       <c r="BC15">
-        <v>0.98475443499607906</v>
+        <v>0.98620687652221406</v>
       </c>
       <c r="BD15">
-        <v>601.9858707809102</v>
+        <v>590.53579008321287</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -11102,16 +11102,16 @@
         <v>575</v>
       </c>
       <c r="Y16" t="s">
-        <v>482</v>
+        <v>436</v>
       </c>
       <c r="Z16" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AA16">
-        <v>0.9830960556239321</v>
+        <v>0.98213469589758429</v>
       </c>
       <c r="AB16">
-        <v>309.90564689457773</v>
+        <v>327.53057521095576</v>
       </c>
       <c r="AD16" t="s">
         <v>562</v>
@@ -11141,13 +11141,13 @@
         <v>1129</v>
       </c>
       <c r="AN16" t="s">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="AO16">
-        <v>0.99224743662419923</v>
+        <v>0.98880526729129725</v>
       </c>
       <c r="AP16">
-        <v>142.13032855634668</v>
+        <v>205.23676632621752</v>
       </c>
       <c r="AR16" t="s">
         <v>562</v>
@@ -11177,13 +11177,13 @@
         <v>1310</v>
       </c>
       <c r="BB16" t="s">
-        <v>887</v>
+        <v>847</v>
       </c>
       <c r="BC16">
-        <v>0.97776667041974696</v>
+        <v>0.97563785990108609</v>
       </c>
       <c r="BD16">
-        <v>657.0727481909945</v>
+        <v>673.85487111310465</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -11248,16 +11248,16 @@
         <v>577</v>
       </c>
       <c r="Y17" t="s">
-        <v>483</v>
+        <v>439</v>
       </c>
       <c r="Z17" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AA17">
-        <v>0.97890021753140011</v>
+        <v>0.98161750782838286</v>
       </c>
       <c r="AB17">
-        <v>386.8293452576653</v>
+        <v>337.01235647964734</v>
       </c>
       <c r="AD17" t="s">
         <v>562</v>
@@ -11287,13 +11287,13 @@
         <v>1130</v>
       </c>
       <c r="AN17" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="AO17">
-        <v>0.96642968891663028</v>
+        <v>0.98562926828922137</v>
       </c>
       <c r="AP17">
-        <v>615.45570319511182</v>
+        <v>263.46341469760875</v>
       </c>
       <c r="AR17" t="s">
         <v>562</v>
@@ -11323,13 +11323,13 @@
         <v>1311</v>
       </c>
       <c r="BB17" t="s">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="BC17">
-        <v>0.98620687652221406</v>
+        <v>0.97060428364656626</v>
       </c>
       <c r="BD17">
-        <v>590.53579008321287</v>
+        <v>713.53623058623612</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11394,16 +11394,16 @@
         <v>579</v>
       </c>
       <c r="Y18" t="s">
-        <v>500</v>
+        <v>442</v>
       </c>
       <c r="Z18" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AA18">
-        <v>0.99101211074213258</v>
+        <v>0.98975592846808447</v>
       </c>
       <c r="AB18">
-        <v>164.77796972756968</v>
+        <v>187.80797808511727</v>
       </c>
       <c r="AD18" t="s">
         <v>562</v>
@@ -11433,13 +11433,13 @@
         <v>1131</v>
       </c>
       <c r="AN18" t="s">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="AO18">
-        <v>0.97580462137033996</v>
+        <v>0.98557285435300757</v>
       </c>
       <c r="AP18">
-        <v>443.58194154376798</v>
+        <v>264.4976701948608</v>
       </c>
       <c r="AR18" t="s">
         <v>562</v>
@@ -11469,13 +11469,13 @@
         <v>1312</v>
       </c>
       <c r="BB18" t="s">
-        <v>894</v>
+        <v>870</v>
       </c>
       <c r="BC18">
-        <v>0.97563785990108609</v>
+        <v>0.98574293134283075</v>
       </c>
       <c r="BD18">
-        <v>673.85487111310465</v>
+        <v>594.19322458068439</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11540,16 +11540,16 @@
         <v>581</v>
       </c>
       <c r="Y19" t="s">
-        <v>543</v>
+        <v>480</v>
       </c>
       <c r="Z19" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AA19">
-        <v>0.98808830690953586</v>
+        <v>0.97312873356481211</v>
       </c>
       <c r="AB19">
-        <v>218.38103999184321</v>
+        <v>492.63988464511067</v>
       </c>
       <c r="AD19" t="s">
         <v>562</v>
@@ -11579,13 +11579,13 @@
         <v>1132</v>
       </c>
       <c r="AN19" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="AO19">
-        <v>0.98941824689872981</v>
+        <v>0.99063307902321618</v>
       </c>
       <c r="AP19">
-        <v>193.99880685662112</v>
+        <v>171.72688457437104</v>
       </c>
       <c r="AR19" t="s">
         <v>562</v>
@@ -11615,13 +11615,13 @@
         <v>1313</v>
       </c>
       <c r="BB19" t="s">
-        <v>862</v>
+        <v>886</v>
       </c>
       <c r="BC19">
-        <v>0.97060428364656626</v>
+        <v>0.98120414321706895</v>
       </c>
       <c r="BD19">
-        <v>713.53623058623612</v>
+        <v>629.97400430543962</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11686,16 +11686,16 @@
         <v>583</v>
       </c>
       <c r="Y20" t="s">
-        <v>429</v>
+        <v>488</v>
       </c>
       <c r="Z20" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="AA20">
-        <v>0.99232963975206445</v>
+        <v>0.98977266598403368</v>
       </c>
       <c r="AB20">
-        <v>140.62327121215228</v>
+        <v>187.50112362604992</v>
       </c>
       <c r="AD20" t="s">
         <v>562</v>
@@ -11725,13 +11725,13 @@
         <v>1133</v>
       </c>
       <c r="AN20" t="s">
-        <v>878</v>
+        <v>852</v>
       </c>
       <c r="AO20">
-        <v>0.9911899510437201</v>
+        <v>0.9733086107906429</v>
       </c>
       <c r="AP20">
-        <v>161.51756419846544</v>
+        <v>489.34213550487942</v>
       </c>
       <c r="AR20" t="s">
         <v>562</v>
@@ -11761,13 +11761,13 @@
         <v>1314</v>
       </c>
       <c r="BB20" t="s">
-        <v>862</v>
+        <v>891</v>
       </c>
       <c r="BC20">
-        <v>0.98574293134283075</v>
+        <v>0.97775230782134392</v>
       </c>
       <c r="BD20">
-        <v>594.19322458068439</v>
+        <v>657.18597334173887</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11832,16 +11832,16 @@
         <v>585</v>
       </c>
       <c r="Y21" t="s">
-        <v>443</v>
+        <v>499</v>
       </c>
       <c r="Z21" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="AA21">
-        <v>0.98863637284234351</v>
+        <v>0.99537444599393454</v>
       </c>
       <c r="AB21">
-        <v>208.33316455703533</v>
+        <v>84.801823444534008</v>
       </c>
       <c r="AD21" t="s">
         <v>562</v>
@@ -11871,13 +11871,13 @@
         <v>1134</v>
       </c>
       <c r="AN21" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="AO21">
-        <v>0.97139194185607003</v>
+        <v>0.9839431789633305</v>
       </c>
       <c r="AP21">
-        <v>524.48106597204946</v>
+        <v>294.37505233894177</v>
       </c>
       <c r="AR21" t="s">
         <v>562</v>
@@ -11907,13 +11907,13 @@
         <v>1315</v>
       </c>
       <c r="BB21" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="BC21">
-        <v>0.98120414321706895</v>
+        <v>0.97884476097844741</v>
       </c>
       <c r="BD21">
-        <v>629.97400430543962</v>
+        <v>648.57380095323958</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11978,16 +11978,16 @@
         <v>587</v>
       </c>
       <c r="Y22" t="s">
-        <v>454</v>
+        <v>505</v>
       </c>
       <c r="Z22" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="AA22">
-        <v>0.99016939403137849</v>
+        <v>0.99218262773253396</v>
       </c>
       <c r="AB22">
-        <v>180.22777609139402</v>
+        <v>143.31849157021014</v>
       </c>
       <c r="AD22" t="s">
         <v>562</v>
@@ -12017,13 +12017,13 @@
         <v>1135</v>
       </c>
       <c r="AN22" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="AO22">
-        <v>0.98117052771194446</v>
+        <v>0.96950481457473103</v>
       </c>
       <c r="AP22">
-        <v>345.20699194768525</v>
+        <v>559.0783994632643</v>
       </c>
       <c r="AR22" t="s">
         <v>562</v>
@@ -12053,13 +12053,13 @@
         <v>1316</v>
       </c>
       <c r="BB22" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="BC22">
-        <v>0.98556171669906312</v>
+        <v>0.9783099865431607</v>
       </c>
       <c r="BD22">
-        <v>595.62180002238608</v>
+        <v>652.78960608475018</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -12124,16 +12124,16 @@
         <v>589</v>
       </c>
       <c r="Y23" t="s">
-        <v>461</v>
+        <v>549</v>
       </c>
       <c r="Z23" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="AA23">
-        <v>0.9849937388690081</v>
+        <v>0.99477407524212647</v>
       </c>
       <c r="AB23">
-        <v>275.11478740151779</v>
+        <v>95.808620561014351</v>
       </c>
       <c r="AD23" t="s">
         <v>562</v>
@@ -12163,13 +12163,13 @@
         <v>1136</v>
       </c>
       <c r="AN23" t="s">
-        <v>865</v>
+        <v>882</v>
       </c>
       <c r="AO23">
-        <v>0.98127559165304223</v>
+        <v>0.99331955625657153</v>
       </c>
       <c r="AP23">
-        <v>343.28081969422635</v>
+        <v>122.47480196285512</v>
       </c>
       <c r="AR23" t="s">
         <v>562</v>
@@ -12199,13 +12199,13 @@
         <v>1317</v>
       </c>
       <c r="BB23" t="s">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="BC23">
-        <v>0.99041503856315227</v>
+        <v>0.91905535977869501</v>
       </c>
       <c r="BD23">
-        <v>557.36144599381669</v>
+        <v>1119.9135804112877</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -12270,16 +12270,16 @@
         <v>591</v>
       </c>
       <c r="Y24" t="s">
-        <v>465</v>
+        <v>555</v>
       </c>
       <c r="Z24" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="AA24">
-        <v>0.96879824550148963</v>
+        <v>0.99340406403388481</v>
       </c>
       <c r="AB24">
-        <v>572.03216580602339</v>
+        <v>120.92549271211209</v>
       </c>
       <c r="AD24" t="s">
         <v>562</v>
@@ -12309,13 +12309,13 @@
         <v>1137</v>
       </c>
       <c r="AN24" t="s">
-        <v>853</v>
+        <v>895</v>
       </c>
       <c r="AO24">
-        <v>0.98086141539930738</v>
+        <v>0.99328472140937729</v>
       </c>
       <c r="AP24">
-        <v>350.87405101269854</v>
+        <v>123.11344082808277</v>
       </c>
       <c r="AR24" t="s">
         <v>562</v>
@@ -12345,13 +12345,13 @@
         <v>1318</v>
       </c>
       <c r="BB24" t="s">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="BC24">
-        <v>0.98222546540109945</v>
+        <v>0.9808842004636289</v>
       </c>
       <c r="BD24">
-        <v>621.92258108799922</v>
+        <v>632.49621967839255</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12416,16 +12416,16 @@
         <v>593</v>
       </c>
       <c r="Y25" t="s">
-        <v>497</v>
+        <v>446</v>
       </c>
       <c r="Z25" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="AA25">
-        <v>0.99058937597842778</v>
+        <v>0.98950135873743683</v>
       </c>
       <c r="AB25">
-        <v>172.52810706215647</v>
+        <v>192.47508981365891</v>
       </c>
       <c r="AD25" t="s">
         <v>562</v>
@@ -12455,13 +12455,13 @@
         <v>1138</v>
       </c>
       <c r="AN25" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AO25">
-        <v>0.98555037049604</v>
+        <v>0.96363263183226566</v>
       </c>
       <c r="AP25">
-        <v>264.90987423926674</v>
+        <v>666.73508307513055</v>
       </c>
       <c r="AR25" t="s">
         <v>562</v>
@@ -12491,13 +12491,13 @@
         <v>1319</v>
       </c>
       <c r="BB25" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="BC25">
-        <v>0.90514503736235263</v>
+        <v>0.97529697423998973</v>
       </c>
       <c r="BD25">
-        <v>1229.5732887934535</v>
+        <v>676.54218640808119</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12562,16 +12562,16 @@
         <v>595</v>
       </c>
       <c r="Y26" t="s">
-        <v>517</v>
+        <v>450</v>
       </c>
       <c r="Z26" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="AA26">
-        <v>0.98884641033160892</v>
+        <v>0.99488206120957279</v>
       </c>
       <c r="AB26">
-        <v>204.48247725383573</v>
+        <v>93.828877824498619</v>
       </c>
       <c r="AD26" t="s">
         <v>562</v>
@@ -12601,13 +12601,13 @@
         <v>1139</v>
       </c>
       <c r="AN26" t="s">
-        <v>855</v>
+        <v>893</v>
       </c>
       <c r="AO26">
-        <v>0.98040327309339681</v>
+        <v>0.99153439104508034</v>
       </c>
       <c r="AP26">
-        <v>359.27332662105931</v>
+        <v>155.20283084019445</v>
       </c>
       <c r="AR26" t="s">
         <v>562</v>
@@ -12637,13 +12637,13 @@
         <v>1320</v>
       </c>
       <c r="BB26" t="s">
-        <v>878</v>
+        <v>891</v>
       </c>
       <c r="BC26">
-        <v>0.99613925038938234</v>
+        <v>0.98556171669906312</v>
       </c>
       <c r="BD26">
-        <v>322.44811734269933</v>
+        <v>595.62180002238608</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12708,16 +12708,16 @@
         <v>597</v>
       </c>
       <c r="Y27" t="s">
-        <v>524</v>
+        <v>453</v>
       </c>
       <c r="Z27" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="AA27">
-        <v>0.98971858307134875</v>
+        <v>0.98929007854358664</v>
       </c>
       <c r="AB27">
-        <v>188.49264369194051</v>
+        <v>196.34856003424409</v>
       </c>
       <c r="AD27" t="s">
         <v>562</v>
@@ -12747,13 +12747,13 @@
         <v>1140</v>
       </c>
       <c r="AN27" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="AO27">
-        <v>0.99177071872011402</v>
+        <v>0.98940041671700285</v>
       </c>
       <c r="AP27">
-        <v>150.87015679790983</v>
+        <v>194.32569352161357</v>
       </c>
       <c r="AR27" t="s">
         <v>562</v>
@@ -12783,13 +12783,13 @@
         <v>1321</v>
       </c>
       <c r="BB27" t="s">
-        <v>887</v>
+        <v>862</v>
       </c>
       <c r="BC27">
-        <v>0.97775230782134392</v>
+        <v>0.99041503856315227</v>
       </c>
       <c r="BD27">
-        <v>657.18597334173887</v>
+        <v>557.36144599381669</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12854,16 +12854,16 @@
         <v>599</v>
       </c>
       <c r="Y28" t="s">
-        <v>556</v>
+        <v>458</v>
       </c>
       <c r="Z28" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="AA28">
-        <v>0.98974367616617376</v>
+        <v>0.9692587148013998</v>
       </c>
       <c r="AB28">
-        <v>188.03260362014854</v>
+        <v>563.59022864100291</v>
       </c>
       <c r="AD28" t="s">
         <v>562</v>
@@ -12893,13 +12893,13 @@
         <v>1141</v>
       </c>
       <c r="AN28" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AO28">
-        <v>0.9871975802659102</v>
+        <v>0.98639521029542421</v>
       </c>
       <c r="AP28">
-        <v>234.7110284583128</v>
+        <v>249.42114458389037</v>
       </c>
       <c r="AR28" t="s">
         <v>562</v>
@@ -12929,13 +12929,13 @@
         <v>1322</v>
       </c>
       <c r="BB28" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="BC28">
-        <v>0.97884476097844741</v>
+        <v>0.98222546540109945</v>
       </c>
       <c r="BD28">
-        <v>648.57380095323958</v>
+        <v>621.92258108799922</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -13000,16 +13000,16 @@
         <v>601</v>
       </c>
       <c r="Y29" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="Z29" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="AA29">
-        <v>0.98950135873743683</v>
+        <v>0.99120757651401414</v>
       </c>
       <c r="AB29">
-        <v>192.47508981365891</v>
+        <v>161.19443057640677</v>
       </c>
       <c r="AD29" t="s">
         <v>562</v>
@@ -13042,10 +13042,10 @@
         <v>883</v>
       </c>
       <c r="AO29">
-        <v>0.99140701799255504</v>
+        <v>0.99270552118216204</v>
       </c>
       <c r="AP29">
-        <v>157.53800346982385</v>
+        <v>133.73211166036262</v>
       </c>
       <c r="AR29" t="s">
         <v>562</v>
@@ -13075,13 +13075,13 @@
         <v>1323</v>
       </c>
       <c r="BB29" t="s">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="BC29">
-        <v>0.96340904814790773</v>
+        <v>0.90514503736235263</v>
       </c>
       <c r="BD29">
-        <v>770.2586704339941</v>
+        <v>1229.5732887934535</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -13146,16 +13146,16 @@
         <v>603</v>
       </c>
       <c r="Y30" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="Z30" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="AA30">
-        <v>0.99488206120957279</v>
+        <v>0.98661661227366804</v>
       </c>
       <c r="AB30">
-        <v>93.828877824498619</v>
+        <v>245.36210831608693</v>
       </c>
       <c r="AD30" t="s">
         <v>562</v>
@@ -13185,13 +13185,13 @@
         <v>1143</v>
       </c>
       <c r="AN30" t="s">
-        <v>845</v>
+        <v>868</v>
       </c>
       <c r="AO30">
-        <v>0.98565286420409937</v>
+        <v>0.99077061821894719</v>
       </c>
       <c r="AP30">
-        <v>263.03082292484481</v>
+        <v>169.20533265263529</v>
       </c>
       <c r="AR30" t="s">
         <v>562</v>
@@ -13221,13 +13221,13 @@
         <v>1324</v>
       </c>
       <c r="BB30" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="BC30">
-        <v>0.97671054233736465</v>
+        <v>0.99613925038938234</v>
       </c>
       <c r="BD30">
-        <v>665.39855790710828</v>
+        <v>322.44811734269933</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -13292,16 +13292,16 @@
         <v>605</v>
       </c>
       <c r="Y31" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="Z31" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="AA31">
-        <v>0.98929007854358664</v>
+        <v>0.98939469221283771</v>
       </c>
       <c r="AB31">
-        <v>196.34856003424409</v>
+        <v>194.43064276464273</v>
       </c>
       <c r="AD31" t="s">
         <v>562</v>
@@ -13331,13 +13331,13 @@
         <v>1144</v>
       </c>
       <c r="AN31" t="s">
-        <v>866</v>
+        <v>844</v>
       </c>
       <c r="AO31">
-        <v>0.98600984216520959</v>
+        <v>0.97911240890549023</v>
       </c>
       <c r="AP31">
-        <v>256.48622697115769</v>
+        <v>382.93917006601345</v>
       </c>
       <c r="AR31" t="s">
         <v>562</v>
@@ -13367,13 +13367,13 @@
         <v>1325</v>
       </c>
       <c r="BB31" t="s">
-        <v>878</v>
+        <v>857</v>
       </c>
       <c r="BC31">
-        <v>0.98758818560479655</v>
+        <v>0.96340904814790773</v>
       </c>
       <c r="BD31">
-        <v>579.64647014885406</v>
+        <v>770.2586704339941</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13438,16 +13438,16 @@
         <v>607</v>
       </c>
       <c r="Y32" t="s">
-        <v>458</v>
+        <v>507</v>
       </c>
       <c r="Z32" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="AA32">
-        <v>0.9692587148013998</v>
+        <v>0.99170776895032964</v>
       </c>
       <c r="AB32">
-        <v>563.59022864100291</v>
+        <v>152.02423591062336</v>
       </c>
       <c r="AD32" t="s">
         <v>562</v>
@@ -13477,13 +13477,13 @@
         <v>1145</v>
       </c>
       <c r="AN32" t="s">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="AO32">
-        <v>0.9913968450205024</v>
+        <v>0.98540042793923122</v>
       </c>
       <c r="AP32">
-        <v>157.72450795745584</v>
+        <v>267.65882111409439</v>
       </c>
       <c r="AR32" t="s">
         <v>562</v>
@@ -13513,13 +13513,13 @@
         <v>1326</v>
       </c>
       <c r="BB32" t="s">
-        <v>882</v>
+        <v>857</v>
       </c>
       <c r="BC32">
-        <v>0.97985329377358876</v>
+        <v>0.98029614417839783</v>
       </c>
       <c r="BD32">
-        <v>640.6232007515423</v>
+        <v>637.13206339363023</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13584,16 +13584,16 @@
         <v>609</v>
       </c>
       <c r="Y33" t="s">
-        <v>472</v>
+        <v>546</v>
       </c>
       <c r="Z33" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="AA33">
-        <v>0.99120757651401414</v>
+        <v>0.99042342806455907</v>
       </c>
       <c r="AB33">
-        <v>161.19443057640677</v>
+        <v>175.57048548308435</v>
       </c>
       <c r="AD33" t="s">
         <v>562</v>
@@ -13623,13 +13623,13 @@
         <v>1146</v>
       </c>
       <c r="AN33" t="s">
-        <v>893</v>
+        <v>876</v>
       </c>
       <c r="AO33">
-        <v>0.98662924242305594</v>
+        <v>0.99328745157332987</v>
       </c>
       <c r="AP33">
-        <v>245.13055557730874</v>
+        <v>123.06338782228508</v>
       </c>
       <c r="AR33" t="s">
         <v>562</v>
@@ -13659,13 +13659,13 @@
         <v>1327</v>
       </c>
       <c r="BB33" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="BC33">
-        <v>0.98029614417839783</v>
+        <v>0.98865855459335616</v>
       </c>
       <c r="BD33">
-        <v>637.13206339363023</v>
+        <v>571.20839462237564</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13730,16 +13730,16 @@
         <v>611</v>
       </c>
       <c r="Y34" t="s">
-        <v>474</v>
+        <v>557</v>
       </c>
       <c r="Z34" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="AA34">
-        <v>0.98661661227366804</v>
+        <v>0.99253864063271646</v>
       </c>
       <c r="AB34">
-        <v>245.36210831608693</v>
+        <v>136.79158840019849</v>
       </c>
       <c r="AD34" t="s">
         <v>562</v>
@@ -13769,13 +13769,13 @@
         <v>1147</v>
       </c>
       <c r="AN34" t="s">
-        <v>844</v>
+        <v>889</v>
       </c>
       <c r="AO34">
-        <v>0.99375979852043306</v>
+        <v>0.97466160251195344</v>
       </c>
       <c r="AP34">
-        <v>114.40369379206156</v>
+        <v>464.53728728085309</v>
       </c>
       <c r="AR34" t="s">
         <v>562</v>
@@ -13805,13 +13805,13 @@
         <v>1328</v>
       </c>
       <c r="BB34" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="BC34">
-        <v>0.98865855459335616</v>
+        <v>0.97216269524702603</v>
       </c>
       <c r="BD34">
-        <v>571.20839462237564</v>
+        <v>701.2507524692785</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13876,16 +13876,16 @@
         <v>613</v>
       </c>
       <c r="Y35" t="s">
-        <v>479</v>
+        <v>430</v>
       </c>
       <c r="Z35" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="AA35">
-        <v>0.98939469221283771</v>
+        <v>0.9925555661059412</v>
       </c>
       <c r="AB35">
-        <v>194.43064276464273</v>
+        <v>136.48128805774428</v>
       </c>
       <c r="AD35" t="s">
         <v>562</v>
@@ -13915,13 +13915,13 @@
         <v>1148</v>
       </c>
       <c r="AN35" t="s">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="AO35">
-        <v>0.9935955776192904</v>
+        <v>0.99748710010368635</v>
       </c>
       <c r="AP35">
-        <v>117.41441031301009</v>
+        <v>46.069831432417168</v>
       </c>
       <c r="AR35" t="s">
         <v>562</v>
@@ -13951,13 +13951,13 @@
         <v>1329</v>
       </c>
       <c r="BB35" t="s">
-        <v>856</v>
+        <v>888</v>
       </c>
       <c r="BC35">
-        <v>0.9808842004636289</v>
+        <v>0.97987853234085787</v>
       </c>
       <c r="BD35">
-        <v>632.49621967839255</v>
+        <v>640.42423671290419</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -14022,16 +14022,16 @@
         <v>615</v>
       </c>
       <c r="Y36" t="s">
-        <v>507</v>
+        <v>435</v>
       </c>
       <c r="Z36" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="AA36">
-        <v>0.99170776895032964</v>
+        <v>0.99065873626587397</v>
       </c>
       <c r="AB36">
-        <v>152.02423591062336</v>
+        <v>171.25650179230999</v>
       </c>
       <c r="AD36" t="s">
         <v>562</v>
@@ -14061,13 +14061,13 @@
         <v>1149</v>
       </c>
       <c r="AN36" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="AO36">
-        <v>0.9895134548380341</v>
+        <v>0.99472130687422744</v>
       </c>
       <c r="AP36">
-        <v>192.25332796937471</v>
+        <v>96.776040639162858</v>
       </c>
       <c r="AR36" t="s">
         <v>562</v>
@@ -14097,13 +14097,13 @@
         <v>1330</v>
       </c>
       <c r="BB36" t="s">
-        <v>862</v>
+        <v>886</v>
       </c>
       <c r="BC36">
-        <v>0.97529697423998973</v>
+        <v>0.97542834759532293</v>
       </c>
       <c r="BD36">
-        <v>676.54218640808119</v>
+        <v>675.5065264568708</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -14168,16 +14168,16 @@
         <v>617</v>
       </c>
       <c r="Y37" t="s">
-        <v>546</v>
+        <v>457</v>
       </c>
       <c r="Z37" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="AA37">
-        <v>0.99042342806455907</v>
+        <v>0.98938807156910591</v>
       </c>
       <c r="AB37">
-        <v>175.57048548308435</v>
+        <v>194.55202123305756</v>
       </c>
       <c r="AD37" t="s">
         <v>562</v>
@@ -14207,13 +14207,13 @@
         <v>1150</v>
       </c>
       <c r="AN37" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="AO37">
-        <v>0.98960179851646224</v>
+        <v>0.99387886431172578</v>
       </c>
       <c r="AP37">
-        <v>190.63369386485829</v>
+        <v>112.22082095169485</v>
       </c>
       <c r="AR37" t="s">
         <v>562</v>
@@ -14243,13 +14243,13 @@
         <v>1331</v>
       </c>
       <c r="BB37" t="s">
-        <v>851</v>
+        <v>891</v>
       </c>
       <c r="BC37">
-        <v>0.97190684035904551</v>
+        <v>0.97748676055693473</v>
       </c>
       <c r="BD37">
-        <v>703.26774183619148</v>
+        <v>659.27937094283163</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14314,16 +14314,16 @@
         <v>619</v>
       </c>
       <c r="Y38" t="s">
-        <v>557</v>
+        <v>473</v>
       </c>
       <c r="Z38" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="AA38">
-        <v>0.99253864063271646</v>
+        <v>0.99343882906134406</v>
       </c>
       <c r="AB38">
-        <v>136.79158840019849</v>
+        <v>120.28813387535965</v>
       </c>
       <c r="AD38" t="s">
         <v>562</v>
@@ -14353,13 +14353,13 @@
         <v>1151</v>
       </c>
       <c r="AN38" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AO38">
-        <v>0.99430130634228164</v>
+        <v>0.9864929875546109</v>
       </c>
       <c r="AP38">
-        <v>104.47605039150224</v>
+        <v>247.62856149880113</v>
       </c>
       <c r="AR38" t="s">
         <v>562</v>
@@ -14389,13 +14389,13 @@
         <v>1332</v>
       </c>
       <c r="BB38" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="BC38">
-        <v>0.99063171688389717</v>
+        <v>0.98661815843628831</v>
       </c>
       <c r="BD38">
-        <v>548.62415996795482</v>
+        <v>587.29351766059415</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14460,16 +14460,16 @@
         <v>621</v>
       </c>
       <c r="Y39" t="s">
-        <v>428</v>
+        <v>481</v>
       </c>
       <c r="Z39" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="AA39">
-        <v>0.99495645179599901</v>
+        <v>0.98651074125865823</v>
       </c>
       <c r="AB39">
-        <v>92.465050406684512</v>
+        <v>247.30307692459905</v>
       </c>
       <c r="AD39" t="s">
         <v>562</v>
@@ -14499,13 +14499,13 @@
         <v>1152</v>
       </c>
       <c r="AN39" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="AO39">
-        <v>0.99215445883125275</v>
+        <v>0.99214368255188645</v>
       </c>
       <c r="AP39">
-        <v>143.83492142703278</v>
+        <v>144.03248654874827</v>
       </c>
       <c r="AR39" t="s">
         <v>562</v>
@@ -14535,13 +14535,13 @@
         <v>1333</v>
       </c>
       <c r="BB39" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="BC39">
-        <v>0.97543237988175824</v>
+        <v>0.99038640993878491</v>
       </c>
       <c r="BD39">
-        <v>675.47473859880586</v>
+        <v>557.58713498257862</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14606,16 +14606,16 @@
         <v>623</v>
       </c>
       <c r="Y40" t="s">
-        <v>451</v>
+        <v>482</v>
       </c>
       <c r="Z40" t="s">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="AA40">
-        <v>0.99335434882803453</v>
+        <v>0.9830960556239321</v>
       </c>
       <c r="AB40">
-        <v>121.83693815269984</v>
+        <v>309.90564689457773</v>
       </c>
       <c r="AD40" t="s">
         <v>562</v>
@@ -14645,13 +14645,13 @@
         <v>1153</v>
       </c>
       <c r="AN40" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="AO40">
-        <v>0.97814391961975855</v>
+        <v>0.9928290104176094</v>
       </c>
       <c r="AP40">
-        <v>400.69480697109378</v>
+        <v>131.46814234382811</v>
       </c>
       <c r="AR40" t="s">
         <v>562</v>
@@ -14681,13 +14681,13 @@
         <v>1334</v>
       </c>
       <c r="BB40" t="s">
-        <v>887</v>
+        <v>840</v>
       </c>
       <c r="BC40">
-        <v>0.9783099865431607</v>
+        <v>0.97190684035904551</v>
       </c>
       <c r="BD40">
-        <v>652.78960608475018</v>
+        <v>703.26774183619148</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14752,16 +14752,16 @@
         <v>625</v>
       </c>
       <c r="Y41" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="Z41" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="AA41">
-        <v>0.97858303227439647</v>
+        <v>0.97890021753140011</v>
       </c>
       <c r="AB41">
-        <v>392.64440830273202</v>
+        <v>386.8293452576653</v>
       </c>
       <c r="AD41" t="s">
         <v>562</v>
@@ -14791,13 +14791,13 @@
         <v>1154</v>
       </c>
       <c r="AN41" t="s">
-        <v>858</v>
+        <v>871</v>
       </c>
       <c r="AO41">
-        <v>0.99224639661619274</v>
+        <v>0.97791499844986385</v>
       </c>
       <c r="AP41">
-        <v>142.14939536980046</v>
+        <v>404.89169508582842</v>
       </c>
       <c r="AR41" t="s">
         <v>562</v>
@@ -14827,13 +14827,13 @@
         <v>1335</v>
       </c>
       <c r="BB41" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="BC41">
-        <v>0.91905535977869501</v>
+        <v>0.99063171688389717</v>
       </c>
       <c r="BD41">
-        <v>1119.9135804112877</v>
+        <v>548.62415996795482</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14898,16 +14898,16 @@
         <v>627</v>
       </c>
       <c r="Y42" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="Z42" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="AA42">
-        <v>0.99121272120977255</v>
+        <v>0.99101211074213258</v>
       </c>
       <c r="AB42">
-        <v>161.10011115417001</v>
+        <v>164.77796972756968</v>
       </c>
       <c r="AD42" t="s">
         <v>562</v>
@@ -14937,13 +14937,13 @@
         <v>1155</v>
       </c>
       <c r="AN42" t="s">
-        <v>872</v>
+        <v>889</v>
       </c>
       <c r="AO42">
-        <v>0.98477063994548064</v>
+        <v>0.977944947494224</v>
       </c>
       <c r="AP42">
-        <v>279.20493433285503</v>
+        <v>404.34262927256032</v>
       </c>
       <c r="AR42" t="s">
         <v>562</v>
@@ -14973,13 +14973,13 @@
         <v>1336</v>
       </c>
       <c r="BB42" t="s">
-        <v>839</v>
+        <v>881</v>
       </c>
       <c r="BC42">
-        <v>0.97216269524702603</v>
+        <v>0.98758818560479655</v>
       </c>
       <c r="BD42">
-        <v>701.2507524692785</v>
+        <v>579.64647014885406</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -15044,16 +15044,16 @@
         <v>629</v>
       </c>
       <c r="Y43" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="Z43" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="AA43">
-        <v>0.98955141276769387</v>
+        <v>0.98808830690953586</v>
       </c>
       <c r="AB43">
-        <v>191.55743259227802</v>
+        <v>218.38103999184321</v>
       </c>
       <c r="AD43" t="s">
         <v>562</v>
@@ -15083,13 +15083,13 @@
         <v>1156</v>
       </c>
       <c r="AN43" t="s">
-        <v>850</v>
+        <v>867</v>
       </c>
       <c r="AO43">
-        <v>0.98880526729129725</v>
+        <v>0.99502057695725243</v>
       </c>
       <c r="AP43">
-        <v>205.23676632621752</v>
+        <v>91.289422450372911</v>
       </c>
       <c r="AR43" t="s">
         <v>562</v>
@@ -15119,13 +15119,13 @@
         <v>1337</v>
       </c>
       <c r="BB43" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="BC43">
-        <v>0.97987853234085787</v>
+        <v>0.97985329377358876</v>
       </c>
       <c r="BD43">
-        <v>640.42423671290419</v>
+        <v>640.6232007515423</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -15190,16 +15190,16 @@
         <v>631</v>
       </c>
       <c r="Y44" t="s">
-        <v>516</v>
+        <v>467</v>
       </c>
       <c r="Z44" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="AA44">
-        <v>0.97668119298957756</v>
+        <v>0.97154747480032433</v>
       </c>
       <c r="AB44">
-        <v>427.51146185774559</v>
+        <v>521.62962866072098</v>
       </c>
       <c r="AD44" t="s">
         <v>562</v>
@@ -15229,13 +15229,13 @@
         <v>1157</v>
       </c>
       <c r="AN44" t="s">
-        <v>883</v>
+        <v>841</v>
       </c>
       <c r="AO44">
-        <v>0.98562926828922137</v>
+        <v>0.9742069477253853</v>
       </c>
       <c r="AP44">
-        <v>263.46341469760875</v>
+        <v>472.87262503460209</v>
       </c>
       <c r="AR44" t="s">
         <v>562</v>
@@ -15265,13 +15265,13 @@
         <v>1338</v>
       </c>
       <c r="BB44" t="s">
-        <v>850</v>
+        <v>881</v>
       </c>
       <c r="BC44">
-        <v>0.97542834759532293</v>
+        <v>0.97671054233736465</v>
       </c>
       <c r="BD44">
-        <v>675.5065264568708</v>
+        <v>665.39855790710828</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -15336,16 +15336,16 @@
         <v>633</v>
       </c>
       <c r="Y45" t="s">
-        <v>518</v>
+        <v>468</v>
       </c>
       <c r="Z45" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="AA45">
-        <v>0.98845897140196071</v>
+        <v>0.9790049953928549</v>
       </c>
       <c r="AB45">
-        <v>211.58552429738629</v>
+        <v>384.908417797661</v>
       </c>
       <c r="AD45" t="s">
         <v>562</v>
@@ -15375,13 +15375,13 @@
         <v>1158</v>
       </c>
       <c r="AN45" t="s">
-        <v>845</v>
+        <v>892</v>
       </c>
       <c r="AO45">
-        <v>0.98557285435300757</v>
+        <v>0.99090442938878043</v>
       </c>
       <c r="AP45">
-        <v>264.4976701948608</v>
+        <v>166.75212787235887</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15446,16 +15446,16 @@
         <v>635</v>
       </c>
       <c r="Y46" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="Z46" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="AA46">
-        <v>0.98629851964686077</v>
+        <v>0.99512310450028352</v>
       </c>
       <c r="AB46">
-        <v>251.19380647421841</v>
+        <v>89.409750828135486</v>
       </c>
       <c r="AD46" t="s">
         <v>562</v>
@@ -15485,13 +15485,13 @@
         <v>1159</v>
       </c>
       <c r="AN46" t="s">
-        <v>866</v>
+        <v>851</v>
       </c>
       <c r="AO46">
-        <v>0.99063307902321618</v>
+        <v>0.99222882711684135</v>
       </c>
       <c r="AP46">
-        <v>171.72688457437104</v>
+        <v>142.4715028579086</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15556,16 +15556,16 @@
         <v>637</v>
       </c>
       <c r="Y47" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="Z47" t="s">
-        <v>866</v>
+        <v>841</v>
       </c>
       <c r="AA47">
-        <v>0.98289372536542474</v>
+        <v>0.99180643818152092</v>
       </c>
       <c r="AB47">
-        <v>313.61503496721377</v>
+        <v>150.21530000545005</v>
       </c>
       <c r="AD47" t="s">
         <v>562</v>
@@ -15595,13 +15595,13 @@
         <v>1160</v>
       </c>
       <c r="AN47" t="s">
-        <v>868</v>
+        <v>844</v>
       </c>
       <c r="AO47">
-        <v>0.99317814360692358</v>
+        <v>0.97986124669518093</v>
       </c>
       <c r="AP47">
-        <v>125.06736720640154</v>
+        <v>369.21047725501711</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15666,16 +15666,16 @@
         <v>639</v>
       </c>
       <c r="Y48" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="Z48" t="s">
-        <v>867</v>
+        <v>841</v>
       </c>
       <c r="AA48">
-        <v>0.99506342503584544</v>
+        <v>0.97919938492738179</v>
       </c>
       <c r="AB48">
-        <v>90.503874342833086</v>
+        <v>381.34460966466662</v>
       </c>
       <c r="AD48" t="s">
         <v>562</v>
@@ -15705,13 +15705,13 @@
         <v>1161</v>
       </c>
       <c r="AN48" t="s">
-        <v>846</v>
+        <v>882</v>
       </c>
       <c r="AO48">
-        <v>0.99086943207021283</v>
+        <v>0.99347009078887716</v>
       </c>
       <c r="AP48">
-        <v>167.3937453794307</v>
+        <v>119.71500220391977</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15776,16 +15776,16 @@
         <v>641</v>
       </c>
       <c r="Y49" t="s">
-        <v>427</v>
+        <v>548</v>
       </c>
       <c r="Z49" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="AA49">
-        <v>0.9941804823678142</v>
+        <v>0.98325714881672288</v>
       </c>
       <c r="AB49">
-        <v>106.6911565900724</v>
+        <v>306.95227169341439</v>
       </c>
       <c r="AD49" t="s">
         <v>562</v>
@@ -15815,13 +15815,13 @@
         <v>1162</v>
       </c>
       <c r="AN49" t="s">
-        <v>861</v>
+        <v>875</v>
       </c>
       <c r="AO49">
-        <v>0.99302300928376919</v>
+        <v>0.98231817048454484</v>
       </c>
       <c r="AP49">
-        <v>127.91149646423172</v>
+        <v>324.16687445001179</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15886,16 +15886,16 @@
         <v>643</v>
       </c>
       <c r="Y50" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z50" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AA50">
-        <v>0.99511659056551938</v>
+        <v>0.98994820353208668</v>
       </c>
       <c r="AB50">
-        <v>89.52917296547848</v>
+        <v>184.28293524507683</v>
       </c>
       <c r="AD50" t="s">
         <v>562</v>
@@ -15925,13 +15925,13 @@
         <v>1163</v>
       </c>
       <c r="AN50" t="s">
-        <v>841</v>
+        <v>860</v>
       </c>
       <c r="AO50">
-        <v>0.99011319269869458</v>
+        <v>0.99390376443666895</v>
       </c>
       <c r="AP50">
-        <v>181.25813385726678</v>
+        <v>111.76431866107015</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15996,16 +15996,16 @@
         <v>645</v>
       </c>
       <c r="Y51" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="Z51" t="s">
-        <v>840</v>
+        <v>857</v>
       </c>
       <c r="AA51">
-        <v>0.96952136011150125</v>
+        <v>0.99211578471201944</v>
       </c>
       <c r="AB51">
-        <v>558.77506462247754</v>
+        <v>144.54394694630997</v>
       </c>
       <c r="AD51" t="s">
         <v>562</v>
@@ -16035,13 +16035,13 @@
         <v>1164</v>
       </c>
       <c r="AN51" t="s">
-        <v>842</v>
+        <v>873</v>
       </c>
       <c r="AO51">
-        <v>0.99448552674849922</v>
+        <v>0.98228212315007546</v>
       </c>
       <c r="AP51">
-        <v>101.09867627751461</v>
+        <v>324.82774224861657</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -16106,16 +16106,16 @@
         <v>647</v>
       </c>
       <c r="Y52" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Z52" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AA52">
-        <v>0.98977876009625232</v>
+        <v>0.99243446061187979</v>
       </c>
       <c r="AB52">
-        <v>187.38939823537481</v>
+        <v>138.70155544887155</v>
       </c>
       <c r="AD52" t="s">
         <v>562</v>
@@ -16145,13 +16145,13 @@
         <v>1165</v>
       </c>
       <c r="AN52" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="AO52">
-        <v>0.98107014020732863</v>
+        <v>0.98086141539930738</v>
       </c>
       <c r="AP52">
-        <v>347.04742953230885</v>
+        <v>350.87405101269854</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -16216,16 +16216,16 @@
         <v>649</v>
       </c>
       <c r="Y53" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="Z53" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AA53">
-        <v>0.99133392870479353</v>
+        <v>0.98250540566262157</v>
       </c>
       <c r="AB53">
-        <v>158.87797374545147</v>
+        <v>320.7342295186051</v>
       </c>
       <c r="AD53" t="s">
         <v>562</v>
@@ -16255,13 +16255,13 @@
         <v>1166</v>
       </c>
       <c r="AN53" t="s">
-        <v>882</v>
+        <v>855</v>
       </c>
       <c r="AO53">
-        <v>0.99547447105677267</v>
+        <v>0.98555037049604</v>
       </c>
       <c r="AP53">
-        <v>82.96803062583389</v>
+        <v>264.90987423926674</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -16326,16 +16326,16 @@
         <v>651</v>
       </c>
       <c r="Y54" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="Z54" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="AA54">
-        <v>0.9810875794416769</v>
+        <v>0.97974410411433677</v>
       </c>
       <c r="AB54">
-        <v>346.72771023592401</v>
+        <v>371.35809123716024</v>
       </c>
       <c r="AD54" t="s">
         <v>562</v>
@@ -16365,13 +16365,13 @@
         <v>1167</v>
       </c>
       <c r="AN54" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="AO54">
-        <v>0.98690358786307586</v>
+        <v>0.98040327309339681</v>
       </c>
       <c r="AP54">
-        <v>240.10088917694185</v>
+        <v>359.27332662105931</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16436,16 +16436,16 @@
         <v>653</v>
       </c>
       <c r="Y55" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="Z55" t="s">
-        <v>872</v>
+        <v>849</v>
       </c>
       <c r="AA55">
-        <v>0.99206450778354704</v>
+        <v>0.98904809077723221</v>
       </c>
       <c r="AB55">
-        <v>145.4840239683044</v>
+        <v>200.7850024174094</v>
       </c>
       <c r="AD55" t="s">
         <v>562</v>
@@ -16475,13 +16475,13 @@
         <v>1168</v>
       </c>
       <c r="AN55" t="s">
-        <v>875</v>
+        <v>857</v>
       </c>
       <c r="AO55">
-        <v>0.9941444177652955</v>
+        <v>0.99177071872011402</v>
       </c>
       <c r="AP55">
-        <v>107.35234096958277</v>
+        <v>150.87015679790983</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16546,16 +16546,16 @@
         <v>655</v>
       </c>
       <c r="Y56" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="Z56" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AA56">
-        <v>0.98787020216528199</v>
+        <v>0.992383122341708</v>
       </c>
       <c r="AB56">
-        <v>222.37962696982947</v>
+        <v>139.64275706868568</v>
       </c>
       <c r="AD56" t="s">
         <v>562</v>
@@ -16585,13 +16585,13 @@
         <v>1169</v>
       </c>
       <c r="AN56" t="s">
-        <v>853</v>
+        <v>878</v>
       </c>
       <c r="AO56">
-        <v>0.9733086107906429</v>
+        <v>0.9871975802659102</v>
       </c>
       <c r="AP56">
-        <v>489.34213550487942</v>
+        <v>234.7110284583128</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16656,16 +16656,16 @@
         <v>657</v>
       </c>
       <c r="Y57" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="Z57" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AA57">
-        <v>0.98780336216423326</v>
+        <v>0.98782738263402425</v>
       </c>
       <c r="AB57">
-        <v>223.60502698905651</v>
+        <v>223.16465170955473</v>
       </c>
       <c r="AD57" t="s">
         <v>562</v>
@@ -16695,13 +16695,13 @@
         <v>1170</v>
       </c>
       <c r="AN57" t="s">
-        <v>876</v>
+        <v>843</v>
       </c>
       <c r="AO57">
-        <v>0.9839431789633305</v>
+        <v>0.99140701799255504</v>
       </c>
       <c r="AP57">
-        <v>294.37505233894177</v>
+        <v>157.53800346982385</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16766,16 +16766,16 @@
         <v>659</v>
       </c>
       <c r="Y58" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="Z58" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="AA58">
-        <v>0.9935358987764813</v>
+        <v>0.9912814094707586</v>
       </c>
       <c r="AB58">
-        <v>118.50852243117704</v>
+        <v>159.84082636942577</v>
       </c>
       <c r="AD58" t="s">
         <v>562</v>
@@ -16805,13 +16805,13 @@
         <v>1171</v>
       </c>
       <c r="AN58" t="s">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="AO58">
-        <v>0.96950481457473103</v>
+        <v>0.98565286420409937</v>
       </c>
       <c r="AP58">
-        <v>559.0783994632643</v>
+        <v>263.03082292484481</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16876,16 +16876,16 @@
         <v>661</v>
       </c>
       <c r="Y59" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="Z59" t="s">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="AA59">
-        <v>0.97583059150286178</v>
+        <v>0.9941804823678142</v>
       </c>
       <c r="AB59">
-        <v>443.10582244753374</v>
+        <v>106.6911565900724</v>
       </c>
       <c r="AD59" t="s">
         <v>562</v>
@@ -16915,13 +16915,13 @@
         <v>1172</v>
       </c>
       <c r="AN59" t="s">
-        <v>890</v>
+        <v>873</v>
       </c>
       <c r="AO59">
-        <v>0.99331955625657153</v>
+        <v>0.98600984216520959</v>
       </c>
       <c r="AP59">
-        <v>122.47480196285512</v>
+        <v>256.48622697115769</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16986,16 +16986,16 @@
         <v>663</v>
       </c>
       <c r="Y60" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="Z60" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="AA60">
-        <v>0.98625550635031922</v>
+        <v>0.99511659056551938</v>
       </c>
       <c r="AB60">
-        <v>251.98238357748133</v>
+        <v>89.52917296547848</v>
       </c>
       <c r="AD60" t="s">
         <v>562</v>
@@ -17025,13 +17025,13 @@
         <v>1173</v>
       </c>
       <c r="AN60" t="s">
-        <v>892</v>
+        <v>855</v>
       </c>
       <c r="AO60">
-        <v>0.99328472140937729</v>
+        <v>0.97263268500799516</v>
       </c>
       <c r="AP60">
-        <v>123.11344082808277</v>
+        <v>501.73410818675478</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -17096,16 +17096,16 @@
         <v>665</v>
       </c>
       <c r="Y61" t="s">
-        <v>501</v>
+        <v>438</v>
       </c>
       <c r="Z61" t="s">
         <v>844</v>
       </c>
       <c r="AA61">
-        <v>0.99445721337660409</v>
+        <v>0.96952136011150125</v>
       </c>
       <c r="AB61">
-        <v>101.61775476225793</v>
+        <v>558.77506462247754</v>
       </c>
       <c r="AD61" t="s">
         <v>562</v>
@@ -17135,13 +17135,13 @@
         <v>1174</v>
       </c>
       <c r="AN61" t="s">
-        <v>886</v>
+        <v>839</v>
       </c>
       <c r="AO61">
-        <v>0.99702387631899381</v>
+        <v>0.99099526421280915</v>
       </c>
       <c r="AP61">
-        <v>54.562267485114141</v>
+        <v>165.08682276516558</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -17206,16 +17206,16 @@
         <v>667</v>
       </c>
       <c r="Y62" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="Z62" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="AA62">
-        <v>0.99323673511280519</v>
+        <v>0.98977876009625232</v>
       </c>
       <c r="AB62">
-        <v>123.99318959857249</v>
+        <v>187.38939823537481</v>
       </c>
       <c r="AD62" t="s">
         <v>562</v>
@@ -17245,13 +17245,13 @@
         <v>1175</v>
       </c>
       <c r="AN62" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="AO62">
-        <v>0.99193693152956208</v>
+        <v>0.99072339258685749</v>
       </c>
       <c r="AP62">
-        <v>147.8229219580285</v>
+        <v>170.07113590761304</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -17316,16 +17316,16 @@
         <v>669</v>
       </c>
       <c r="Y63" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="Z63" t="s">
-        <v>872</v>
+        <v>848</v>
       </c>
       <c r="AA63">
-        <v>0.98413237776361673</v>
+        <v>0.99133392870479353</v>
       </c>
       <c r="AB63">
-        <v>290.90640766702762</v>
+        <v>158.87797374545147</v>
       </c>
       <c r="AD63" t="s">
         <v>562</v>
@@ -17355,13 +17355,13 @@
         <v>1176</v>
       </c>
       <c r="AN63" t="s">
-        <v>849</v>
+        <v>877</v>
       </c>
       <c r="AO63">
-        <v>0.99063792186488431</v>
+        <v>0.98702528039583703</v>
       </c>
       <c r="AP63">
-        <v>171.63809914378689</v>
+        <v>237.86985940965451</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17426,16 +17426,16 @@
         <v>671</v>
       </c>
       <c r="Y64" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="Z64" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="AA64">
-        <v>0.99131351134049961</v>
+        <v>0.9810875794416769</v>
       </c>
       <c r="AB64">
-        <v>159.25229209083986</v>
+        <v>346.72771023592401</v>
       </c>
       <c r="AD64" t="s">
         <v>562</v>
@@ -17465,13 +17465,13 @@
         <v>1177</v>
       </c>
       <c r="AN64" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AO64">
-        <v>0.9898048456745685</v>
+        <v>0.99511776358677106</v>
       </c>
       <c r="AP64">
-        <v>186.91116263291045</v>
+        <v>89.507667575863124</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17536,16 +17536,16 @@
         <v>673</v>
       </c>
       <c r="Y65" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="Z65" t="s">
-        <v>859</v>
+        <v>876</v>
       </c>
       <c r="AA65">
-        <v>0.98661257708946326</v>
+        <v>0.99206450778354704</v>
       </c>
       <c r="AB65">
-        <v>245.43608669317408</v>
+        <v>145.4840239683044</v>
       </c>
       <c r="AD65" t="s">
         <v>562</v>
@@ -17575,13 +17575,13 @@
         <v>1178</v>
       </c>
       <c r="AN65" t="s">
-        <v>879</v>
+        <v>851</v>
       </c>
       <c r="AO65">
-        <v>0.99270552118216204</v>
+        <v>0.99298280898033964</v>
       </c>
       <c r="AP65">
-        <v>133.73211166036262</v>
+        <v>128.64850202710696</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17646,16 +17646,16 @@
         <v>675</v>
       </c>
       <c r="Y66" t="s">
-        <v>560</v>
+        <v>525</v>
       </c>
       <c r="Z66" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AA66">
-        <v>0.99314801780790185</v>
+        <v>0.98787020216528199</v>
       </c>
       <c r="AB66">
-        <v>125.61967352179877</v>
+        <v>222.37962696982947</v>
       </c>
       <c r="AD66" t="s">
         <v>562</v>
@@ -17685,13 +17685,13 @@
         <v>1179</v>
       </c>
       <c r="AN66" t="s">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="AO66">
-        <v>0.99077061821894719</v>
+        <v>0.99562564597459979</v>
       </c>
       <c r="AP66">
-        <v>169.20533265263529</v>
+        <v>80.196490465669797</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17756,16 +17756,16 @@
         <v>677</v>
       </c>
       <c r="Y67" t="s">
-        <v>426</v>
+        <v>536</v>
       </c>
       <c r="Z67" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="AA67">
-        <v>0.99359770729841634</v>
+        <v>0.98780336216423326</v>
       </c>
       <c r="AB67">
-        <v>117.37536619570103</v>
+        <v>223.60502698905651</v>
       </c>
       <c r="AD67" t="s">
         <v>562</v>
@@ -17795,13 +17795,13 @@
         <v>1180</v>
       </c>
       <c r="AN67" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="AO67">
-        <v>0.97911240890549023</v>
+        <v>0.98896692202674552</v>
       </c>
       <c r="AP67">
-        <v>382.93917006601345</v>
+        <v>202.27309617633225</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17866,16 +17866,16 @@
         <v>679</v>
       </c>
       <c r="Y68" t="s">
-        <v>432</v>
+        <v>559</v>
       </c>
       <c r="Z68" t="s">
         <v>879</v>
       </c>
       <c r="AA68">
-        <v>0.99364006102472313</v>
+        <v>0.9935358987764813</v>
       </c>
       <c r="AB68">
-        <v>116.59888121340903</v>
+        <v>118.50852243117704</v>
       </c>
       <c r="AD68" t="s">
         <v>562</v>
@@ -17905,13 +17905,13 @@
         <v>1181</v>
       </c>
       <c r="AN68" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AO68">
-        <v>0.98540042793923122</v>
+        <v>0.99224743662419923</v>
       </c>
       <c r="AP68">
-        <v>267.65882111409439</v>
+        <v>142.13032855634668</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17976,16 +17976,16 @@
         <v>681</v>
       </c>
       <c r="Y69" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Z69" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AA69">
-        <v>0.96029753299263365</v>
+        <v>0.97583059150286178</v>
       </c>
       <c r="AB69">
-        <v>727.87856180171616</v>
+        <v>443.10582244753374</v>
       </c>
       <c r="AD69" t="s">
         <v>562</v>
@@ -18015,13 +18015,13 @@
         <v>1182</v>
       </c>
       <c r="AN69" t="s">
-        <v>872</v>
+        <v>852</v>
       </c>
       <c r="AO69">
-        <v>0.99328745157332987</v>
+        <v>0.96642968891663028</v>
       </c>
       <c r="AP69">
-        <v>123.06338782228508</v>
+        <v>615.45570319511182</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -18086,16 +18086,16 @@
         <v>683</v>
       </c>
       <c r="Y70" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="Z70" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="AA70">
-        <v>0.97893171539705459</v>
+        <v>0.98625550635031922</v>
       </c>
       <c r="AB70">
-        <v>386.25188438733272</v>
+        <v>251.98238357748133</v>
       </c>
       <c r="AD70" t="s">
         <v>562</v>
@@ -18125,13 +18125,13 @@
         <v>1183</v>
       </c>
       <c r="AN70" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="AO70">
-        <v>0.97466160251195344</v>
+        <v>0.97580462137033996</v>
       </c>
       <c r="AP70">
-        <v>464.53728728085309</v>
+        <v>443.58194154376798</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -18196,16 +18196,16 @@
         <v>685</v>
       </c>
       <c r="Y71" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="Z71" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="AA71">
-        <v>0.99099682968404001</v>
+        <v>0.99445721337660409</v>
       </c>
       <c r="AB71">
-        <v>165.05812245926603</v>
+        <v>101.61775476225793</v>
       </c>
       <c r="AD71" t="s">
         <v>562</v>
@@ -18235,13 +18235,13 @@
         <v>1184</v>
       </c>
       <c r="AN71" t="s">
-        <v>897</v>
+        <v>871</v>
       </c>
       <c r="AO71">
-        <v>0.99748710010368635</v>
+        <v>0.98941824689872981</v>
       </c>
       <c r="AP71">
-        <v>46.069831432417168</v>
+        <v>193.99880685662112</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -18306,16 +18306,16 @@
         <v>687</v>
       </c>
       <c r="Y72" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="Z72" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="AA72">
-        <v>0.97972538426958966</v>
+        <v>0.99323673511280519</v>
       </c>
       <c r="AB72">
-        <v>371.70128839085726</v>
+        <v>123.99318959857249</v>
       </c>
       <c r="AD72" t="s">
         <v>562</v>
@@ -18345,13 +18345,13 @@
         <v>1185</v>
       </c>
       <c r="AN72" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="AO72">
-        <v>0.99472130687422744</v>
+        <v>0.9911899510437201</v>
       </c>
       <c r="AP72">
-        <v>96.776040639162858</v>
+        <v>161.51756419846544</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -18416,16 +18416,16 @@
         <v>689</v>
       </c>
       <c r="Y73" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="Z73" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="AA73">
-        <v>0.98785527533632433</v>
+        <v>0.98413237776361673</v>
       </c>
       <c r="AB73">
-        <v>222.65328550072056</v>
+        <v>290.90640766702762</v>
       </c>
       <c r="AD73" t="s">
         <v>562</v>
@@ -18455,13 +18455,13 @@
         <v>1186</v>
       </c>
       <c r="AN73" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="AO73">
-        <v>0.99387886431172578</v>
+        <v>0.97139194185607003</v>
       </c>
       <c r="AP73">
-        <v>112.22082095169485</v>
+        <v>524.48106597204946</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -18526,16 +18526,16 @@
         <v>691</v>
       </c>
       <c r="Y74" t="s">
-        <v>486</v>
+        <v>522</v>
       </c>
       <c r="Z74" t="s">
-        <v>843</v>
+        <v>881</v>
       </c>
       <c r="AA74">
-        <v>0.98415070826722661</v>
+        <v>0.99131351134049961</v>
       </c>
       <c r="AB74">
-        <v>290.5703484341791</v>
+        <v>159.25229209083986</v>
       </c>
       <c r="AD74" t="s">
         <v>562</v>
@@ -18565,13 +18565,13 @@
         <v>1187</v>
       </c>
       <c r="AN74" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="AO74">
-        <v>0.9864929875546109</v>
+        <v>0.98117052771194446</v>
       </c>
       <c r="AP74">
-        <v>247.62856149880113</v>
+        <v>345.20699194768525</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18636,16 +18636,16 @@
         <v>693</v>
       </c>
       <c r="Y75" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="Z75" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="AA75">
-        <v>0.9922931816569136</v>
+        <v>0.98661257708946326</v>
       </c>
       <c r="AB75">
-        <v>141.29166962325118</v>
+        <v>245.43608669317408</v>
       </c>
       <c r="AD75" t="s">
         <v>562</v>
@@ -18675,13 +18675,13 @@
         <v>1188</v>
       </c>
       <c r="AN75" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AO75">
-        <v>0.99214368255188645</v>
+        <v>0.98127559165304223</v>
       </c>
       <c r="AP75">
-        <v>144.03248654874827</v>
+        <v>343.28081969422635</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18746,16 +18746,16 @@
         <v>695</v>
       </c>
       <c r="Y76" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
       <c r="Z76" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="AA76">
-        <v>0.99053483022914257</v>
+        <v>0.99314801780790185</v>
       </c>
       <c r="AB76">
-        <v>173.52811246571903</v>
+        <v>125.61967352179877</v>
       </c>
       <c r="AD76" t="s">
         <v>562</v>
@@ -18785,13 +18785,13 @@
         <v>1189</v>
       </c>
       <c r="AN76" t="s">
-        <v>894</v>
+        <v>862</v>
       </c>
       <c r="AO76">
-        <v>0.9928290104176094</v>
+        <v>0.99304329114881718</v>
       </c>
       <c r="AP76">
-        <v>131.46814234382811</v>
+        <v>127.53966227168546</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18856,16 +18856,16 @@
         <v>697</v>
       </c>
       <c r="Y77" t="s">
-        <v>540</v>
+        <v>456</v>
       </c>
       <c r="Z77" t="s">
-        <v>845</v>
+        <v>863</v>
       </c>
       <c r="AA77">
-        <v>0.98320360732321854</v>
+        <v>0.98602445832668828</v>
       </c>
       <c r="AB77">
-        <v>307.93386574099321</v>
+        <v>256.2182640107153</v>
       </c>
       <c r="AD77" t="s">
         <v>562</v>
@@ -18895,13 +18895,13 @@
         <v>1190</v>
       </c>
       <c r="AN77" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="AO77">
-        <v>0.97791499844986385</v>
+        <v>0.99264385543323097</v>
       </c>
       <c r="AP77">
-        <v>404.89169508582842</v>
+        <v>134.8626503907652</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18966,16 +18966,16 @@
         <v>699</v>
       </c>
       <c r="Y78" t="s">
-        <v>542</v>
+        <v>470</v>
       </c>
       <c r="Z78" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="AA78">
-        <v>0.98897406466844573</v>
+        <v>0.98274955259938535</v>
       </c>
       <c r="AB78">
-        <v>202.14214774516236</v>
+        <v>316.25820234460127</v>
       </c>
       <c r="AD78" t="s">
         <v>562</v>
@@ -19005,13 +19005,13 @@
         <v>1191</v>
       </c>
       <c r="AN78" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="AO78">
-        <v>0.977944947494224</v>
+        <v>0.98530274641518678</v>
       </c>
       <c r="AP78">
-        <v>404.34262927256032</v>
+        <v>269.44964905490986</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -19076,16 +19076,16 @@
         <v>701</v>
       </c>
       <c r="Y79" t="s">
-        <v>554</v>
+        <v>491</v>
       </c>
       <c r="Z79" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AA79">
-        <v>0.99152145048007134</v>
+        <v>0.99368873088044474</v>
       </c>
       <c r="AB79">
-        <v>155.44007453202627</v>
+        <v>115.70660052517967</v>
       </c>
       <c r="AD79" t="s">
         <v>562</v>
@@ -19115,13 +19115,13 @@
         <v>1192</v>
       </c>
       <c r="AN79" t="s">
-        <v>889</v>
+        <v>854</v>
       </c>
       <c r="AO79">
-        <v>0.99502057695725243</v>
+        <v>0.98558146952732006</v>
       </c>
       <c r="AP79">
-        <v>91.289422450372911</v>
+        <v>264.33972533246634</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -19186,16 +19186,16 @@
         <v>703</v>
       </c>
       <c r="Y80" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="Z80" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="AA80">
-        <v>0.99142410630444711</v>
+        <v>0.99323001255738197</v>
       </c>
       <c r="AB80">
-        <v>157.22471775180347</v>
+        <v>124.11643644799697</v>
       </c>
       <c r="AD80" t="s">
         <v>562</v>
@@ -19225,13 +19225,13 @@
         <v>1193</v>
       </c>
       <c r="AN80" t="s">
-        <v>865</v>
+        <v>846</v>
       </c>
       <c r="AO80">
-        <v>0.9742069477253853</v>
+        <v>0.98563706266808038</v>
       </c>
       <c r="AP80">
-        <v>472.87262503460209</v>
+        <v>263.32051775185897</v>
       </c>
     </row>
     <row r="81" spans="2:42">
@@ -19296,16 +19296,16 @@
         <v>705</v>
       </c>
       <c r="Y81" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="Z81" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="AA81">
-        <v>0.99218904910018979</v>
+        <v>0.99148244782956252</v>
       </c>
       <c r="AB81">
-        <v>143.20076649652023</v>
+        <v>156.15512312468667</v>
       </c>
       <c r="AD81" t="s">
         <v>562</v>
@@ -19335,13 +19335,13 @@
         <v>1194</v>
       </c>
       <c r="AN81" t="s">
-        <v>888</v>
+        <v>870</v>
       </c>
       <c r="AO81">
-        <v>0.99090442938878043</v>
+        <v>0.9859891893004602</v>
       </c>
       <c r="AP81">
-        <v>166.75212787235887</v>
+        <v>256.8648628248954</v>
       </c>
     </row>
     <row r="82" spans="2:42">
@@ -19406,16 +19406,16 @@
         <v>707</v>
       </c>
       <c r="Y82" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="Z82" t="s">
-        <v>865</v>
+        <v>841</v>
       </c>
       <c r="AA82">
-        <v>0.97564251840922733</v>
+        <v>0.96906520826310416</v>
       </c>
       <c r="AB82">
-        <v>446.55382916416522</v>
+        <v>567.13784850975708</v>
       </c>
       <c r="AD82" t="s">
         <v>562</v>
@@ -19445,13 +19445,13 @@
         <v>1195</v>
       </c>
       <c r="AN82" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="AO82">
-        <v>0.99222882711684135</v>
+        <v>0.98980378364600918</v>
       </c>
       <c r="AP82">
-        <v>142.4715028579086</v>
+        <v>186.93063315649889</v>
       </c>
     </row>
     <row r="83" spans="2:42">
@@ -19516,16 +19516,16 @@
         <v>709</v>
       </c>
       <c r="Y83" t="s">
-        <v>534</v>
+        <v>431</v>
       </c>
       <c r="Z83" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AA83">
-        <v>0.9954097472817981</v>
+        <v>0.99217497048797409</v>
       </c>
       <c r="AB83">
-        <v>84.154633167035314</v>
+        <v>143.45887438714203</v>
       </c>
       <c r="AD83" t="s">
         <v>562</v>
@@ -19555,13 +19555,13 @@
         <v>1196</v>
       </c>
       <c r="AN83" t="s">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="AO83">
-        <v>0.97263268500799516</v>
+        <v>0.99069539601336043</v>
       </c>
       <c r="AP83">
-        <v>501.73410818675478</v>
+        <v>170.5844064217261</v>
       </c>
     </row>
     <row r="84" spans="2:42">
@@ -19626,16 +19626,16 @@
         <v>711</v>
       </c>
       <c r="Y84" t="s">
-        <v>538</v>
+        <v>441</v>
       </c>
       <c r="Z84" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AA84">
-        <v>0.98928836714403978</v>
+        <v>0.99688734285602987</v>
       </c>
       <c r="AB84">
-        <v>196.37993569260354</v>
+        <v>57.065380972786443</v>
       </c>
       <c r="AD84" t="s">
         <v>562</v>
@@ -19665,13 +19665,13 @@
         <v>1197</v>
       </c>
       <c r="AN84" t="s">
-        <v>877</v>
+        <v>860</v>
       </c>
       <c r="AO84">
-        <v>0.99099526421280915</v>
+        <v>0.98658832734700097</v>
       </c>
       <c r="AP84">
-        <v>165.08682276516558</v>
+        <v>245.88066530498185</v>
       </c>
     </row>
     <row r="85" spans="2:42">
@@ -19736,16 +19736,16 @@
         <v>713</v>
       </c>
       <c r="Y85" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="Z85" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="AA85">
-        <v>0.98994820353208668</v>
+        <v>0.99243001465918479</v>
       </c>
       <c r="AB85">
-        <v>184.28293524507683</v>
+        <v>138.78306458161211</v>
       </c>
       <c r="AD85" t="s">
         <v>562</v>
@@ -19778,10 +19778,10 @@
         <v>884</v>
       </c>
       <c r="AO85">
-        <v>0.99072339258685749</v>
+        <v>0.99702387631899381</v>
       </c>
       <c r="AP85">
-        <v>170.07113590761304</v>
+        <v>54.562267485114141</v>
       </c>
     </row>
     <row r="86" spans="2:42">
@@ -19846,16 +19846,16 @@
         <v>715</v>
       </c>
       <c r="Y86" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="Z86" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
       <c r="AA86">
-        <v>0.99211578471201944</v>
+        <v>0.96964927506180898</v>
       </c>
       <c r="AB86">
-        <v>144.54394694630997</v>
+        <v>556.42995720016825</v>
       </c>
       <c r="AD86" t="s">
         <v>562</v>
@@ -19885,13 +19885,13 @@
         <v>1199</v>
       </c>
       <c r="AN86" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="AO86">
-        <v>0.98702528039583703</v>
+        <v>0.99193693152956208</v>
       </c>
       <c r="AP86">
-        <v>237.86985940965451</v>
+        <v>147.8229219580285</v>
       </c>
     </row>
     <row r="87" spans="2:42">
@@ -19956,16 +19956,16 @@
         <v>717</v>
       </c>
       <c r="Y87" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="Z87" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="AA87">
-        <v>0.99243446061187979</v>
+        <v>0.9741863781992316</v>
       </c>
       <c r="AB87">
-        <v>138.70155544887155</v>
+        <v>473.24973301408767</v>
       </c>
       <c r="AD87" t="s">
         <v>562</v>
@@ -19995,13 +19995,13 @@
         <v>1200</v>
       </c>
       <c r="AN87" t="s">
-        <v>895</v>
+        <v>871</v>
       </c>
       <c r="AO87">
-        <v>0.99511776358677106</v>
+        <v>0.99063792186488431</v>
       </c>
       <c r="AP87">
-        <v>89.507667575863124</v>
+        <v>171.63809914378689</v>
       </c>
     </row>
     <row r="88" spans="2:42">
@@ -20066,16 +20066,16 @@
         <v>719</v>
       </c>
       <c r="Y88" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
       <c r="Z88" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="AA88">
-        <v>0.98250540566262157</v>
+        <v>0.99407588262977375</v>
       </c>
       <c r="AB88">
-        <v>320.7342295186051</v>
+        <v>108.60881845414757</v>
       </c>
       <c r="AD88" t="s">
         <v>562</v>
@@ -20105,13 +20105,13 @@
         <v>1201</v>
       </c>
       <c r="AN88" t="s">
-        <v>881</v>
+        <v>840</v>
       </c>
       <c r="AO88">
-        <v>0.99298280898033964</v>
+        <v>0.9898048456745685</v>
       </c>
       <c r="AP88">
-        <v>128.64850202710696</v>
+        <v>186.91116263291045</v>
       </c>
     </row>
     <row r="89" spans="2:42">
@@ -20176,16 +20176,16 @@
         <v>721</v>
       </c>
       <c r="Y89" t="s">
-        <v>496</v>
+        <v>547</v>
       </c>
       <c r="Z89" t="s">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="AA89">
-        <v>0.97974410411433677</v>
+        <v>0.97256549686216975</v>
       </c>
       <c r="AB89">
-        <v>371.35809123716024</v>
+        <v>502.96589086022118</v>
       </c>
       <c r="AD89" t="s">
         <v>562</v>
@@ -20215,13 +20215,13 @@
         <v>1202</v>
       </c>
       <c r="AN89" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AO89">
-        <v>0.99562564597459979</v>
+        <v>0.9913968450205024</v>
       </c>
       <c r="AP89">
-        <v>80.196490465669797</v>
+        <v>157.72450795745584</v>
       </c>
     </row>
     <row r="90" spans="2:42">
@@ -20286,16 +20286,16 @@
         <v>723</v>
       </c>
       <c r="Y90" t="s">
-        <v>504</v>
+        <v>429</v>
       </c>
       <c r="Z90" t="s">
-        <v>884</v>
+        <v>862</v>
       </c>
       <c r="AA90">
-        <v>0.98904809077723221</v>
+        <v>0.99232963975206445</v>
       </c>
       <c r="AB90">
-        <v>200.7850024174094</v>
+        <v>140.62327121215228</v>
       </c>
       <c r="AD90" t="s">
         <v>562</v>
@@ -20325,13 +20325,13 @@
         <v>1203</v>
       </c>
       <c r="AN90" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="AO90">
-        <v>0.99304329114881718</v>
+        <v>0.98662924242305594</v>
       </c>
       <c r="AP90">
-        <v>127.53966227168546</v>
+        <v>245.13055557730874</v>
       </c>
     </row>
     <row r="91" spans="2:42">
@@ -20396,16 +20396,16 @@
         <v>725</v>
       </c>
       <c r="Y91" t="s">
-        <v>521</v>
+        <v>443</v>
       </c>
       <c r="Z91" t="s">
         <v>885</v>
       </c>
       <c r="AA91">
-        <v>0.992383122341708</v>
+        <v>0.98863637284234351</v>
       </c>
       <c r="AB91">
-        <v>139.64275706868568</v>
+        <v>208.33316455703533</v>
       </c>
       <c r="AD91" t="s">
         <v>562</v>
@@ -20435,13 +20435,13 @@
         <v>1204</v>
       </c>
       <c r="AN91" t="s">
-        <v>839</v>
+        <v>865</v>
       </c>
       <c r="AO91">
-        <v>0.99264385543323097</v>
+        <v>0.99375979852043306</v>
       </c>
       <c r="AP91">
-        <v>134.8626503907652</v>
+        <v>114.40369379206156</v>
       </c>
     </row>
     <row r="92" spans="2:42">
@@ -20506,16 +20506,16 @@
         <v>727</v>
       </c>
       <c r="Y92" t="s">
-        <v>551</v>
+        <v>454</v>
       </c>
       <c r="Z92" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="AA92">
-        <v>0.98782738263402425</v>
+        <v>0.99016939403137849</v>
       </c>
       <c r="AB92">
-        <v>223.16465170955473</v>
+        <v>180.22777609139402</v>
       </c>
       <c r="AD92" t="s">
         <v>562</v>
@@ -20545,13 +20545,13 @@
         <v>1205</v>
       </c>
       <c r="AN92" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
       <c r="AO92">
-        <v>0.98530274641518678</v>
+        <v>0.9935955776192904</v>
       </c>
       <c r="AP92">
-        <v>269.44964905490986</v>
+        <v>117.41441031301009</v>
       </c>
     </row>
     <row r="93" spans="2:42">
@@ -20616,16 +20616,16 @@
         <v>729</v>
       </c>
       <c r="Y93" t="s">
-        <v>553</v>
+        <v>461</v>
       </c>
       <c r="Z93" t="s">
-        <v>866</v>
+        <v>855</v>
       </c>
       <c r="AA93">
-        <v>0.9912814094707586</v>
+        <v>0.9849937388690081</v>
       </c>
       <c r="AB93">
-        <v>159.84082636942577</v>
+        <v>275.11478740151779</v>
       </c>
       <c r="AD93" t="s">
         <v>562</v>
@@ -20655,13 +20655,13 @@
         <v>1206</v>
       </c>
       <c r="AN93" t="s">
-        <v>847</v>
+        <v>875</v>
       </c>
       <c r="AO93">
-        <v>0.98558146952732006</v>
+        <v>0.9895134548380341</v>
       </c>
       <c r="AP93">
-        <v>264.33972533246634</v>
+        <v>192.25332796937471</v>
       </c>
     </row>
     <row r="94" spans="2:42">
@@ -20726,16 +20726,16 @@
         <v>731</v>
       </c>
       <c r="Y94" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="Z94" t="s">
-        <v>879</v>
+        <v>855</v>
       </c>
       <c r="AA94">
-        <v>0.99217497048797409</v>
+        <v>0.96879824550148963</v>
       </c>
       <c r="AB94">
-        <v>143.45887438714203</v>
+        <v>572.03216580602339</v>
       </c>
       <c r="AD94" t="s">
         <v>562</v>
@@ -20765,13 +20765,13 @@
         <v>1207</v>
       </c>
       <c r="AN94" t="s">
-        <v>843</v>
+        <v>878</v>
       </c>
       <c r="AO94">
-        <v>0.98563706266808038</v>
+        <v>0.98960179851646224</v>
       </c>
       <c r="AP94">
-        <v>263.32051775185897</v>
+        <v>190.63369386485829</v>
       </c>
     </row>
     <row r="95" spans="2:42">
@@ -20836,16 +20836,16 @@
         <v>733</v>
       </c>
       <c r="Y95" t="s">
-        <v>441</v>
+        <v>497</v>
       </c>
       <c r="Z95" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="AA95">
-        <v>0.99688734285602987</v>
+        <v>0.99058937597842778</v>
       </c>
       <c r="AB95">
-        <v>57.065380972786443</v>
+        <v>172.52810706215647</v>
       </c>
       <c r="AD95" t="s">
         <v>562</v>
@@ -20875,13 +20875,13 @@
         <v>1208</v>
       </c>
       <c r="AN95" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="AO95">
-        <v>0.9859891893004602</v>
+        <v>0.99317814360692358</v>
       </c>
       <c r="AP95">
-        <v>256.8648628248954</v>
+        <v>125.06736720640154</v>
       </c>
     </row>
     <row r="96" spans="2:42">
@@ -20946,16 +20946,16 @@
         <v>735</v>
       </c>
       <c r="Y96" t="s">
-        <v>444</v>
+        <v>517</v>
       </c>
       <c r="Z96" t="s">
-        <v>846</v>
+        <v>886</v>
       </c>
       <c r="AA96">
-        <v>0.99243001465918479</v>
+        <v>0.98884641033160892</v>
       </c>
       <c r="AB96">
-        <v>138.78306458161211</v>
+        <v>204.48247725383573</v>
       </c>
       <c r="AD96" t="s">
         <v>562</v>
@@ -20985,13 +20985,13 @@
         <v>1209</v>
       </c>
       <c r="AN96" t="s">
-        <v>863</v>
+        <v>885</v>
       </c>
       <c r="AO96">
-        <v>0.98980378364600918</v>
+        <v>0.99086943207021283</v>
       </c>
       <c r="AP96">
-        <v>186.93063315649889</v>
+        <v>167.3937453794307</v>
       </c>
     </row>
     <row r="97" spans="2:42">
@@ -21056,16 +21056,16 @@
         <v>737</v>
       </c>
       <c r="Y97" t="s">
-        <v>484</v>
+        <v>524</v>
       </c>
       <c r="Z97" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="AA97">
-        <v>0.96964927506180898</v>
+        <v>0.98971858307134875</v>
       </c>
       <c r="AB97">
-        <v>556.42995720016825</v>
+        <v>188.49264369194051</v>
       </c>
       <c r="AD97" t="s">
         <v>562</v>
@@ -21095,13 +21095,13 @@
         <v>1210</v>
       </c>
       <c r="AN97" t="s">
-        <v>845</v>
+        <v>888</v>
       </c>
       <c r="AO97">
-        <v>0.99069539601336043</v>
+        <v>0.99302300928376919</v>
       </c>
       <c r="AP97">
-        <v>170.5844064217261</v>
+        <v>127.91149646423172</v>
       </c>
     </row>
     <row r="98" spans="2:42">
@@ -21166,16 +21166,16 @@
         <v>739</v>
       </c>
       <c r="Y98" t="s">
-        <v>495</v>
+        <v>556</v>
       </c>
       <c r="Z98" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="AA98">
-        <v>0.9741863781992316</v>
+        <v>0.98974367616617376</v>
       </c>
       <c r="AB98">
-        <v>473.24973301408767</v>
+        <v>188.03260362014854</v>
       </c>
       <c r="AD98" t="s">
         <v>562</v>
@@ -21205,13 +21205,13 @@
         <v>1211</v>
       </c>
       <c r="AN98" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="AO98">
-        <v>0.98658832734700097</v>
+        <v>0.99011319269869458</v>
       </c>
       <c r="AP98">
-        <v>245.88066530498185</v>
+        <v>181.25813385726678</v>
       </c>
     </row>
     <row r="99" spans="2:42">
@@ -21276,16 +21276,16 @@
         <v>741</v>
       </c>
       <c r="Y99" t="s">
-        <v>545</v>
+        <v>428</v>
       </c>
       <c r="Z99" t="s">
-        <v>859</v>
+        <v>887</v>
       </c>
       <c r="AA99">
-        <v>0.99407588262977375</v>
+        <v>0.99495645179599901</v>
       </c>
       <c r="AB99">
-        <v>108.60881845414757</v>
+        <v>92.465050406684512</v>
       </c>
       <c r="AD99" t="s">
         <v>562</v>
@@ -21315,13 +21315,13 @@
         <v>1212</v>
       </c>
       <c r="AN99" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="AO99">
-        <v>0.99423394997920433</v>
+        <v>0.99448552674849922</v>
       </c>
       <c r="AP99">
-        <v>105.71091704792103</v>
+        <v>101.09867627751461</v>
       </c>
     </row>
     <row r="100" spans="2:42">
@@ -21386,16 +21386,16 @@
         <v>743</v>
       </c>
       <c r="Y100" t="s">
-        <v>547</v>
+        <v>451</v>
       </c>
       <c r="Z100" t="s">
-        <v>859</v>
+        <v>888</v>
       </c>
       <c r="AA100">
-        <v>0.97256549686216975</v>
+        <v>0.99335434882803453</v>
       </c>
       <c r="AB100">
-        <v>502.96589086022118</v>
+        <v>121.83693815269984</v>
       </c>
       <c r="AD100" t="s">
         <v>562</v>
@@ -21425,13 +21425,13 @@
         <v>1213</v>
       </c>
       <c r="AN100" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="AO100">
-        <v>0.99467731181029251</v>
+        <v>0.98107014020732863</v>
       </c>
       <c r="AP100">
-        <v>97.582616811304106</v>
+        <v>347.04742953230885</v>
       </c>
     </row>
     <row r="101" spans="2:42">
@@ -21496,16 +21496,16 @@
         <v>745</v>
       </c>
       <c r="Y101" t="s">
-        <v>425</v>
+        <v>471</v>
       </c>
       <c r="Z101" t="s">
-        <v>887</v>
+        <v>856</v>
       </c>
       <c r="AA101">
-        <v>0.99579045202592908</v>
+        <v>0.97858303227439647</v>
       </c>
       <c r="AB101">
-        <v>77.175046191301078</v>
+        <v>392.64440830273202</v>
       </c>
       <c r="AD101" t="s">
         <v>562</v>
@@ -21535,13 +21535,13 @@
         <v>1214</v>
       </c>
       <c r="AN101" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="AO101">
-        <v>0.97803634076421897</v>
+        <v>0.99547447105677267</v>
       </c>
       <c r="AP101">
-        <v>402.6670859893182</v>
+        <v>82.96803062583389</v>
       </c>
     </row>
     <row r="102" spans="2:42">
@@ -21606,16 +21606,16 @@
         <v>747</v>
       </c>
       <c r="Y102" t="s">
-        <v>437</v>
+        <v>490</v>
       </c>
       <c r="Z102" t="s">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="AA102">
-        <v>0.95765547041534393</v>
+        <v>0.99121272120977255</v>
       </c>
       <c r="AB102">
-        <v>776.31637571869453</v>
+        <v>161.10011115417001</v>
       </c>
       <c r="AD102" t="s">
         <v>562</v>
@@ -21645,13 +21645,13 @@
         <v>1215</v>
       </c>
       <c r="AN102" t="s">
-        <v>884</v>
+        <v>860</v>
       </c>
       <c r="AO102">
-        <v>0.99267357107797494</v>
+        <v>0.98690358786307586</v>
       </c>
       <c r="AP102">
-        <v>134.31786357045974</v>
+        <v>240.10088917694185</v>
       </c>
     </row>
     <row r="103" spans="2:42">
@@ -21716,16 +21716,16 @@
         <v>749</v>
       </c>
       <c r="Y103" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="Z103" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
       <c r="AA103">
-        <v>0.98394190948405269</v>
+        <v>0.98955141276769387</v>
       </c>
       <c r="AB103">
-        <v>294.3983261257012</v>
+        <v>191.55743259227802</v>
       </c>
       <c r="AD103" t="s">
         <v>562</v>
@@ -21755,13 +21755,13 @@
         <v>1216</v>
       </c>
       <c r="AN103" t="s">
-        <v>850</v>
+        <v>879</v>
       </c>
       <c r="AO103">
-        <v>0.98837316480290893</v>
+        <v>0.9941444177652955</v>
       </c>
       <c r="AP103">
-        <v>213.15864528000296</v>
+        <v>107.35234096958277</v>
       </c>
     </row>
     <row r="104" spans="2:42">
@@ -21826,16 +21826,16 @@
         <v>751</v>
       </c>
       <c r="Y104" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="Z104" t="s">
-        <v>865</v>
+        <v>889</v>
       </c>
       <c r="AA104">
-        <v>0.97498879609676647</v>
+        <v>0.97668119298957756</v>
       </c>
       <c r="AB104">
-        <v>458.53873822594755</v>
+        <v>427.51146185774559</v>
       </c>
       <c r="AD104" t="s">
         <v>562</v>
@@ -21865,13 +21865,13 @@
         <v>1217</v>
       </c>
       <c r="AN104" t="s">
-        <v>852</v>
+        <v>891</v>
       </c>
       <c r="AO104">
-        <v>0.9924503916821712</v>
+        <v>0.99388898978830953</v>
       </c>
       <c r="AP104">
-        <v>138.40948582686161</v>
+        <v>112.03518721432623</v>
       </c>
     </row>
     <row r="105" spans="2:42">
@@ -21936,16 +21936,16 @@
         <v>753</v>
       </c>
       <c r="Y105" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="Z105" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="AA105">
-        <v>0.9903652333518761</v>
+        <v>0.98845897140196071</v>
       </c>
       <c r="AB105">
-        <v>176.63738854893887</v>
+        <v>211.58552429738629</v>
       </c>
       <c r="AD105" t="s">
         <v>562</v>
@@ -21975,13 +21975,13 @@
         <v>1218</v>
       </c>
       <c r="AN105" t="s">
-        <v>887</v>
+        <v>844</v>
       </c>
       <c r="AO105">
-        <v>0.99388898978830953</v>
+        <v>0.98965200571238932</v>
       </c>
       <c r="AP105">
-        <v>112.03518721432623</v>
+        <v>189.71322860619625</v>
       </c>
     </row>
     <row r="106" spans="2:42">
@@ -22046,16 +22046,16 @@
         <v>755</v>
       </c>
       <c r="Y106" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="Z106" t="s">
-        <v>883</v>
+        <v>841</v>
       </c>
       <c r="AA106">
-        <v>0.98359157932992225</v>
+        <v>0.98629851964686077</v>
       </c>
       <c r="AB106">
-        <v>300.82104561809257</v>
+        <v>251.19380647421841</v>
       </c>
       <c r="AD106" t="s">
         <v>562</v>
@@ -22085,13 +22085,13 @@
         <v>1219</v>
       </c>
       <c r="AN106" t="s">
-        <v>840</v>
+        <v>869</v>
       </c>
       <c r="AO106">
-        <v>0.98965200571238932</v>
+        <v>0.9865110114696487</v>
       </c>
       <c r="AP106">
-        <v>189.71322860619625</v>
+        <v>247.29812305643949</v>
       </c>
     </row>
     <row r="107" spans="2:42">
@@ -22156,16 +22156,16 @@
         <v>757</v>
       </c>
       <c r="Y107" t="s">
-        <v>467</v>
+        <v>552</v>
       </c>
       <c r="Z107" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="AA107">
-        <v>0.97154747480032433</v>
+        <v>0.98289372536542474</v>
       </c>
       <c r="AB107">
-        <v>521.62962866072098</v>
+        <v>313.61503496721377</v>
       </c>
       <c r="AD107" t="s">
         <v>562</v>
@@ -22195,13 +22195,13 @@
         <v>1220</v>
       </c>
       <c r="AN107" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="AO107">
-        <v>0.9865110114696487</v>
+        <v>0.98499499268435309</v>
       </c>
       <c r="AP107">
-        <v>247.29812305643949</v>
+        <v>275.09180078686103</v>
       </c>
     </row>
     <row r="108" spans="2:42">
@@ -22266,16 +22266,16 @@
         <v>759</v>
       </c>
       <c r="Y108" t="s">
-        <v>468</v>
+        <v>558</v>
       </c>
       <c r="Z108" t="s">
-        <v>848</v>
+        <v>890</v>
       </c>
       <c r="AA108">
-        <v>0.9790049953928549</v>
+        <v>0.99506342503584544</v>
       </c>
       <c r="AB108">
-        <v>384.908417797661</v>
+        <v>90.503874342833086</v>
       </c>
       <c r="AD108" t="s">
         <v>562</v>
@@ -22305,13 +22305,13 @@
         <v>1221</v>
       </c>
       <c r="AN108" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AO108">
-        <v>0.98499499268435309</v>
+        <v>0.99401320046908392</v>
       </c>
       <c r="AP108">
-        <v>275.09180078686103</v>
+        <v>109.75799140012764</v>
       </c>
     </row>
     <row r="109" spans="2:42">
@@ -22376,16 +22376,16 @@
         <v>761</v>
       </c>
       <c r="Y109" t="s">
-        <v>519</v>
+        <v>425</v>
       </c>
       <c r="Z109" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AA109">
-        <v>0.99512310450028352</v>
+        <v>0.99579045202592908</v>
       </c>
       <c r="AB109">
-        <v>89.409750828135486</v>
+        <v>77.175046191301078</v>
       </c>
       <c r="AD109" t="s">
         <v>562</v>
@@ -22415,13 +22415,13 @@
         <v>1222</v>
       </c>
       <c r="AN109" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="AO109">
-        <v>0.99401320046908392</v>
+        <v>0.99518979370471228</v>
       </c>
       <c r="AP109">
-        <v>109.75799140012764</v>
+        <v>88.187115413608197</v>
       </c>
     </row>
     <row r="110" spans="2:42">
@@ -22486,16 +22486,16 @@
         <v>763</v>
       </c>
       <c r="Y110" t="s">
-        <v>531</v>
+        <v>437</v>
       </c>
       <c r="Z110" t="s">
-        <v>865</v>
+        <v>844</v>
       </c>
       <c r="AA110">
-        <v>0.99180643818152092</v>
+        <v>0.95765547041534393</v>
       </c>
       <c r="AB110">
-        <v>150.21530000545005</v>
+        <v>776.31637571869453</v>
       </c>
       <c r="AD110" t="s">
         <v>562</v>
@@ -22525,13 +22525,13 @@
         <v>1223</v>
       </c>
       <c r="AN110" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="AO110">
-        <v>0.97986124669518093</v>
+        <v>0.99193701535303302</v>
       </c>
       <c r="AP110">
-        <v>369.21047725501711</v>
+        <v>147.82138519439451</v>
       </c>
     </row>
     <row r="111" spans="2:42">
@@ -22596,16 +22596,16 @@
         <v>765</v>
       </c>
       <c r="Y111" t="s">
-        <v>532</v>
+        <v>494</v>
       </c>
       <c r="Z111" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="AA111">
-        <v>0.97919938492738179</v>
+        <v>0.98394190948405269</v>
       </c>
       <c r="AB111">
-        <v>381.34460966466662</v>
+        <v>294.3983261257012</v>
       </c>
       <c r="AD111" t="s">
         <v>562</v>
@@ -22635,13 +22635,13 @@
         <v>1224</v>
       </c>
       <c r="AN111" t="s">
-        <v>890</v>
+        <v>852</v>
       </c>
       <c r="AO111">
-        <v>0.99347009078887716</v>
+        <v>0.98119061265866536</v>
       </c>
       <c r="AP111">
-        <v>119.71500220391977</v>
+        <v>344.8387679244683</v>
       </c>
     </row>
     <row r="112" spans="2:42">
@@ -22706,16 +22706,16 @@
         <v>767</v>
       </c>
       <c r="Y112" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="Z112" t="s">
-        <v>859</v>
+        <v>841</v>
       </c>
       <c r="AA112">
-        <v>0.98325714881672288</v>
+        <v>0.97498879609676647</v>
       </c>
       <c r="AB112">
-        <v>306.95227169341439</v>
+        <v>458.53873822594755</v>
       </c>
       <c r="AD112" t="s">
         <v>562</v>
@@ -22748,10 +22748,10 @@
         <v>863</v>
       </c>
       <c r="AO112">
-        <v>0.98231817048454484</v>
+        <v>0.98974332571937795</v>
       </c>
       <c r="AP112">
-        <v>324.16687445001179</v>
+        <v>188.03902847807063</v>
       </c>
     </row>
     <row r="113" spans="2:42">
@@ -22816,16 +22816,16 @@
         <v>769</v>
       </c>
       <c r="Y113" t="s">
-        <v>456</v>
+        <v>533</v>
       </c>
       <c r="Z113" t="s">
-        <v>841</v>
+        <v>892</v>
       </c>
       <c r="AA113">
-        <v>0.98602445832668828</v>
+        <v>0.9903652333518761</v>
       </c>
       <c r="AB113">
-        <v>256.2182640107153</v>
+        <v>176.63738854893887</v>
       </c>
       <c r="AD113" t="s">
         <v>562</v>
@@ -22855,13 +22855,13 @@
         <v>1226</v>
       </c>
       <c r="AN113" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="AO113">
-        <v>0.99390376443666895</v>
+        <v>0.99413168612390446</v>
       </c>
       <c r="AP113">
-        <v>111.76431866107015</v>
+        <v>107.58575439508574</v>
       </c>
     </row>
     <row r="114" spans="2:42">
@@ -22926,16 +22926,16 @@
         <v>771</v>
       </c>
       <c r="Y114" t="s">
-        <v>470</v>
+        <v>539</v>
       </c>
       <c r="Z114" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="AA114">
-        <v>0.98274955259938535</v>
+        <v>0.98359157932992225</v>
       </c>
       <c r="AB114">
-        <v>316.25820234460127</v>
+        <v>300.82104561809257</v>
       </c>
       <c r="AD114" t="s">
         <v>562</v>
@@ -22965,13 +22965,13 @@
         <v>1227</v>
       </c>
       <c r="AN114" t="s">
-        <v>866</v>
+        <v>846</v>
       </c>
       <c r="AO114">
-        <v>0.98228212315007546</v>
+        <v>0.96802468703178957</v>
       </c>
       <c r="AP114">
-        <v>324.82774224861657</v>
+        <v>586.21407108385756</v>
       </c>
     </row>
     <row r="115" spans="2:42">
@@ -23036,16 +23036,16 @@
         <v>773</v>
       </c>
       <c r="Y115" t="s">
-        <v>491</v>
+        <v>426</v>
       </c>
       <c r="Z115" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="AA115">
-        <v>0.99368873088044474</v>
+        <v>0.99359770729841634</v>
       </c>
       <c r="AB115">
-        <v>115.70660052517967</v>
+        <v>117.37536619570103</v>
       </c>
       <c r="AD115" t="s">
         <v>562</v>
@@ -23075,13 +23075,13 @@
         <v>1228</v>
       </c>
       <c r="AN115" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="AO115">
-        <v>0.99518979370471228</v>
+        <v>0.97711913570486986</v>
       </c>
       <c r="AP115">
-        <v>88.187115413608197</v>
+        <v>419.48251207738639</v>
       </c>
     </row>
     <row r="116" spans="2:42">
@@ -23146,16 +23146,16 @@
         <v>775</v>
       </c>
       <c r="Y116" t="s">
-        <v>492</v>
+        <v>432</v>
       </c>
       <c r="Z116" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="AA116">
-        <v>0.99323001255738197</v>
+        <v>0.99364006102472313</v>
       </c>
       <c r="AB116">
-        <v>124.11643644799697</v>
+        <v>116.59888121340903</v>
       </c>
       <c r="AD116" t="s">
         <v>562</v>
@@ -23185,13 +23185,13 @@
         <v>1229</v>
       </c>
       <c r="AN116" t="s">
-        <v>893</v>
+        <v>841</v>
       </c>
       <c r="AO116">
-        <v>0.99193701535303302</v>
+        <v>0.97535827976293088</v>
       </c>
       <c r="AP116">
-        <v>147.82138519439451</v>
+        <v>451.76487101293469</v>
       </c>
     </row>
     <row r="117" spans="2:42">
@@ -23256,16 +23256,16 @@
         <v>777</v>
       </c>
       <c r="Y117" t="s">
-        <v>508</v>
+        <v>447</v>
       </c>
       <c r="Z117" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="AA117">
-        <v>0.99148244782956252</v>
+        <v>0.96029753299263365</v>
       </c>
       <c r="AB117">
-        <v>156.15512312468667</v>
+        <v>727.87856180171616</v>
       </c>
       <c r="AD117" t="s">
         <v>562</v>
@@ -23295,13 +23295,13 @@
         <v>1230</v>
       </c>
       <c r="AN117" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="AO117">
-        <v>0.98119061265866536</v>
+        <v>0.9754113935826384</v>
       </c>
       <c r="AP117">
-        <v>344.8387679244683</v>
+        <v>450.79111765163026</v>
       </c>
     </row>
     <row r="118" spans="2:42">
@@ -23366,16 +23366,16 @@
         <v>779</v>
       </c>
       <c r="Y118" t="s">
-        <v>530</v>
+        <v>462</v>
       </c>
       <c r="Z118" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="AA118">
-        <v>0.96906520826310416</v>
+        <v>0.97893171539705459</v>
       </c>
       <c r="AB118">
-        <v>567.13784850975708</v>
+        <v>386.25188438733272</v>
       </c>
       <c r="AD118" t="s">
         <v>562</v>
@@ -23405,13 +23405,13 @@
         <v>1231</v>
       </c>
       <c r="AN118" t="s">
-        <v>841</v>
+        <v>883</v>
       </c>
       <c r="AO118">
-        <v>0.98974332571937795</v>
+        <v>0.99423394997920433</v>
       </c>
       <c r="AP118">
-        <v>188.03902847807063</v>
+        <v>105.71091704792103</v>
       </c>
     </row>
     <row r="119" spans="2:42">
@@ -23476,16 +23476,16 @@
         <v>781</v>
       </c>
       <c r="Y119" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="Z119" t="s">
-        <v>891</v>
+        <v>855</v>
       </c>
       <c r="AA119">
-        <v>0.98379026718553741</v>
+        <v>0.99099682968404001</v>
       </c>
       <c r="AB119">
-        <v>297.17843493181346</v>
+        <v>165.05812245926603</v>
       </c>
       <c r="AD119" t="s">
         <v>562</v>
@@ -23515,13 +23515,13 @@
         <v>1232</v>
       </c>
       <c r="AN119" t="s">
-        <v>870</v>
+        <v>853</v>
       </c>
       <c r="AO119">
-        <v>0.99413168612390446</v>
+        <v>0.99467731181029251</v>
       </c>
       <c r="AP119">
-        <v>107.58575439508574</v>
+        <v>97.582616811304106</v>
       </c>
     </row>
     <row r="120" spans="2:42">
@@ -23586,16 +23586,16 @@
         <v>783</v>
       </c>
       <c r="Y120" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="Z120" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="AA120">
-        <v>0.98593186434108759</v>
+        <v>0.97972538426958966</v>
       </c>
       <c r="AB120">
-        <v>257.91582041339416</v>
+        <v>371.70128839085726</v>
       </c>
       <c r="AD120" t="s">
         <v>562</v>
@@ -23625,13 +23625,13 @@
         <v>1233</v>
       </c>
       <c r="AN120" t="s">
-        <v>843</v>
+        <v>871</v>
       </c>
       <c r="AO120">
-        <v>0.96802468703178957</v>
+        <v>0.97803634076421897</v>
       </c>
       <c r="AP120">
-        <v>586.21407108385756</v>
+        <v>402.6670859893182</v>
       </c>
     </row>
     <row r="121" spans="2:42">
@@ -23696,16 +23696,16 @@
         <v>785</v>
       </c>
       <c r="Y121" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="Z121" t="s">
-        <v>848</v>
+        <v>893</v>
       </c>
       <c r="AA121">
-        <v>0.97774932819141058</v>
+        <v>0.98785527533632433</v>
       </c>
       <c r="AB121">
-        <v>407.92898315747328</v>
+        <v>222.65328550072056</v>
       </c>
       <c r="AD121" t="s">
         <v>562</v>
@@ -23735,13 +23735,13 @@
         <v>1234</v>
       </c>
       <c r="AN121" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="AO121">
-        <v>0.97711913570486986</v>
+        <v>0.99267357107797494</v>
       </c>
       <c r="AP121">
-        <v>419.48251207738639</v>
+        <v>134.31786357045974</v>
       </c>
     </row>
     <row r="122" spans="2:42">
@@ -23806,16 +23806,16 @@
         <v>787</v>
       </c>
       <c r="Y122" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="Z122" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="AA122">
-        <v>0.97689468820002234</v>
+        <v>0.98415070826722661</v>
       </c>
       <c r="AB122">
-        <v>423.59738299959002</v>
+        <v>290.5703484341791</v>
       </c>
       <c r="AD122" t="s">
         <v>562</v>
@@ -23845,13 +23845,13 @@
         <v>1235</v>
       </c>
       <c r="AN122" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="AO122">
-        <v>0.97535827976293088</v>
+        <v>0.98837316480290893</v>
       </c>
       <c r="AP122">
-        <v>451.76487101293469</v>
+        <v>213.15864528000296</v>
       </c>
     </row>
     <row r="123" spans="2:42">
@@ -23916,16 +23916,16 @@
         <v>789</v>
       </c>
       <c r="Y123" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="Z123" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="AA123">
-        <v>0.96097855629761675</v>
+        <v>0.9922931816569136</v>
       </c>
       <c r="AB123">
-        <v>715.39313454369221</v>
+        <v>141.29166962325118</v>
       </c>
       <c r="AD123" t="s">
         <v>562</v>
@@ -23955,13 +23955,13 @@
         <v>1236</v>
       </c>
       <c r="AN123" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="AO123">
-        <v>0.9754113935826384</v>
+        <v>0.9924503916821712</v>
       </c>
       <c r="AP123">
-        <v>450.79111765163026</v>
+        <v>138.40948582686161</v>
       </c>
     </row>
     <row r="124" spans="2:42">
@@ -24026,16 +24026,16 @@
         <v>791</v>
       </c>
       <c r="Y124" t="s">
-        <v>485</v>
+        <v>535</v>
       </c>
       <c r="Z124" t="s">
-        <v>843</v>
+        <v>878</v>
       </c>
       <c r="AA124">
-        <v>0.97961944565164727</v>
+        <v>0.99053483022914257</v>
       </c>
       <c r="AB124">
-        <v>373.64349638646644</v>
+        <v>173.52811246571903</v>
       </c>
     </row>
     <row r="125" spans="2:42">
@@ -24100,16 +24100,16 @@
         <v>793</v>
       </c>
       <c r="Y125" t="s">
-        <v>493</v>
+        <v>540</v>
       </c>
       <c r="Z125" t="s">
-        <v>849</v>
+        <v>866</v>
       </c>
       <c r="AA125">
-        <v>0.97558364374549811</v>
+        <v>0.98320360732321854</v>
       </c>
       <c r="AB125">
-        <v>447.63319799920112</v>
+        <v>307.93386574099321</v>
       </c>
     </row>
     <row r="126" spans="2:42">
@@ -24174,16 +24174,16 @@
         <v>795</v>
       </c>
       <c r="Y126" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="Z126" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AA126">
-        <v>0.98695232420711065</v>
+        <v>0.98897406466844573</v>
       </c>
       <c r="AB126">
-        <v>239.2073895363051</v>
+        <v>202.14214774516236</v>
       </c>
     </row>
     <row r="127" spans="2:42">
@@ -24248,16 +24248,16 @@
         <v>797</v>
       </c>
       <c r="Y127" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="Z127" t="s">
-        <v>892</v>
+        <v>851</v>
       </c>
       <c r="AA127">
-        <v>0.99609138632252892</v>
+        <v>0.99152145048007134</v>
       </c>
       <c r="AB127">
-        <v>71.657917420303932</v>
+        <v>155.44007453202627</v>
       </c>
     </row>
     <row r="128" spans="2:42">
@@ -24322,16 +24322,16 @@
         <v>799</v>
       </c>
       <c r="Y128" t="s">
-        <v>550</v>
+        <v>455</v>
       </c>
       <c r="Z128" t="s">
-        <v>866</v>
+        <v>894</v>
       </c>
       <c r="AA128">
-        <v>0.97457415963573191</v>
+        <v>0.98379026718553741</v>
       </c>
       <c r="AB128">
-        <v>466.14040667824753</v>
+        <v>297.17843493181346</v>
       </c>
     </row>
     <row r="129" spans="2:28">
@@ -24396,16 +24396,16 @@
         <v>801</v>
       </c>
       <c r="Y129" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="Z129" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="AA129">
-        <v>0.98213469589758429</v>
+        <v>0.98593186434108759</v>
       </c>
       <c r="AB129">
-        <v>327.53057521095576</v>
+        <v>257.91582041339416</v>
       </c>
     </row>
     <row r="130" spans="2:28">
@@ -24470,16 +24470,16 @@
         <v>803</v>
       </c>
       <c r="Y130" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="Z130" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="AA130">
-        <v>0.98161750782838286</v>
+        <v>0.97774932819141058</v>
       </c>
       <c r="AB130">
-        <v>337.01235647964734</v>
+        <v>407.92898315747328</v>
       </c>
     </row>
     <row r="131" spans="2:28">
@@ -24544,16 +24544,16 @@
         <v>805</v>
       </c>
       <c r="Y131" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="Z131" t="s">
-        <v>893</v>
+        <v>855</v>
       </c>
       <c r="AA131">
-        <v>0.98975592846808447</v>
+        <v>0.97689468820002234</v>
       </c>
       <c r="AB131">
-        <v>187.80797808511727</v>
+        <v>423.59738299959002</v>
       </c>
     </row>
     <row r="132" spans="2:28">
@@ -24618,16 +24618,16 @@
         <v>807</v>
       </c>
       <c r="Y132" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="Z132" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="AA132">
-        <v>0.97312873356481211</v>
+        <v>0.96097855629761675</v>
       </c>
       <c r="AB132">
-        <v>492.63988464511067</v>
+        <v>715.39313454369221</v>
       </c>
     </row>
     <row r="133" spans="2:28">
@@ -24692,16 +24692,16 @@
         <v>809</v>
       </c>
       <c r="Y133" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="Z133" t="s">
-        <v>894</v>
+        <v>846</v>
       </c>
       <c r="AA133">
-        <v>0.98977266598403368</v>
+        <v>0.97961944565164727</v>
       </c>
       <c r="AB133">
-        <v>187.50112362604992</v>
+        <v>373.64349638646644</v>
       </c>
     </row>
     <row r="134" spans="2:28">
@@ -24766,16 +24766,16 @@
         <v>811</v>
       </c>
       <c r="Y134" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="Z134" t="s">
         <v>871</v>
       </c>
       <c r="AA134">
-        <v>0.99537444599393454</v>
+        <v>0.97558364374549811</v>
       </c>
       <c r="AB134">
-        <v>84.801823444534008</v>
+        <v>447.63319799920112</v>
       </c>
     </row>
     <row r="135" spans="2:28">
@@ -24840,16 +24840,16 @@
         <v>813</v>
       </c>
       <c r="Y135" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="Z135" t="s">
-        <v>884</v>
+        <v>841</v>
       </c>
       <c r="AA135">
-        <v>0.99218262773253396</v>
+        <v>0.98695232420711065</v>
       </c>
       <c r="AB135">
-        <v>143.31849157021014</v>
+        <v>239.2073895363051</v>
       </c>
     </row>
     <row r="136" spans="2:28">
@@ -24914,16 +24914,16 @@
         <v>815</v>
       </c>
       <c r="Y136" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="Z136" t="s">
         <v>895</v>
       </c>
       <c r="AA136">
-        <v>0.99477407524212647</v>
+        <v>0.99609138632252892</v>
       </c>
       <c r="AB136">
-        <v>95.808620561014351</v>
+        <v>71.657917420303932</v>
       </c>
     </row>
     <row r="137" spans="2:28">
@@ -24988,16 +24988,16 @@
         <v>817</v>
       </c>
       <c r="Y137" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="Z137" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="AA137">
-        <v>0.99340406403388481</v>
+        <v>0.97457415963573191</v>
       </c>
       <c r="AB137">
-        <v>120.92549271211209</v>
+        <v>466.14040667824753</v>
       </c>
     </row>
     <row r="138" spans="2:28">
@@ -25065,7 +25065,7 @@
         <v>440</v>
       </c>
       <c r="Z138" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="AA138">
         <v>0.98669711903630763</v>
@@ -25139,7 +25139,7 @@
         <v>445</v>
       </c>
       <c r="Z139" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AA139">
         <v>0.98530250408542552</v>
@@ -25213,7 +25213,7 @@
         <v>448</v>
       </c>
       <c r="Z140" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AA140">
         <v>0.98165693570331325</v>
@@ -25287,7 +25287,7 @@
         <v>487</v>
       </c>
       <c r="Z141" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="AA141">
         <v>0.98743360691918236</v>
@@ -25435,7 +25435,7 @@
         <v>512</v>
       </c>
       <c r="Z143" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="AA143">
         <v>0.98720259752020922</v>
@@ -25509,7 +25509,7 @@
         <v>515</v>
       </c>
       <c r="Z144" t="s">
-        <v>864</v>
+        <v>889</v>
       </c>
       <c r="AA144">
         <v>0.99047826508727854</v>
@@ -25657,7 +25657,7 @@
         <v>541</v>
       </c>
       <c r="Z146" t="s">
-        <v>845</v>
+        <v>866</v>
       </c>
       <c r="AA146">
         <v>0.99098265052846923</v>
@@ -25672,7 +25672,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{784B0D07-BF27-4DCF-91A0-A5BC3B1520B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3DDB26-9D2E-4645-88DA-59B62FF7EEE0}">
   <dimension ref="B9:Z123"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -25784,7 +25784,7 @@
         <v>1339</v>
       </c>
       <c r="K11" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="L11">
         <v>27.051418854318303</v>
@@ -25817,7 +25817,7 @@
         <v>1565</v>
       </c>
       <c r="X11" t="s">
-        <v>1306</v>
+        <v>1331</v>
       </c>
       <c r="Y11">
         <v>52.78875</v>
@@ -25852,7 +25852,7 @@
         <v>1341</v>
       </c>
       <c r="K12" t="s">
-        <v>1160</v>
+        <v>1208</v>
       </c>
       <c r="L12">
         <v>57.614147689498935</v>
@@ -25885,7 +25885,7 @@
         <v>1567</v>
       </c>
       <c r="X12" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="Y12">
         <v>71.001750000000001</v>
@@ -25920,7 +25920,7 @@
         <v>1343</v>
       </c>
       <c r="K13" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="L13">
         <v>25.242848867026897</v>
@@ -25953,7 +25953,7 @@
         <v>1569</v>
       </c>
       <c r="X13" t="s">
-        <v>1334</v>
+        <v>1316</v>
       </c>
       <c r="Y13">
         <v>24.94275</v>
@@ -25988,7 +25988,7 @@
         <v>1345</v>
       </c>
       <c r="K14" t="s">
-        <v>1203</v>
+        <v>1189</v>
       </c>
       <c r="L14">
         <v>43.902302147039038</v>
@@ -26021,7 +26021,7 @@
         <v>1571</v>
       </c>
       <c r="X14" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
       <c r="Y14">
         <v>17.73075</v>
@@ -26056,7 +26056,7 @@
         <v>1347</v>
       </c>
       <c r="K15" t="s">
-        <v>1204</v>
+        <v>1190</v>
       </c>
       <c r="L15">
         <v>32.44184075061812</v>
@@ -26089,7 +26089,7 @@
         <v>1573</v>
       </c>
       <c r="X15" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="Y15">
         <v>23.870999999999999</v>
@@ -26124,7 +26124,7 @@
         <v>1349</v>
       </c>
       <c r="K16" t="s">
-        <v>1212</v>
+        <v>1231</v>
       </c>
       <c r="L16">
         <v>14.992230227018849</v>
@@ -26157,7 +26157,7 @@
         <v>1575</v>
       </c>
       <c r="X16" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="Y16">
         <v>37.262999999999998</v>
@@ -26192,7 +26192,7 @@
         <v>1351</v>
       </c>
       <c r="K17" t="s">
-        <v>1178</v>
+        <v>1142</v>
       </c>
       <c r="L17">
         <v>56.364601686534712</v>
@@ -26225,7 +26225,7 @@
         <v>1577</v>
       </c>
       <c r="X17" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="Y17">
         <v>1.7999999999999999E-2</v>
@@ -26260,7 +26260,7 @@
         <v>1353</v>
       </c>
       <c r="K18" t="s">
-        <v>1145</v>
+        <v>1202</v>
       </c>
       <c r="L18">
         <v>84.735566295985308</v>
@@ -26293,7 +26293,7 @@
         <v>1579</v>
       </c>
       <c r="X18" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="Y18">
         <v>59.504249999999999</v>
@@ -26328,7 +26328,7 @@
         <v>1355</v>
       </c>
       <c r="K19" t="s">
-        <v>1179</v>
+        <v>1143</v>
       </c>
       <c r="L19">
         <v>28.608114870958335</v>
@@ -26361,7 +26361,7 @@
         <v>1581</v>
       </c>
       <c r="X19" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
       <c r="Y19">
         <v>3.0209999999999999</v>
@@ -26396,7 +26396,7 @@
         <v>1357</v>
       </c>
       <c r="K20" t="s">
-        <v>1124</v>
+        <v>1138</v>
       </c>
       <c r="L20">
         <v>86.169947952833951</v>
@@ -26429,7 +26429,7 @@
         <v>1583</v>
       </c>
       <c r="X20" t="s">
-        <v>1307</v>
+        <v>1332</v>
       </c>
       <c r="Y20">
         <v>2.29725</v>
@@ -26464,7 +26464,7 @@
         <v>1359</v>
       </c>
       <c r="K21" t="s">
-        <v>1180</v>
+        <v>1144</v>
       </c>
       <c r="L21">
         <v>135.76851915542863</v>
@@ -26497,7 +26497,7 @@
         <v>1585</v>
       </c>
       <c r="X21" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="Y21">
         <v>4.3282499999999997</v>
@@ -26532,7 +26532,7 @@
         <v>1361</v>
       </c>
       <c r="K22" t="s">
-        <v>1223</v>
+        <v>1160</v>
       </c>
       <c r="L22">
         <v>75.454555795713105</v>
@@ -26565,7 +26565,7 @@
         <v>1587</v>
       </c>
       <c r="X22" t="s">
-        <v>1335</v>
+        <v>1317</v>
       </c>
       <c r="Y22">
         <v>15.962249999999999</v>
@@ -26600,7 +26600,7 @@
         <v>1363</v>
       </c>
       <c r="K23" t="s">
-        <v>1128</v>
+        <v>1180</v>
       </c>
       <c r="L23">
         <v>108.040942281193</v>
@@ -26633,7 +26633,7 @@
         <v>1589</v>
       </c>
       <c r="X23" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="Y23">
         <v>42.801749999999998</v>
@@ -26668,7 +26668,7 @@
         <v>1365</v>
       </c>
       <c r="K24" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="L24">
         <v>94.096948686413384</v>
@@ -26701,7 +26701,7 @@
         <v>1591</v>
       </c>
       <c r="X24" t="s">
-        <v>1329</v>
+        <v>1318</v>
       </c>
       <c r="Y24">
         <v>99.272000000000006</v>
@@ -26736,7 +26736,7 @@
         <v>1367</v>
       </c>
       <c r="K25" t="s">
-        <v>1174</v>
+        <v>1198</v>
       </c>
       <c r="L25">
         <v>8.9494246845612864</v>
@@ -26769,7 +26769,7 @@
         <v>1593</v>
       </c>
       <c r="X25" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="Y25">
         <v>91.025999999999996</v>
@@ -26804,7 +26804,7 @@
         <v>1369</v>
       </c>
       <c r="K26" t="s">
-        <v>1146</v>
+        <v>1203</v>
       </c>
       <c r="L26">
         <v>33.544698798614917</v>
@@ -26837,7 +26837,7 @@
         <v>1595</v>
       </c>
       <c r="X26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="Y26">
         <v>12.12725</v>
@@ -26872,7 +26872,7 @@
         <v>1371</v>
       </c>
       <c r="K27" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="L27">
         <v>106.84696382448234</v>
@@ -26905,7 +26905,7 @@
         <v>1597</v>
       </c>
       <c r="X27" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="Y27">
         <v>45.726999999999997</v>
@@ -26940,7 +26940,7 @@
         <v>1373</v>
       </c>
       <c r="K28" t="s">
-        <v>1161</v>
+        <v>1209</v>
       </c>
       <c r="L28">
         <v>52.9204127043377</v>
@@ -26973,7 +26973,7 @@
         <v>1599</v>
       </c>
       <c r="X28" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="Y28">
         <v>34.919249999999998</v>
@@ -27008,7 +27008,7 @@
         <v>1375</v>
       </c>
       <c r="K29" t="s">
-        <v>1175</v>
+        <v>1199</v>
       </c>
       <c r="L29">
         <v>55.916621965246243</v>
@@ -27041,7 +27041,7 @@
         <v>1601</v>
       </c>
       <c r="X29" t="s">
-        <v>1308</v>
+        <v>1333</v>
       </c>
       <c r="Y29">
         <v>40.524250000000002</v>
@@ -27076,7 +27076,7 @@
         <v>1377</v>
       </c>
       <c r="K30" t="s">
-        <v>1129</v>
+        <v>1181</v>
       </c>
       <c r="L30">
         <v>87.443747963825231</v>
@@ -27109,7 +27109,7 @@
         <v>1603</v>
       </c>
       <c r="X30" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="Y30">
         <v>0.98775000000000002</v>
@@ -27144,7 +27144,7 @@
         <v>1379</v>
       </c>
       <c r="K31" t="s">
-        <v>1181</v>
+        <v>1145</v>
       </c>
       <c r="L31">
         <v>172.5523017705126</v>
@@ -27177,7 +27177,7 @@
         <v>1605</v>
       </c>
       <c r="X31" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="Y31">
         <v>48.910499999999999</v>
@@ -27212,7 +27212,7 @@
         <v>1381</v>
       </c>
       <c r="K32" t="s">
-        <v>1205</v>
+        <v>1191</v>
       </c>
       <c r="L32">
         <v>102.98555875333584</v>
@@ -27245,7 +27245,7 @@
         <v>1607</v>
       </c>
       <c r="X32" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="Y32">
         <v>36.347749999999998</v>
@@ -27280,7 +27280,7 @@
         <v>1383</v>
       </c>
       <c r="K33" t="s">
-        <v>1169</v>
+        <v>1133</v>
       </c>
       <c r="L33">
         <v>85.200664877226515</v>
@@ -27313,7 +27313,7 @@
         <v>1609</v>
       </c>
       <c r="X33" t="s">
-        <v>1330</v>
+        <v>1319</v>
       </c>
       <c r="Y33">
         <v>67.007249999999999</v>
@@ -27348,7 +27348,7 @@
         <v>1385</v>
       </c>
       <c r="K34" t="s">
-        <v>1130</v>
+        <v>1182</v>
       </c>
       <c r="L34">
         <v>177.8003763762469</v>
@@ -27381,7 +27381,7 @@
         <v>1611</v>
       </c>
       <c r="X34" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="Y34">
         <v>1.5687500000000001</v>
@@ -27416,7 +27416,7 @@
         <v>1387</v>
       </c>
       <c r="K35" t="s">
-        <v>1137</v>
+        <v>1165</v>
       </c>
       <c r="L35">
         <v>65.743485434259441</v>
@@ -27449,7 +27449,7 @@
         <v>1613</v>
       </c>
       <c r="X35" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="Y35">
         <v>33.194249999999997</v>
@@ -27484,7 +27484,7 @@
         <v>1389</v>
       </c>
       <c r="K36" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="L36">
         <v>115.09990295278101</v>
@@ -27517,7 +27517,7 @@
         <v>1615</v>
       </c>
       <c r="X36" t="s">
-        <v>1325</v>
+        <v>1336</v>
       </c>
       <c r="Y36">
         <v>47.134250000000002</v>
@@ -27552,7 +27552,7 @@
         <v>1391</v>
       </c>
       <c r="K37" t="s">
-        <v>1213</v>
+        <v>1232</v>
       </c>
       <c r="L37">
         <v>51.347810077174991</v>
@@ -27585,7 +27585,7 @@
         <v>1617</v>
       </c>
       <c r="X37" t="s">
-        <v>1324</v>
+        <v>1338</v>
       </c>
       <c r="Y37">
         <v>55.260750000000002</v>
@@ -27620,7 +27620,7 @@
         <v>1393</v>
       </c>
       <c r="K38" t="s">
-        <v>1162</v>
+        <v>1210</v>
       </c>
       <c r="L38">
         <v>39.896721906351679</v>
@@ -27653,7 +27653,7 @@
         <v>1619</v>
       </c>
       <c r="X38" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="Y38">
         <v>0.16950000000000001</v>
@@ -27688,7 +27688,7 @@
         <v>1395</v>
       </c>
       <c r="K39" t="s">
-        <v>1170</v>
+        <v>1134</v>
       </c>
       <c r="L39">
         <v>12.342304500833409</v>
@@ -27721,7 +27721,7 @@
         <v>1621</v>
       </c>
       <c r="X39" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="Y39">
         <v>39.408499999999997</v>
@@ -27756,7 +27756,7 @@
         <v>1397</v>
       </c>
       <c r="K40" t="s">
-        <v>1206</v>
+        <v>1192</v>
       </c>
       <c r="L40">
         <v>10.648262891289743</v>
@@ -27789,7 +27789,7 @@
         <v>1623</v>
       </c>
       <c r="X40" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="Y40">
         <v>45.729750000000003</v>
@@ -27824,7 +27824,7 @@
         <v>1399</v>
       </c>
       <c r="K41" t="s">
-        <v>1163</v>
+        <v>1211</v>
       </c>
       <c r="L41">
         <v>11.96428491306677</v>
@@ -27857,7 +27857,7 @@
         <v>1625</v>
       </c>
       <c r="X41" t="s">
-        <v>1322</v>
+        <v>1315</v>
       </c>
       <c r="Y41">
         <v>20.15625</v>
@@ -27892,7 +27892,7 @@
         <v>1401</v>
       </c>
       <c r="K42" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="L42">
         <v>100.17368030050729</v>
@@ -27925,7 +27925,7 @@
         <v>1627</v>
       </c>
       <c r="X42" t="s">
-        <v>1333</v>
+        <v>1306</v>
       </c>
       <c r="Y42">
         <v>13.438750000000001</v>
@@ -27960,7 +27960,7 @@
         <v>1403</v>
       </c>
       <c r="K43" t="s">
-        <v>1131</v>
+        <v>1183</v>
       </c>
       <c r="L43">
         <v>140.78744799166597</v>
@@ -27993,7 +27993,7 @@
         <v>1629</v>
       </c>
       <c r="X43" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -28028,7 +28028,7 @@
         <v>1405</v>
       </c>
       <c r="K44" t="s">
-        <v>1138</v>
+        <v>1166</v>
       </c>
       <c r="L44">
         <v>95.626237386807603</v>
@@ -28061,7 +28061,7 @@
         <v>1631</v>
       </c>
       <c r="X44" t="s">
-        <v>1326</v>
+        <v>1337</v>
       </c>
       <c r="Y44">
         <v>3.5819999999999999</v>
@@ -28096,7 +28096,7 @@
         <v>1407</v>
       </c>
       <c r="K45" t="s">
-        <v>1196</v>
+        <v>1173</v>
       </c>
       <c r="L45">
         <v>34.163999190511113</v>
@@ -28131,7 +28131,7 @@
         <v>1409</v>
       </c>
       <c r="K46" t="s">
-        <v>1171</v>
+        <v>1135</v>
       </c>
       <c r="L46">
         <v>207.1481757149796</v>
@@ -28166,7 +28166,7 @@
         <v>1411</v>
       </c>
       <c r="K47" t="s">
-        <v>1139</v>
+        <v>1167</v>
       </c>
       <c r="L47">
         <v>111.12738154265756</v>
@@ -28201,7 +28201,7 @@
         <v>1413</v>
       </c>
       <c r="K48" t="s">
-        <v>1187</v>
+        <v>1151</v>
       </c>
       <c r="L48">
         <v>98.095071240233523</v>
@@ -28236,7 +28236,7 @@
         <v>1415</v>
       </c>
       <c r="K49" t="s">
-        <v>1151</v>
+        <v>1124</v>
       </c>
       <c r="L49">
         <v>64.315635873076587</v>
@@ -28271,7 +28271,7 @@
         <v>1417</v>
       </c>
       <c r="K50" t="s">
-        <v>1188</v>
+        <v>1152</v>
       </c>
       <c r="L50">
         <v>45.702226228379438</v>
@@ -28306,7 +28306,7 @@
         <v>1419</v>
       </c>
       <c r="K51" t="s">
-        <v>1164</v>
+        <v>1212</v>
       </c>
       <c r="L51">
         <v>59.22613388284995</v>
@@ -28341,7 +28341,7 @@
         <v>1421</v>
       </c>
       <c r="K52" t="s">
-        <v>1140</v>
+        <v>1168</v>
       </c>
       <c r="L52">
         <v>66.961183738536505</v>
@@ -28376,7 +28376,7 @@
         <v>1423</v>
       </c>
       <c r="K53" t="s">
-        <v>1125</v>
+        <v>1139</v>
       </c>
       <c r="L53">
         <v>44.273024128052612</v>
@@ -28411,7 +28411,7 @@
         <v>1425</v>
       </c>
       <c r="K54" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="L54">
         <v>46.793995714201756</v>
@@ -28446,7 +28446,7 @@
         <v>1427</v>
       </c>
       <c r="K55" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="L55">
         <v>59.530532128881013</v>
@@ -28481,7 +28481,7 @@
         <v>1429</v>
       </c>
       <c r="K56" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="L56">
         <v>89.411053786052506</v>
@@ -28516,7 +28516,7 @@
         <v>1431</v>
       </c>
       <c r="K57" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="L57">
         <v>108.09584041406336</v>
@@ -28551,7 +28551,7 @@
         <v>1433</v>
       </c>
       <c r="K58" t="s">
-        <v>1207</v>
+        <v>1193</v>
       </c>
       <c r="L58">
         <v>91.237739856046062</v>
@@ -28586,7 +28586,7 @@
         <v>1435</v>
       </c>
       <c r="K59" t="s">
-        <v>1165</v>
+        <v>1213</v>
       </c>
       <c r="L59">
         <v>192.9650320730417</v>
@@ -28621,7 +28621,7 @@
         <v>1437</v>
       </c>
       <c r="K60" t="s">
-        <v>1189</v>
+        <v>1153</v>
       </c>
       <c r="L60">
         <v>25.232461853069559</v>
@@ -28656,7 +28656,7 @@
         <v>1439</v>
       </c>
       <c r="K61" t="s">
-        <v>1152</v>
+        <v>1125</v>
       </c>
       <c r="L61">
         <v>39.902969803255665</v>
@@ -28691,7 +28691,7 @@
         <v>1441</v>
       </c>
       <c r="K62" t="s">
-        <v>1208</v>
+        <v>1194</v>
       </c>
       <c r="L62">
         <v>39.915995812987873</v>
@@ -28726,7 +28726,7 @@
         <v>1443</v>
       </c>
       <c r="K63" t="s">
-        <v>1172</v>
+        <v>1136</v>
       </c>
       <c r="L63">
         <v>34.696565986692178</v>
@@ -28761,7 +28761,7 @@
         <v>1445</v>
       </c>
       <c r="K64" t="s">
-        <v>1224</v>
+        <v>1161</v>
       </c>
       <c r="L64">
         <v>48.227180082759602</v>
@@ -28796,7 +28796,7 @@
         <v>1447</v>
       </c>
       <c r="K65" t="s">
-        <v>1190</v>
+        <v>1154</v>
       </c>
       <c r="L65">
         <v>64.191891810077777</v>
@@ -28831,7 +28831,7 @@
         <v>1449</v>
       </c>
       <c r="K66" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="L66">
         <v>80.212558918950478</v>
@@ -28866,7 +28866,7 @@
         <v>1451</v>
       </c>
       <c r="K67" t="s">
-        <v>1132</v>
+        <v>1184</v>
       </c>
       <c r="L67">
         <v>144.2227931240181</v>
@@ -28901,7 +28901,7 @@
         <v>1453</v>
       </c>
       <c r="K68" t="s">
-        <v>1214</v>
+        <v>1233</v>
       </c>
       <c r="L68">
         <v>204.53213654986922</v>
@@ -28936,7 +28936,7 @@
         <v>1455</v>
       </c>
       <c r="K69" t="s">
-        <v>1153</v>
+        <v>1126</v>
       </c>
       <c r="L69">
         <v>72.404673370923575</v>
@@ -28971,7 +28971,7 @@
         <v>1457</v>
       </c>
       <c r="K70" t="s">
-        <v>1176</v>
+        <v>1200</v>
       </c>
       <c r="L70">
         <v>64.954594485891391</v>
@@ -29006,7 +29006,7 @@
         <v>1459</v>
       </c>
       <c r="K71" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="L71">
         <v>61.916146181403967</v>
@@ -29041,7 +29041,7 @@
         <v>1461</v>
       </c>
       <c r="K72" t="s">
-        <v>1147</v>
+        <v>1204</v>
       </c>
       <c r="L72">
         <v>53.406412652926484</v>
@@ -29076,7 +29076,7 @@
         <v>1463</v>
       </c>
       <c r="K73" t="s">
-        <v>1148</v>
+        <v>1205</v>
       </c>
       <c r="L73">
         <v>37.750501639222641</v>
@@ -29111,7 +29111,7 @@
         <v>1465</v>
       </c>
       <c r="K74" t="s">
-        <v>1197</v>
+        <v>1174</v>
       </c>
       <c r="L74">
         <v>48.128176812360053</v>
@@ -29146,7 +29146,7 @@
         <v>1467</v>
       </c>
       <c r="K75" t="s">
-        <v>1215</v>
+        <v>1234</v>
       </c>
       <c r="L75">
         <v>35.264260528801714</v>
@@ -29181,7 +29181,7 @@
         <v>1469</v>
       </c>
       <c r="K76" t="s">
-        <v>1198</v>
+        <v>1175</v>
       </c>
       <c r="L76">
         <v>48.935077389045837</v>
@@ -29216,7 +29216,7 @@
         <v>1471</v>
       </c>
       <c r="K77" t="s">
-        <v>1154</v>
+        <v>1127</v>
       </c>
       <c r="L77">
         <v>8.0094170122860895</v>
@@ -29251,7 +29251,7 @@
         <v>1473</v>
       </c>
       <c r="K78" t="s">
-        <v>1225</v>
+        <v>1162</v>
       </c>
       <c r="L78">
         <v>109.65079318086688</v>
@@ -29286,7 +29286,7 @@
         <v>1475</v>
       </c>
       <c r="K79" t="s">
-        <v>1149</v>
+        <v>1206</v>
       </c>
       <c r="L79">
         <v>77.803564600712548</v>
@@ -29321,7 +29321,7 @@
         <v>1477</v>
       </c>
       <c r="K80" t="s">
-        <v>1209</v>
+        <v>1195</v>
       </c>
       <c r="L80">
         <v>67.474115268645178</v>
@@ -29356,7 +29356,7 @@
         <v>1479</v>
       </c>
       <c r="K81" t="s">
-        <v>1155</v>
+        <v>1128</v>
       </c>
       <c r="L81">
         <v>65.312013184050656</v>
@@ -29391,7 +29391,7 @@
         <v>1481</v>
       </c>
       <c r="K82" t="s">
-        <v>1182</v>
+        <v>1146</v>
       </c>
       <c r="L82">
         <v>75.218591396116096</v>
@@ -29426,7 +29426,7 @@
         <v>1483</v>
       </c>
       <c r="K83" t="s">
-        <v>1191</v>
+        <v>1155</v>
       </c>
       <c r="L83">
         <v>17.521750000000001</v>
@@ -29461,7 +29461,7 @@
         <v>1485</v>
       </c>
       <c r="K84" t="s">
-        <v>1183</v>
+        <v>1147</v>
       </c>
       <c r="L84">
         <v>52.234770000197621</v>
@@ -29496,7 +29496,7 @@
         <v>1487</v>
       </c>
       <c r="K85" t="s">
-        <v>1216</v>
+        <v>1235</v>
       </c>
       <c r="L85">
         <v>45.76084342305311</v>
@@ -29531,7 +29531,7 @@
         <v>1489</v>
       </c>
       <c r="K86" t="s">
-        <v>1156</v>
+        <v>1129</v>
       </c>
       <c r="L86">
         <v>49.108938806553653</v>
@@ -29566,7 +29566,7 @@
         <v>1491</v>
       </c>
       <c r="K87" t="s">
-        <v>1192</v>
+        <v>1156</v>
       </c>
       <c r="L87">
         <v>26.261957058240878</v>
@@ -29601,7 +29601,7 @@
         <v>1493</v>
       </c>
       <c r="K88" t="s">
-        <v>1184</v>
+        <v>1148</v>
       </c>
       <c r="L88">
         <v>13.244256296686441</v>
@@ -29636,7 +29636,7 @@
         <v>1495</v>
       </c>
       <c r="K89" t="s">
-        <v>1185</v>
+        <v>1149</v>
       </c>
       <c r="L89">
         <v>26.625616712501689</v>
@@ -29671,7 +29671,7 @@
         <v>1497</v>
       </c>
       <c r="K90" t="s">
-        <v>1126</v>
+        <v>1140</v>
       </c>
       <c r="L90">
         <v>49.153745052732859</v>
@@ -29706,7 +29706,7 @@
         <v>1499</v>
       </c>
       <c r="K91" t="s">
-        <v>1133</v>
+        <v>1185</v>
       </c>
       <c r="L91">
         <v>15.55402548304518</v>
@@ -29741,7 +29741,7 @@
         <v>1501</v>
       </c>
       <c r="K92" t="s">
-        <v>1177</v>
+        <v>1201</v>
       </c>
       <c r="L92">
         <v>62.003939746896343</v>
@@ -29776,7 +29776,7 @@
         <v>1503</v>
       </c>
       <c r="K93" t="s">
-        <v>1199</v>
+        <v>1176</v>
       </c>
       <c r="L93">
         <v>16.014965255639893</v>
@@ -29811,7 +29811,7 @@
         <v>1505</v>
       </c>
       <c r="K94" t="s">
-        <v>1193</v>
+        <v>1157</v>
       </c>
       <c r="L94">
         <v>38.584000000000003</v>
@@ -29846,7 +29846,7 @@
         <v>1507</v>
       </c>
       <c r="K95" t="s">
-        <v>1134</v>
+        <v>1186</v>
       </c>
       <c r="L95">
         <v>140.43602248182191</v>
@@ -29881,7 +29881,7 @@
         <v>1509</v>
       </c>
       <c r="K96" t="s">
-        <v>1135</v>
+        <v>1187</v>
       </c>
       <c r="L96">
         <v>150.99747268719702</v>
@@ -29916,7 +29916,7 @@
         <v>1511</v>
       </c>
       <c r="K97" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="L97">
         <v>44.73673083293798</v>
@@ -29951,7 +29951,7 @@
         <v>1513</v>
       </c>
       <c r="K98" t="s">
-        <v>1136</v>
+        <v>1188</v>
       </c>
       <c r="L98">
         <v>226.25148836074212</v>
@@ -29986,7 +29986,7 @@
         <v>1515</v>
       </c>
       <c r="K99" t="s">
-        <v>1194</v>
+        <v>1158</v>
       </c>
       <c r="L99">
         <v>18.646473949300262</v>
@@ -30021,7 +30021,7 @@
         <v>1517</v>
       </c>
       <c r="K100" t="s">
-        <v>1166</v>
+        <v>1214</v>
       </c>
       <c r="L100">
         <v>26.04488435253138</v>
@@ -30056,7 +30056,7 @@
         <v>1519</v>
       </c>
       <c r="K101" t="s">
-        <v>1150</v>
+        <v>1207</v>
       </c>
       <c r="L101">
         <v>90.393333069959539</v>
@@ -30091,7 +30091,7 @@
         <v>1521</v>
       </c>
       <c r="K102" t="s">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="L102">
         <v>113.2451692674213</v>
@@ -30126,7 +30126,7 @@
         <v>1523</v>
       </c>
       <c r="K103" t="s">
-        <v>1173</v>
+        <v>1137</v>
       </c>
       <c r="L103">
         <v>45.474002071914207</v>
@@ -30161,7 +30161,7 @@
         <v>1525</v>
       </c>
       <c r="K104" t="s">
-        <v>1157</v>
+        <v>1130</v>
       </c>
       <c r="L104">
         <v>101.1351044976128</v>
@@ -30196,7 +30196,7 @@
         <v>1527</v>
       </c>
       <c r="K105" t="s">
-        <v>1142</v>
+        <v>1170</v>
       </c>
       <c r="L105">
         <v>48.32858989272242</v>
@@ -30231,7 +30231,7 @@
         <v>1529</v>
       </c>
       <c r="K106" t="s">
-        <v>1143</v>
+        <v>1171</v>
       </c>
       <c r="L106">
         <v>139.37189500220191</v>
@@ -30266,7 +30266,7 @@
         <v>1531</v>
       </c>
       <c r="K107" t="s">
-        <v>1158</v>
+        <v>1131</v>
       </c>
       <c r="L107">
         <v>61.671957239760111</v>
@@ -30301,7 +30301,7 @@
         <v>1533</v>
       </c>
       <c r="K108" t="s">
-        <v>1210</v>
+        <v>1196</v>
       </c>
       <c r="L108">
         <v>105.33147698141694</v>
@@ -30336,7 +30336,7 @@
         <v>1535</v>
       </c>
       <c r="K109" t="s">
-        <v>1226</v>
+        <v>1163</v>
       </c>
       <c r="L109">
         <v>36.210317598354067</v>
@@ -30371,7 +30371,7 @@
         <v>1537</v>
       </c>
       <c r="K110" t="s">
-        <v>1211</v>
+        <v>1197</v>
       </c>
       <c r="L110">
         <v>90.092175297443433</v>
@@ -30406,7 +30406,7 @@
         <v>1539</v>
       </c>
       <c r="K111" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="L111">
         <v>110.96409224017792</v>
@@ -30441,7 +30441,7 @@
         <v>1541</v>
       </c>
       <c r="K112" t="s">
-        <v>1167</v>
+        <v>1215</v>
       </c>
       <c r="L112">
         <v>113.43792605984484</v>
@@ -30476,7 +30476,7 @@
         <v>1543</v>
       </c>
       <c r="K113" t="s">
-        <v>1200</v>
+        <v>1177</v>
       </c>
       <c r="L113">
         <v>31.78765414876472</v>
@@ -30511,7 +30511,7 @@
         <v>1545</v>
       </c>
       <c r="K114" t="s">
-        <v>1227</v>
+        <v>1164</v>
       </c>
       <c r="L114">
         <v>71.274548031134074</v>
@@ -30546,7 +30546,7 @@
         <v>1547</v>
       </c>
       <c r="K115" t="s">
-        <v>1159</v>
+        <v>1132</v>
       </c>
       <c r="L115">
         <v>96.887432705643064</v>
@@ -30581,7 +30581,7 @@
         <v>1549</v>
       </c>
       <c r="K116" t="s">
-        <v>1144</v>
+        <v>1172</v>
       </c>
       <c r="L116">
         <v>66.898902254497202</v>
@@ -30616,7 +30616,7 @@
         <v>1551</v>
       </c>
       <c r="K117" t="s">
-        <v>1127</v>
+        <v>1141</v>
       </c>
       <c r="L117">
         <v>114.06234142107614</v>
@@ -30651,7 +30651,7 @@
         <v>1553</v>
       </c>
       <c r="K118" t="s">
-        <v>1201</v>
+        <v>1178</v>
       </c>
       <c r="L118">
         <v>51.576115979506419</v>
@@ -30686,7 +30686,7 @@
         <v>1555</v>
       </c>
       <c r="K119" t="s">
-        <v>1195</v>
+        <v>1159</v>
       </c>
       <c r="L119">
         <v>41.324901461177753</v>
@@ -30721,7 +30721,7 @@
         <v>1557</v>
       </c>
       <c r="K120" t="s">
-        <v>1217</v>
+        <v>1236</v>
       </c>
       <c r="L120">
         <v>38.777240522327702</v>
@@ -30756,7 +30756,7 @@
         <v>1559</v>
       </c>
       <c r="K121" t="s">
-        <v>1186</v>
+        <v>1150</v>
       </c>
       <c r="L121">
         <v>36.792797269437031</v>
@@ -30791,7 +30791,7 @@
         <v>1561</v>
       </c>
       <c r="K122" t="s">
-        <v>1202</v>
+        <v>1179</v>
       </c>
       <c r="L122">
         <v>30.189135355473383</v>
@@ -30826,7 +30826,7 @@
         <v>1563</v>
       </c>
       <c r="K123" t="s">
-        <v>1168</v>
+        <v>1216</v>
       </c>
       <c r="L123">
         <v>50.047283123236681</v>
@@ -30841,7 +30841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D49D7E-7664-4C1E-9483-602F0F9E28A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD095EC1-4CE6-467F-B6C3-06C0ABD30762}">
   <dimension ref="B9:Y151"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -35661,7 +35661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEEC3B71-FF41-4040-934B-297D067F9E44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D13E1C5D-7A47-4C19-93F9-FEB7184B6C71}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
